--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94DACB40-575E-4D01-9CCB-1BF8A367BBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7830688E-CAFE-4236-A895-B5EADD5950A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{FB83DEB1-C202-4A12-A90A-344D479C9865}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="1" xr2:uid="{6DCFBA7B-C962-4AAE-A654-F8C4EFF2DA6E}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="548">
   <si>
     <t>상품코드</t>
   </si>
@@ -1534,6 +1534,120 @@
   </si>
   <si>
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 255</t>
+  </si>
+  <si>
+    <t>X-10H-GYGC</t>
+  </si>
+  <si>
+    <t>썬글라스</t>
+  </si>
+  <si>
+    <t>X-10H</t>
+  </si>
+  <si>
+    <t>공용</t>
+  </si>
+  <si>
+    <t>X-10H-GYGG</t>
+  </si>
+  <si>
+    <t>X-10H-MAGC</t>
+  </si>
+  <si>
+    <t>X-10H-MAGG</t>
+  </si>
+  <si>
+    <t>X-20FS-GYGC</t>
+  </si>
+  <si>
+    <t>X-20FS</t>
+  </si>
+  <si>
+    <t>X-20FS-GYGG</t>
+  </si>
+  <si>
+    <t>X-20FS-MAGC</t>
+  </si>
+  <si>
+    <t>X-20FS-MAGG</t>
+  </si>
+  <si>
+    <t>X-20FA-GYGC</t>
+  </si>
+  <si>
+    <t>X-20FA</t>
+  </si>
+  <si>
+    <t>X-20FA-GYGG</t>
+  </si>
+  <si>
+    <t>X-20FA-MAGC</t>
+  </si>
+  <si>
+    <t>X-20FA-MAGG</t>
+  </si>
+  <si>
+    <t>S-10HA-GYGC</t>
+  </si>
+  <si>
+    <t>S-10HA</t>
+  </si>
+  <si>
+    <t>S-10HA-GYGG</t>
+  </si>
+  <si>
+    <t>S-10HA-MAGC</t>
+  </si>
+  <si>
+    <t>S-10HA-MAGG</t>
+  </si>
+  <si>
+    <t>S-10RA-GYGC</t>
+  </si>
+  <si>
+    <t>S-10RA</t>
+  </si>
+  <si>
+    <t>S-10RA-GYGG</t>
+  </si>
+  <si>
+    <t>S-10RA-MAGC</t>
+  </si>
+  <si>
+    <t>S-10RA-MAGG</t>
+  </si>
+  <si>
+    <t>S-20R-GYGC</t>
+  </si>
+  <si>
+    <t>S-20R</t>
+  </si>
+  <si>
+    <t>S-20R-GYGG</t>
+  </si>
+  <si>
+    <t>S-20R-MAGC</t>
+  </si>
+  <si>
+    <t>S-20R-MAGG</t>
+  </si>
+  <si>
+    <t>R-10F-GYMB</t>
+  </si>
+  <si>
+    <t>R-10F</t>
+  </si>
+  <si>
+    <t>R-10F-BRMB</t>
+  </si>
+  <si>
+    <t>R-10FB-GYMB</t>
+  </si>
+  <si>
+    <t>R-10FB</t>
+  </si>
+  <si>
+    <t>R-10FB-BRMB</t>
   </si>
   <si>
     <t>날짜</t>
@@ -1952,9 +2066,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A5D413-EE80-4A15-9145-E3CF2D02BDC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F018CC-41A6-498F-A045-BBF090DBF5B1}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O231"/>
+  <dimension ref="A1:O259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -7309,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="N114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114">
         <v>3</v>
@@ -7732,7 +7846,7 @@
         <v>0</v>
       </c>
       <c r="N123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123">
         <v>1</v>
@@ -7967,7 +8081,7 @@
         <v>11</v>
       </c>
       <c r="N128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O128">
         <v>13</v>
@@ -9048,7 +9162,7 @@
         <v>0</v>
       </c>
       <c r="N151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O151">
         <v>1</v>
@@ -10035,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="N172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O172">
         <v>2</v>
@@ -10129,7 +10243,7 @@
         <v>0</v>
       </c>
       <c r="N174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O174">
         <v>2</v>
@@ -10740,7 +10854,7 @@
         <v>3</v>
       </c>
       <c r="N187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O187">
         <v>5</v>
@@ -12811,6 +12925,1154 @@
         <v>0</v>
       </c>
       <c r="O231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>498</v>
+      </c>
+      <c r="B232" t="s">
+        <v>498</v>
+      </c>
+      <c r="C232" t="s">
+        <v>499</v>
+      </c>
+      <c r="D232" t="s">
+        <v>500</v>
+      </c>
+      <c r="E232" t="s">
+        <v>501</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232" t="s">
+        <v>20</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>0</v>
+      </c>
+      <c r="O232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>502</v>
+      </c>
+      <c r="B233" t="s">
+        <v>502</v>
+      </c>
+      <c r="C233" t="s">
+        <v>499</v>
+      </c>
+      <c r="D233" t="s">
+        <v>500</v>
+      </c>
+      <c r="E233" t="s">
+        <v>501</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233" t="s">
+        <v>20</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>0</v>
+      </c>
+      <c r="O233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>503</v>
+      </c>
+      <c r="B234" t="s">
+        <v>503</v>
+      </c>
+      <c r="C234" t="s">
+        <v>499</v>
+      </c>
+      <c r="D234" t="s">
+        <v>500</v>
+      </c>
+      <c r="E234" t="s">
+        <v>501</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234" t="s">
+        <v>20</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>0</v>
+      </c>
+      <c r="O234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>504</v>
+      </c>
+      <c r="B235" t="s">
+        <v>504</v>
+      </c>
+      <c r="C235" t="s">
+        <v>499</v>
+      </c>
+      <c r="D235" t="s">
+        <v>500</v>
+      </c>
+      <c r="E235" t="s">
+        <v>501</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235" t="s">
+        <v>20</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>0</v>
+      </c>
+      <c r="N235">
+        <v>0</v>
+      </c>
+      <c r="O235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>505</v>
+      </c>
+      <c r="B236" t="s">
+        <v>505</v>
+      </c>
+      <c r="C236" t="s">
+        <v>499</v>
+      </c>
+      <c r="D236" t="s">
+        <v>506</v>
+      </c>
+      <c r="E236" t="s">
+        <v>501</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236" t="s">
+        <v>20</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>0</v>
+      </c>
+      <c r="O236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>507</v>
+      </c>
+      <c r="B237" t="s">
+        <v>507</v>
+      </c>
+      <c r="C237" t="s">
+        <v>499</v>
+      </c>
+      <c r="D237" t="s">
+        <v>506</v>
+      </c>
+      <c r="E237" t="s">
+        <v>501</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237" t="s">
+        <v>20</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>0</v>
+      </c>
+      <c r="O237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>508</v>
+      </c>
+      <c r="B238" t="s">
+        <v>508</v>
+      </c>
+      <c r="C238" t="s">
+        <v>499</v>
+      </c>
+      <c r="D238" t="s">
+        <v>506</v>
+      </c>
+      <c r="E238" t="s">
+        <v>501</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238" t="s">
+        <v>20</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>509</v>
+      </c>
+      <c r="B239" t="s">
+        <v>509</v>
+      </c>
+      <c r="C239" t="s">
+        <v>499</v>
+      </c>
+      <c r="D239" t="s">
+        <v>506</v>
+      </c>
+      <c r="E239" t="s">
+        <v>501</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239" t="s">
+        <v>20</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>0</v>
+      </c>
+      <c r="O239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>510</v>
+      </c>
+      <c r="B240" t="s">
+        <v>510</v>
+      </c>
+      <c r="C240" t="s">
+        <v>499</v>
+      </c>
+      <c r="D240" t="s">
+        <v>511</v>
+      </c>
+      <c r="E240" t="s">
+        <v>501</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240" t="s">
+        <v>20</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>0</v>
+      </c>
+      <c r="O240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>512</v>
+      </c>
+      <c r="B241" t="s">
+        <v>512</v>
+      </c>
+      <c r="C241" t="s">
+        <v>499</v>
+      </c>
+      <c r="D241" t="s">
+        <v>511</v>
+      </c>
+      <c r="E241" t="s">
+        <v>501</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241" t="s">
+        <v>20</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>0</v>
+      </c>
+      <c r="O241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>513</v>
+      </c>
+      <c r="B242" t="s">
+        <v>513</v>
+      </c>
+      <c r="C242" t="s">
+        <v>499</v>
+      </c>
+      <c r="D242" t="s">
+        <v>511</v>
+      </c>
+      <c r="E242" t="s">
+        <v>501</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242" t="s">
+        <v>20</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>514</v>
+      </c>
+      <c r="B243" t="s">
+        <v>514</v>
+      </c>
+      <c r="C243" t="s">
+        <v>499</v>
+      </c>
+      <c r="D243" t="s">
+        <v>511</v>
+      </c>
+      <c r="E243" t="s">
+        <v>501</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243" t="s">
+        <v>20</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>0</v>
+      </c>
+      <c r="O243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>515</v>
+      </c>
+      <c r="B244" t="s">
+        <v>515</v>
+      </c>
+      <c r="C244" t="s">
+        <v>499</v>
+      </c>
+      <c r="D244" t="s">
+        <v>516</v>
+      </c>
+      <c r="E244" t="s">
+        <v>501</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244" t="s">
+        <v>20</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>0</v>
+      </c>
+      <c r="O244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>517</v>
+      </c>
+      <c r="B245" t="s">
+        <v>517</v>
+      </c>
+      <c r="C245" t="s">
+        <v>499</v>
+      </c>
+      <c r="D245" t="s">
+        <v>516</v>
+      </c>
+      <c r="E245" t="s">
+        <v>501</v>
+      </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245" t="s">
+        <v>20</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>0</v>
+      </c>
+      <c r="O245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>518</v>
+      </c>
+      <c r="B246" t="s">
+        <v>518</v>
+      </c>
+      <c r="C246" t="s">
+        <v>499</v>
+      </c>
+      <c r="D246" t="s">
+        <v>516</v>
+      </c>
+      <c r="E246" t="s">
+        <v>501</v>
+      </c>
+      <c r="H246">
+        <v>0</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246" t="s">
+        <v>20</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>0</v>
+      </c>
+      <c r="O246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>519</v>
+      </c>
+      <c r="B247" t="s">
+        <v>519</v>
+      </c>
+      <c r="C247" t="s">
+        <v>499</v>
+      </c>
+      <c r="D247" t="s">
+        <v>516</v>
+      </c>
+      <c r="E247" t="s">
+        <v>501</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247">
+        <v>0</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247" t="s">
+        <v>20</v>
+      </c>
+      <c r="L247">
+        <v>0</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>0</v>
+      </c>
+      <c r="O247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>520</v>
+      </c>
+      <c r="B248" t="s">
+        <v>520</v>
+      </c>
+      <c r="C248" t="s">
+        <v>499</v>
+      </c>
+      <c r="D248" t="s">
+        <v>521</v>
+      </c>
+      <c r="E248" t="s">
+        <v>501</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248" t="s">
+        <v>20</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>0</v>
+      </c>
+      <c r="O248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>522</v>
+      </c>
+      <c r="B249" t="s">
+        <v>522</v>
+      </c>
+      <c r="C249" t="s">
+        <v>499</v>
+      </c>
+      <c r="D249" t="s">
+        <v>521</v>
+      </c>
+      <c r="E249" t="s">
+        <v>501</v>
+      </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249" t="s">
+        <v>20</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>0</v>
+      </c>
+      <c r="O249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>523</v>
+      </c>
+      <c r="B250" t="s">
+        <v>523</v>
+      </c>
+      <c r="C250" t="s">
+        <v>499</v>
+      </c>
+      <c r="D250" t="s">
+        <v>521</v>
+      </c>
+      <c r="E250" t="s">
+        <v>501</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250" t="s">
+        <v>20</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>0</v>
+      </c>
+      <c r="O250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>524</v>
+      </c>
+      <c r="B251" t="s">
+        <v>524</v>
+      </c>
+      <c r="C251" t="s">
+        <v>499</v>
+      </c>
+      <c r="D251" t="s">
+        <v>521</v>
+      </c>
+      <c r="E251" t="s">
+        <v>501</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251" t="s">
+        <v>20</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>0</v>
+      </c>
+      <c r="O251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>525</v>
+      </c>
+      <c r="B252" t="s">
+        <v>525</v>
+      </c>
+      <c r="C252" t="s">
+        <v>499</v>
+      </c>
+      <c r="D252" t="s">
+        <v>526</v>
+      </c>
+      <c r="E252" t="s">
+        <v>501</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252" t="s">
+        <v>20</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>0</v>
+      </c>
+      <c r="O252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>527</v>
+      </c>
+      <c r="B253" t="s">
+        <v>527</v>
+      </c>
+      <c r="C253" t="s">
+        <v>499</v>
+      </c>
+      <c r="D253" t="s">
+        <v>526</v>
+      </c>
+      <c r="E253" t="s">
+        <v>501</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253" t="s">
+        <v>20</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>528</v>
+      </c>
+      <c r="B254" t="s">
+        <v>528</v>
+      </c>
+      <c r="C254" t="s">
+        <v>499</v>
+      </c>
+      <c r="D254" t="s">
+        <v>526</v>
+      </c>
+      <c r="E254" t="s">
+        <v>501</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254" t="s">
+        <v>20</v>
+      </c>
+      <c r="L254">
+        <v>0</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>0</v>
+      </c>
+      <c r="O254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>529</v>
+      </c>
+      <c r="B255" t="s">
+        <v>529</v>
+      </c>
+      <c r="C255" t="s">
+        <v>499</v>
+      </c>
+      <c r="D255" t="s">
+        <v>526</v>
+      </c>
+      <c r="E255" t="s">
+        <v>501</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255" t="s">
+        <v>20</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>0</v>
+      </c>
+      <c r="O255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>530</v>
+      </c>
+      <c r="B256" t="s">
+        <v>530</v>
+      </c>
+      <c r="C256" t="s">
+        <v>499</v>
+      </c>
+      <c r="D256" t="s">
+        <v>531</v>
+      </c>
+      <c r="E256" t="s">
+        <v>501</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256" t="s">
+        <v>20</v>
+      </c>
+      <c r="L256">
+        <v>0</v>
+      </c>
+      <c r="M256">
+        <v>0</v>
+      </c>
+      <c r="N256">
+        <v>0</v>
+      </c>
+      <c r="O256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>532</v>
+      </c>
+      <c r="B257" t="s">
+        <v>532</v>
+      </c>
+      <c r="C257" t="s">
+        <v>499</v>
+      </c>
+      <c r="D257" t="s">
+        <v>531</v>
+      </c>
+      <c r="E257" t="s">
+        <v>501</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257" t="s">
+        <v>20</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>0</v>
+      </c>
+      <c r="O257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>533</v>
+      </c>
+      <c r="B258" t="s">
+        <v>533</v>
+      </c>
+      <c r="C258" t="s">
+        <v>499</v>
+      </c>
+      <c r="D258" t="s">
+        <v>534</v>
+      </c>
+      <c r="E258" t="s">
+        <v>501</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258" t="s">
+        <v>20</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
+        <v>0</v>
+      </c>
+      <c r="O258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>535</v>
+      </c>
+      <c r="B259" t="s">
+        <v>535</v>
+      </c>
+      <c r="C259" t="s">
+        <v>499</v>
+      </c>
+      <c r="D259" t="s">
+        <v>534</v>
+      </c>
+      <c r="E259" t="s">
+        <v>501</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>0</v>
+      </c>
+      <c r="K259" t="s">
+        <v>20</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>0</v>
+      </c>
+      <c r="N259">
+        <v>0</v>
+      </c>
+      <c r="O259">
         <v>0</v>
       </c>
     </row>
@@ -12821,14 +14083,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89600325-F311-4E69-B94F-AD053F6A9D62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740871F0-8E8F-4273-B48F-4A8F8DBC1DAA}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:I266"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>498</v>
+        <v>536</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -12840,10 +14102,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="F1" t="s">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -12852,7 +14114,7 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
-        <v>501</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -12869,10 +14131,10 @@
         <v>407</v>
       </c>
       <c r="E2" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F2" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G2">
         <v>255</v>
@@ -12898,10 +14160,10 @@
         <v>407</v>
       </c>
       <c r="E3" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F3" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G3">
         <v>250</v>
@@ -12927,10 +14189,10 @@
         <v>407</v>
       </c>
       <c r="E4" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F4" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G4">
         <v>240</v>
@@ -12956,10 +14218,10 @@
         <v>407</v>
       </c>
       <c r="E5" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F5" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G5">
         <v>245</v>
@@ -12985,10 +14247,10 @@
         <v>282</v>
       </c>
       <c r="E6" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F6" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G6">
         <v>240</v>
@@ -13014,10 +14276,10 @@
         <v>407</v>
       </c>
       <c r="E7" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F7" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G7">
         <v>245</v>
@@ -13043,10 +14305,10 @@
         <v>469</v>
       </c>
       <c r="E8" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F8" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G8">
         <v>235</v>
@@ -13072,10 +14334,10 @@
         <v>469</v>
       </c>
       <c r="E9" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F9" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G9">
         <v>235</v>
@@ -13101,10 +14363,10 @@
         <v>407</v>
       </c>
       <c r="E10" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F10" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G10">
         <v>235</v>
@@ -13130,10 +14392,10 @@
         <v>407</v>
       </c>
       <c r="E11" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F11" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G11">
         <v>250</v>
@@ -13159,10 +14421,10 @@
         <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F12" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G12">
         <v>260</v>
@@ -13188,10 +14450,10 @@
         <v>407</v>
       </c>
       <c r="E13" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F13" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G13">
         <v>245</v>
@@ -13217,10 +14479,10 @@
         <v>407</v>
       </c>
       <c r="E14" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F14" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G14">
         <v>255</v>
@@ -13246,10 +14508,10 @@
         <v>407</v>
       </c>
       <c r="E15" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F15" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G15">
         <v>250</v>
@@ -13275,10 +14537,10 @@
         <v>407</v>
       </c>
       <c r="E16" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F16" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G16">
         <v>250</v>
@@ -13304,10 +14566,10 @@
         <v>407</v>
       </c>
       <c r="E17" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F17" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G17">
         <v>245</v>
@@ -13333,10 +14595,10 @@
         <v>407</v>
       </c>
       <c r="E18" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F18" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G18">
         <v>245</v>
@@ -13362,10 +14624,10 @@
         <v>407</v>
       </c>
       <c r="E19" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F19" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G19">
         <v>245</v>
@@ -13391,10 +14653,10 @@
         <v>407</v>
       </c>
       <c r="E20" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F20" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G20">
         <v>245</v>
@@ -13420,10 +14682,10 @@
         <v>407</v>
       </c>
       <c r="E21" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F21" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G21">
         <v>240</v>
@@ -13449,10 +14711,10 @@
         <v>407</v>
       </c>
       <c r="E22" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F22" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G22">
         <v>245</v>
@@ -13478,10 +14740,10 @@
         <v>407</v>
       </c>
       <c r="E23" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F23" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G23">
         <v>245</v>
@@ -13507,10 +14769,10 @@
         <v>407</v>
       </c>
       <c r="E24" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F24" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G24">
         <v>245</v>
@@ -13536,10 +14798,10 @@
         <v>407</v>
       </c>
       <c r="E25" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F25" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G25">
         <v>240</v>
@@ -13565,10 +14827,10 @@
         <v>407</v>
       </c>
       <c r="E26" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F26" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G26">
         <v>245</v>
@@ -13594,10 +14856,10 @@
         <v>407</v>
       </c>
       <c r="E27" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F27" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G27">
         <v>245</v>
@@ -13623,10 +14885,10 @@
         <v>407</v>
       </c>
       <c r="E28" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F28" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G28">
         <v>250</v>
@@ -13652,10 +14914,10 @@
         <v>407</v>
       </c>
       <c r="E29" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F29" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G29">
         <v>240</v>
@@ -13681,10 +14943,10 @@
         <v>407</v>
       </c>
       <c r="E30" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F30" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G30">
         <v>240</v>
@@ -13710,10 +14972,10 @@
         <v>407</v>
       </c>
       <c r="E31" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F31" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G31">
         <v>240</v>
@@ -13739,10 +15001,10 @@
         <v>282</v>
       </c>
       <c r="E32" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F32" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G32">
         <v>245</v>
@@ -13768,10 +15030,10 @@
         <v>469</v>
       </c>
       <c r="E33" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F33" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G33">
         <v>250</v>
@@ -13797,10 +15059,10 @@
         <v>469</v>
       </c>
       <c r="E34" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F34" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G34">
         <v>245</v>
@@ -13826,10 +15088,10 @@
         <v>407</v>
       </c>
       <c r="E35" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F35" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G35">
         <v>240</v>
@@ -13855,10 +15117,10 @@
         <v>407</v>
       </c>
       <c r="E36" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F36" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G36">
         <v>240</v>
@@ -13884,10 +15146,10 @@
         <v>282</v>
       </c>
       <c r="E37" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F37" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G37">
         <v>250</v>
@@ -13913,10 +15175,10 @@
         <v>469</v>
       </c>
       <c r="E38" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F38" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G38">
         <v>240</v>
@@ -13942,10 +15204,10 @@
         <v>282</v>
       </c>
       <c r="E39" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F39" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G39">
         <v>255</v>
@@ -13971,10 +15233,10 @@
         <v>407</v>
       </c>
       <c r="E40" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F40" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G40">
         <v>240</v>
@@ -14000,10 +15262,10 @@
         <v>407</v>
       </c>
       <c r="E41" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F41" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G41">
         <v>240</v>
@@ -14029,10 +15291,10 @@
         <v>407</v>
       </c>
       <c r="E42" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F42" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G42">
         <v>240</v>
@@ -14058,10 +15320,10 @@
         <v>407</v>
       </c>
       <c r="E43" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F43" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G43">
         <v>240</v>
@@ -14087,10 +15349,10 @@
         <v>469</v>
       </c>
       <c r="E44" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F44" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G44">
         <v>245</v>
@@ -14116,10 +15378,10 @@
         <v>407</v>
       </c>
       <c r="E45" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F45" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G45">
         <v>245</v>
@@ -14145,10 +15407,10 @@
         <v>282</v>
       </c>
       <c r="E46" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F46" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G46">
         <v>240</v>
@@ -14174,10 +15436,10 @@
         <v>407</v>
       </c>
       <c r="E47" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F47" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G47">
         <v>245</v>
@@ -14203,10 +15465,10 @@
         <v>407</v>
       </c>
       <c r="E48" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F48" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G48">
         <v>235</v>
@@ -14232,10 +15494,10 @@
         <v>407</v>
       </c>
       <c r="E49" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F49" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G49">
         <v>240</v>
@@ -14261,10 +15523,10 @@
         <v>469</v>
       </c>
       <c r="E50" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F50" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G50">
         <v>240</v>
@@ -14290,10 +15552,10 @@
         <v>407</v>
       </c>
       <c r="E51" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F51" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G51">
         <v>235</v>
@@ -14319,10 +15581,10 @@
         <v>469</v>
       </c>
       <c r="E52" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F52" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G52">
         <v>235</v>
@@ -14348,10 +15610,10 @@
         <v>407</v>
       </c>
       <c r="E53" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F53" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G53">
         <v>240</v>
@@ -14377,10 +15639,10 @@
         <v>282</v>
       </c>
       <c r="E54" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F54" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G54">
         <v>250</v>
@@ -14406,10 +15668,10 @@
         <v>251</v>
       </c>
       <c r="E55" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F55" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G55">
         <v>275</v>
@@ -14435,10 +15697,10 @@
         <v>251</v>
       </c>
       <c r="E56" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F56" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G56">
         <v>275</v>
@@ -14464,10 +15726,10 @@
         <v>282</v>
       </c>
       <c r="E57" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F57" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G57">
         <v>235</v>
@@ -14493,10 +15755,10 @@
         <v>407</v>
       </c>
       <c r="E58" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F58" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G58">
         <v>255</v>
@@ -14522,10 +15784,10 @@
         <v>251</v>
       </c>
       <c r="E59" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F59" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G59">
         <v>275</v>
@@ -14551,10 +15813,10 @@
         <v>282</v>
       </c>
       <c r="E60" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F60" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G60">
         <v>240</v>
@@ -14580,10 +15842,10 @@
         <v>282</v>
       </c>
       <c r="E61" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F61" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G61">
         <v>235</v>
@@ -14609,10 +15871,10 @@
         <v>469</v>
       </c>
       <c r="E62" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F62" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G62">
         <v>240</v>
@@ -14638,10 +15900,10 @@
         <v>407</v>
       </c>
       <c r="E63" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F63" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G63">
         <v>240</v>
@@ -14667,10 +15929,10 @@
         <v>282</v>
       </c>
       <c r="E64" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F64" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G64">
         <v>255</v>
@@ -14696,10 +15958,10 @@
         <v>407</v>
       </c>
       <c r="E65" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F65" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G65">
         <v>245</v>
@@ -14725,10 +15987,10 @@
         <v>407</v>
       </c>
       <c r="E66" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F66" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G66">
         <v>240</v>
@@ -14754,10 +16016,10 @@
         <v>407</v>
       </c>
       <c r="E67" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F67" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G67">
         <v>245</v>
@@ -14783,10 +16045,10 @@
         <v>407</v>
       </c>
       <c r="E68" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F68" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G68">
         <v>235</v>
@@ -14812,10 +16074,10 @@
         <v>407</v>
       </c>
       <c r="E69" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F69" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G69">
         <v>250</v>
@@ -14841,10 +16103,10 @@
         <v>407</v>
       </c>
       <c r="E70" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F70" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G70">
         <v>240</v>
@@ -14870,10 +16132,10 @@
         <v>407</v>
       </c>
       <c r="E71" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F71" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G71">
         <v>250</v>
@@ -14899,10 +16161,10 @@
         <v>407</v>
       </c>
       <c r="E72" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F72" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G72">
         <v>255</v>
@@ -14928,10 +16190,10 @@
         <v>469</v>
       </c>
       <c r="E73" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F73" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G73">
         <v>240</v>
@@ -14957,10 +16219,10 @@
         <v>282</v>
       </c>
       <c r="E74" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F74" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="G74">
         <v>250</v>
@@ -14986,10 +16248,10 @@
         <v>407</v>
       </c>
       <c r="E75" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F75" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="G75">
         <v>250</v>
@@ -15015,10 +16277,10 @@
         <v>438</v>
       </c>
       <c r="E76" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F76" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="G76">
         <v>250</v>
@@ -15044,10 +16306,10 @@
         <v>407</v>
       </c>
       <c r="E77" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F77" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="G77">
         <v>235</v>
@@ -15073,10 +16335,10 @@
         <v>304</v>
       </c>
       <c r="E78" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F78" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="G78">
         <v>235</v>
@@ -15102,10 +16364,10 @@
         <v>168</v>
       </c>
       <c r="E79" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F79" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G79">
         <v>275</v>
@@ -15131,10 +16393,10 @@
         <v>407</v>
       </c>
       <c r="E80" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F80" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G80">
         <v>245</v>
@@ -15160,10 +16422,10 @@
         <v>407</v>
       </c>
       <c r="E81" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F81" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G81">
         <v>235</v>
@@ -15189,10 +16451,10 @@
         <v>407</v>
       </c>
       <c r="E82" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F82" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G82">
         <v>240</v>
@@ -15218,10 +16480,10 @@
         <v>407</v>
       </c>
       <c r="E83" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F83" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G83">
         <v>235</v>
@@ -15247,10 +16509,10 @@
         <v>407</v>
       </c>
       <c r="E84" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F84" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G84">
         <v>250</v>
@@ -15276,10 +16538,10 @@
         <v>407</v>
       </c>
       <c r="E85" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F85" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G85">
         <v>255</v>
@@ -15305,10 +16567,10 @@
         <v>407</v>
       </c>
       <c r="E86" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F86" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G86">
         <v>240</v>
@@ -15334,10 +16596,10 @@
         <v>407</v>
       </c>
       <c r="E87" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F87" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G87">
         <v>235</v>
@@ -15363,10 +16625,10 @@
         <v>407</v>
       </c>
       <c r="E88" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F88" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G88">
         <v>235</v>
@@ -15392,10 +16654,10 @@
         <v>407</v>
       </c>
       <c r="E89" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F89" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G89">
         <v>240</v>
@@ -15421,10 +16683,10 @@
         <v>407</v>
       </c>
       <c r="E90" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F90" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G90">
         <v>250</v>
@@ -15450,10 +16712,10 @@
         <v>407</v>
       </c>
       <c r="E91" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F91" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G91">
         <v>240</v>
@@ -15479,10 +16741,10 @@
         <v>407</v>
       </c>
       <c r="E92" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F92" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G92">
         <v>245</v>
@@ -15508,10 +16770,10 @@
         <v>407</v>
       </c>
       <c r="E93" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F93" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G93">
         <v>250</v>
@@ -15537,10 +16799,10 @@
         <v>407</v>
       </c>
       <c r="E94" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F94" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G94">
         <v>255</v>
@@ -15566,10 +16828,10 @@
         <v>407</v>
       </c>
       <c r="E95" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F95" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G95">
         <v>245</v>
@@ -15595,10 +16857,10 @@
         <v>407</v>
       </c>
       <c r="E96" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F96" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G96">
         <v>240</v>
@@ -15624,10 +16886,10 @@
         <v>407</v>
       </c>
       <c r="E97" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F97" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G97">
         <v>240</v>
@@ -15653,10 +16915,10 @@
         <v>407</v>
       </c>
       <c r="E98" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F98" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G98">
         <v>240</v>
@@ -15682,10 +16944,10 @@
         <v>407</v>
       </c>
       <c r="E99" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F99" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G99">
         <v>245</v>
@@ -15711,10 +16973,10 @@
         <v>251</v>
       </c>
       <c r="E100" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F100" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G100">
         <v>270</v>
@@ -15740,10 +17002,10 @@
         <v>251</v>
       </c>
       <c r="E101" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F101" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G101">
         <v>265</v>
@@ -15769,10 +17031,10 @@
         <v>251</v>
       </c>
       <c r="E102" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F102" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G102">
         <v>265</v>
@@ -15798,10 +17060,10 @@
         <v>251</v>
       </c>
       <c r="E103" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F103" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G103">
         <v>265</v>
@@ -15827,10 +17089,10 @@
         <v>251</v>
       </c>
       <c r="E104" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F104" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G104">
         <v>280</v>
@@ -15856,10 +17118,10 @@
         <v>469</v>
       </c>
       <c r="E105" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F105" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G105">
         <v>240</v>
@@ -15885,10 +17147,10 @@
         <v>469</v>
       </c>
       <c r="E106" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F106" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G106">
         <v>240</v>
@@ -15914,10 +17176,10 @@
         <v>469</v>
       </c>
       <c r="E107" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F107" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G107">
         <v>245</v>
@@ -15943,10 +17205,10 @@
         <v>469</v>
       </c>
       <c r="E108" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F108" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G108">
         <v>240</v>
@@ -15972,10 +17234,10 @@
         <v>469</v>
       </c>
       <c r="E109" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F109" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G109">
         <v>250</v>
@@ -16001,10 +17263,10 @@
         <v>282</v>
       </c>
       <c r="E110" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F110" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G110">
         <v>250</v>
@@ -16030,10 +17292,10 @@
         <v>282</v>
       </c>
       <c r="E111" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F111" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G111">
         <v>240</v>
@@ -16059,10 +17321,10 @@
         <v>282</v>
       </c>
       <c r="E112" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F112" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G112">
         <v>250</v>
@@ -16088,10 +17350,10 @@
         <v>282</v>
       </c>
       <c r="E113" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F113" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G113">
         <v>250</v>
@@ -16117,10 +17379,10 @@
         <v>282</v>
       </c>
       <c r="E114" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F114" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G114">
         <v>245</v>
@@ -16146,10 +17408,10 @@
         <v>407</v>
       </c>
       <c r="E115" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F115" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G115">
         <v>240</v>
@@ -16175,10 +17437,10 @@
         <v>407</v>
       </c>
       <c r="E116" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F116" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G116">
         <v>255</v>
@@ -16204,10 +17466,10 @@
         <v>407</v>
       </c>
       <c r="E117" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F117" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G117">
         <v>250</v>
@@ -16233,10 +17495,10 @@
         <v>407</v>
       </c>
       <c r="E118" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F118" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G118">
         <v>240</v>
@@ -16262,10 +17524,10 @@
         <v>407</v>
       </c>
       <c r="E119" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F119" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G119">
         <v>235</v>
@@ -16291,10 +17553,10 @@
         <v>469</v>
       </c>
       <c r="E120" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F120" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G120">
         <v>245</v>
@@ -16320,10 +17582,10 @@
         <v>469</v>
       </c>
       <c r="E121" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F121" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G121">
         <v>240</v>
@@ -16349,10 +17611,10 @@
         <v>469</v>
       </c>
       <c r="E122" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F122" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G122">
         <v>240</v>
@@ -16378,10 +17640,10 @@
         <v>469</v>
       </c>
       <c r="E123" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F123" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G123">
         <v>240</v>
@@ -16407,10 +17669,10 @@
         <v>469</v>
       </c>
       <c r="E124" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F124" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G124">
         <v>235</v>
@@ -16436,10 +17698,10 @@
         <v>282</v>
       </c>
       <c r="E125" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F125" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G125">
         <v>245</v>
@@ -16465,10 +17727,10 @@
         <v>282</v>
       </c>
       <c r="E126" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F126" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G126">
         <v>245</v>
@@ -16494,10 +17756,10 @@
         <v>282</v>
       </c>
       <c r="E127" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F127" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G127">
         <v>235</v>
@@ -16523,10 +17785,10 @@
         <v>282</v>
       </c>
       <c r="E128" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F128" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G128">
         <v>235</v>
@@ -16552,10 +17814,10 @@
         <v>282</v>
       </c>
       <c r="E129" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F129" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G129">
         <v>235</v>
@@ -16581,10 +17843,10 @@
         <v>282</v>
       </c>
       <c r="E130" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F130" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G130">
         <v>235</v>
@@ -16610,10 +17872,10 @@
         <v>282</v>
       </c>
       <c r="E131" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F131" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G131">
         <v>235</v>
@@ -16639,10 +17901,10 @@
         <v>282</v>
       </c>
       <c r="E132" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F132" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G132">
         <v>235</v>
@@ -16668,10 +17930,10 @@
         <v>282</v>
       </c>
       <c r="E133" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F133" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G133">
         <v>235</v>
@@ -16697,10 +17959,10 @@
         <v>282</v>
       </c>
       <c r="E134" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F134" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G134">
         <v>250</v>
@@ -16726,10 +17988,10 @@
         <v>282</v>
       </c>
       <c r="E135" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F135" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G135">
         <v>250</v>
@@ -16755,10 +18017,10 @@
         <v>282</v>
       </c>
       <c r="E136" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F136" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G136">
         <v>245</v>
@@ -16784,10 +18046,10 @@
         <v>282</v>
       </c>
       <c r="E137" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F137" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G137">
         <v>245</v>
@@ -16813,10 +18075,10 @@
         <v>282</v>
       </c>
       <c r="E138" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F138" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G138">
         <v>245</v>
@@ -16842,10 +18104,10 @@
         <v>282</v>
       </c>
       <c r="E139" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F139" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G139">
         <v>245</v>
@@ -16871,10 +18133,10 @@
         <v>282</v>
       </c>
       <c r="E140" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F140" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G140">
         <v>240</v>
@@ -16900,10 +18162,10 @@
         <v>282</v>
       </c>
       <c r="E141" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F141" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G141">
         <v>240</v>
@@ -16929,10 +18191,10 @@
         <v>282</v>
       </c>
       <c r="E142" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F142" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G142">
         <v>235</v>
@@ -16958,10 +18220,10 @@
         <v>282</v>
       </c>
       <c r="E143" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F143" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G143">
         <v>235</v>
@@ -16987,10 +18249,10 @@
         <v>407</v>
       </c>
       <c r="E144" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F144" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G144">
         <v>235</v>
@@ -17016,10 +18278,10 @@
         <v>469</v>
       </c>
       <c r="E145" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F145" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G145">
         <v>240</v>
@@ -17045,10 +18307,10 @@
         <v>282</v>
       </c>
       <c r="E146" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F146" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G146">
         <v>235</v>
@@ -17074,10 +18336,10 @@
         <v>469</v>
       </c>
       <c r="E147" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F147" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G147">
         <v>235</v>
@@ -17103,10 +18365,10 @@
         <v>469</v>
       </c>
       <c r="E148" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F148" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G148">
         <v>240</v>
@@ -17132,10 +18394,10 @@
         <v>407</v>
       </c>
       <c r="E149" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F149" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G149">
         <v>255</v>
@@ -17161,10 +18423,10 @@
         <v>282</v>
       </c>
       <c r="E150" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F150" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G150">
         <v>240</v>
@@ -17190,10 +18452,10 @@
         <v>469</v>
       </c>
       <c r="E151" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F151" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G151">
         <v>245</v>
@@ -17219,10 +18481,10 @@
         <v>469</v>
       </c>
       <c r="E152" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F152" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G152">
         <v>235</v>
@@ -17248,10 +18510,10 @@
         <v>251</v>
       </c>
       <c r="E153" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F153" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G153">
         <v>275</v>
@@ -17277,10 +18539,10 @@
         <v>407</v>
       </c>
       <c r="E154" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F154" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G154">
         <v>240</v>
@@ -17306,10 +18568,10 @@
         <v>282</v>
       </c>
       <c r="E155" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F155" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G155">
         <v>240</v>
@@ -17335,10 +18597,10 @@
         <v>251</v>
       </c>
       <c r="E156" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F156" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G156">
         <v>260</v>
@@ -17364,10 +18626,10 @@
         <v>469</v>
       </c>
       <c r="E157" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F157" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G157">
         <v>245</v>
@@ -17393,10 +18655,10 @@
         <v>282</v>
       </c>
       <c r="E158" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F158" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G158">
         <v>240</v>
@@ -17422,10 +18684,10 @@
         <v>251</v>
       </c>
       <c r="E159" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F159" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G159">
         <v>270</v>
@@ -17451,10 +18713,10 @@
         <v>407</v>
       </c>
       <c r="E160" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F160" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G160">
         <v>245</v>
@@ -17480,10 +18742,10 @@
         <v>251</v>
       </c>
       <c r="E161" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F161" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G161">
         <v>260</v>
@@ -17509,10 +18771,10 @@
         <v>282</v>
       </c>
       <c r="E162" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F162" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G162">
         <v>240</v>
@@ -17538,10 +18800,10 @@
         <v>469</v>
       </c>
       <c r="E163" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F163" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G163">
         <v>240</v>
@@ -17567,10 +18829,10 @@
         <v>282</v>
       </c>
       <c r="E164" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F164" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G164">
         <v>235</v>
@@ -17596,10 +18858,10 @@
         <v>407</v>
       </c>
       <c r="E165" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F165" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G165">
         <v>245</v>
@@ -17625,10 +18887,10 @@
         <v>282</v>
       </c>
       <c r="E166" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F166" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G166">
         <v>240</v>
@@ -17654,10 +18916,10 @@
         <v>407</v>
       </c>
       <c r="E167" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F167" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G167">
         <v>250</v>
@@ -17683,10 +18945,10 @@
         <v>469</v>
       </c>
       <c r="E168" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F168" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G168">
         <v>245</v>
@@ -17712,10 +18974,10 @@
         <v>469</v>
       </c>
       <c r="E169" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F169" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G169">
         <v>240</v>
@@ -17741,10 +19003,10 @@
         <v>282</v>
       </c>
       <c r="E170" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F170" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G170">
         <v>250</v>
@@ -17770,10 +19032,10 @@
         <v>251</v>
       </c>
       <c r="E171" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F171" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G171">
         <v>280</v>
@@ -17799,10 +19061,10 @@
         <v>18</v>
       </c>
       <c r="E172" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F172" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G172">
         <v>265</v>
@@ -17828,10 +19090,10 @@
         <v>282</v>
       </c>
       <c r="E173" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F173" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G173">
         <v>240</v>
@@ -17857,10 +19119,10 @@
         <v>407</v>
       </c>
       <c r="E174" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F174" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G174">
         <v>255</v>
@@ -17886,10 +19148,10 @@
         <v>407</v>
       </c>
       <c r="E175" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F175" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G175">
         <v>250</v>
@@ -17915,10 +19177,10 @@
         <v>407</v>
       </c>
       <c r="E176" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F176" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G176">
         <v>250</v>
@@ -17944,10 +19206,10 @@
         <v>407</v>
       </c>
       <c r="E177" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F177" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G177">
         <v>245</v>
@@ -17973,10 +19235,10 @@
         <v>407</v>
       </c>
       <c r="E178" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F178" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G178">
         <v>240</v>
@@ -18002,10 +19264,10 @@
         <v>407</v>
       </c>
       <c r="E179" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F179" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G179">
         <v>240</v>
@@ -18031,10 +19293,10 @@
         <v>469</v>
       </c>
       <c r="E180" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F180" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G180">
         <v>240</v>
@@ -18060,10 +19322,10 @@
         <v>469</v>
       </c>
       <c r="E181" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F181" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G181">
         <v>245</v>
@@ -18089,10 +19351,10 @@
         <v>407</v>
       </c>
       <c r="E182" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F182" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G182">
         <v>235</v>
@@ -18118,10 +19380,10 @@
         <v>469</v>
       </c>
       <c r="E183" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F183" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G183">
         <v>235</v>
@@ -18147,10 +19409,10 @@
         <v>304</v>
       </c>
       <c r="E184" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F184" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G184">
         <v>250</v>
@@ -18176,10 +19438,10 @@
         <v>304</v>
       </c>
       <c r="E185" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F185" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G185">
         <v>250</v>
@@ -18205,10 +19467,10 @@
         <v>469</v>
       </c>
       <c r="E186" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F186" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G186">
         <v>245</v>
@@ -18234,10 +19496,10 @@
         <v>376</v>
       </c>
       <c r="E187" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F187" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G187">
         <v>235</v>
@@ -18263,10 +19525,10 @@
         <v>282</v>
       </c>
       <c r="E188" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F188" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G188">
         <v>245</v>
@@ -18292,10 +19554,10 @@
         <v>469</v>
       </c>
       <c r="E189" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F189" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G189">
         <v>250</v>
@@ -18321,10 +19583,10 @@
         <v>407</v>
       </c>
       <c r="E190" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F190" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G190">
         <v>245</v>
@@ -18350,10 +19612,10 @@
         <v>407</v>
       </c>
       <c r="E191" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F191" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G191">
         <v>250</v>
@@ -18379,10 +19641,10 @@
         <v>407</v>
       </c>
       <c r="E192" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F192" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G192">
         <v>235</v>
@@ -18408,10 +19670,10 @@
         <v>407</v>
       </c>
       <c r="E193" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F193" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G193">
         <v>240</v>
@@ -18437,10 +19699,10 @@
         <v>282</v>
       </c>
       <c r="E194" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F194" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G194">
         <v>235</v>
@@ -18466,10 +19728,10 @@
         <v>282</v>
       </c>
       <c r="E195" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F195" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G195">
         <v>245</v>
@@ -18495,10 +19757,10 @@
         <v>199</v>
       </c>
       <c r="E196" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F196" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G196">
         <v>265</v>
@@ -18524,10 +19786,10 @@
         <v>407</v>
       </c>
       <c r="E197" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F197" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G197">
         <v>245</v>
@@ -18553,10 +19815,10 @@
         <v>407</v>
       </c>
       <c r="E198" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F198" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G198">
         <v>240</v>
@@ -18582,10 +19844,10 @@
         <v>407</v>
       </c>
       <c r="E199" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F199" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G199">
         <v>240</v>
@@ -18611,10 +19873,10 @@
         <v>407</v>
       </c>
       <c r="E200" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F200" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G200">
         <v>235</v>
@@ -18640,10 +19902,10 @@
         <v>251</v>
       </c>
       <c r="E201" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F201" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G201">
         <v>260</v>
@@ -18669,10 +19931,10 @@
         <v>251</v>
       </c>
       <c r="E202" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F202" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G202">
         <v>270</v>
@@ -18698,10 +19960,10 @@
         <v>407</v>
       </c>
       <c r="E203" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F203" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G203">
         <v>235</v>
@@ -18727,10 +19989,10 @@
         <v>407</v>
       </c>
       <c r="E204" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F204" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G204">
         <v>240</v>
@@ -18756,10 +20018,10 @@
         <v>376</v>
       </c>
       <c r="E205" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F205" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G205">
         <v>250</v>
@@ -18785,10 +20047,10 @@
         <v>438</v>
       </c>
       <c r="E206" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F206" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G206">
         <v>250</v>
@@ -18814,10 +20076,10 @@
         <v>376</v>
       </c>
       <c r="E207" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F207" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G207">
         <v>240</v>
@@ -18843,10 +20105,10 @@
         <v>376</v>
       </c>
       <c r="E208" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F208" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G208">
         <v>250</v>
@@ -18872,10 +20134,10 @@
         <v>376</v>
       </c>
       <c r="E209" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F209" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G209">
         <v>255</v>
@@ -18901,10 +20163,10 @@
         <v>376</v>
       </c>
       <c r="E210" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F210" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G210">
         <v>255</v>
@@ -18930,10 +20192,10 @@
         <v>251</v>
       </c>
       <c r="E211" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F211" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G211">
         <v>270</v>
@@ -18959,10 +20221,10 @@
         <v>282</v>
       </c>
       <c r="E212" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F212" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G212">
         <v>250</v>
@@ -18988,10 +20250,10 @@
         <v>304</v>
       </c>
       <c r="E213" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F213" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G213">
         <v>240</v>
@@ -19017,10 +20279,10 @@
         <v>304</v>
       </c>
       <c r="E214" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F214" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G214">
         <v>250</v>
@@ -19046,10 +20308,10 @@
         <v>251</v>
       </c>
       <c r="E215" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F215" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G215">
         <v>260</v>
@@ -19075,10 +20337,10 @@
         <v>407</v>
       </c>
       <c r="E216" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F216" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G216">
         <v>240</v>
@@ -19104,10 +20366,10 @@
         <v>376</v>
       </c>
       <c r="E217" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F217" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G217">
         <v>245</v>
@@ -19133,10 +20395,10 @@
         <v>251</v>
       </c>
       <c r="E218" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F218" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G218">
         <v>265</v>
@@ -19162,10 +20424,10 @@
         <v>282</v>
       </c>
       <c r="E219" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F219" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G219">
         <v>235</v>
@@ -19191,10 +20453,10 @@
         <v>282</v>
       </c>
       <c r="E220" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F220" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G220">
         <v>245</v>
@@ -19220,10 +20482,10 @@
         <v>282</v>
       </c>
       <c r="E221" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F221" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G221">
         <v>240</v>
@@ -19249,10 +20511,10 @@
         <v>282</v>
       </c>
       <c r="E222" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F222" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G222">
         <v>240</v>
@@ -19278,10 +20540,10 @@
         <v>282</v>
       </c>
       <c r="E223" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F223" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G223">
         <v>235</v>
@@ -19307,10 +20569,10 @@
         <v>282</v>
       </c>
       <c r="E224" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F224" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G224">
         <v>240</v>
@@ -19336,10 +20598,10 @@
         <v>282</v>
       </c>
       <c r="E225" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F225" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G225">
         <v>240</v>
@@ -19365,10 +20627,10 @@
         <v>469</v>
       </c>
       <c r="E226" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F226" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G226">
         <v>250</v>
@@ -19394,10 +20656,10 @@
         <v>469</v>
       </c>
       <c r="E227" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F227" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G227">
         <v>250</v>
@@ -19423,10 +20685,10 @@
         <v>282</v>
       </c>
       <c r="E228" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F228" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G228">
         <v>240</v>
@@ -19452,10 +20714,10 @@
         <v>469</v>
       </c>
       <c r="E229" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F229" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G229">
         <v>245</v>
@@ -19481,10 +20743,10 @@
         <v>469</v>
       </c>
       <c r="E230" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F230" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G230">
         <v>245</v>
@@ -19510,10 +20772,10 @@
         <v>469</v>
       </c>
       <c r="E231" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F231" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G231">
         <v>240</v>
@@ -19539,10 +20801,10 @@
         <v>469</v>
       </c>
       <c r="E232" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F232" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G232">
         <v>235</v>
@@ -19568,10 +20830,10 @@
         <v>469</v>
       </c>
       <c r="E233" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F233" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G233">
         <v>235</v>
@@ -19597,10 +20859,10 @@
         <v>469</v>
       </c>
       <c r="E234" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F234" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G234">
         <v>235</v>
@@ -19626,10 +20888,10 @@
         <v>469</v>
       </c>
       <c r="E235" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F235" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G235">
         <v>235</v>
@@ -19655,10 +20917,10 @@
         <v>469</v>
       </c>
       <c r="E236" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F236" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G236">
         <v>255</v>
@@ -19684,10 +20946,10 @@
         <v>469</v>
       </c>
       <c r="E237" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F237" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G237">
         <v>250</v>
@@ -19713,10 +20975,10 @@
         <v>469</v>
       </c>
       <c r="E238" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F238" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G238">
         <v>250</v>
@@ -19742,10 +21004,10 @@
         <v>282</v>
       </c>
       <c r="E239" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F239" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G239">
         <v>240</v>
@@ -19771,10 +21033,10 @@
         <v>469</v>
       </c>
       <c r="E240" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F240" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G240">
         <v>250</v>
@@ -19800,10 +21062,10 @@
         <v>469</v>
       </c>
       <c r="E241" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F241" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G241">
         <v>250</v>
@@ -19829,10 +21091,10 @@
         <v>469</v>
       </c>
       <c r="E242" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F242" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G242">
         <v>250</v>
@@ -19858,10 +21120,10 @@
         <v>469</v>
       </c>
       <c r="E243" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F243" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G243">
         <v>250</v>
@@ -19887,10 +21149,10 @@
         <v>469</v>
       </c>
       <c r="E244" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F244" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G244">
         <v>245</v>
@@ -19916,10 +21178,10 @@
         <v>469</v>
       </c>
       <c r="E245" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F245" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G245">
         <v>240</v>
@@ -19945,10 +21207,10 @@
         <v>469</v>
       </c>
       <c r="E246" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F246" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G246">
         <v>240</v>
@@ -19974,10 +21236,10 @@
         <v>469</v>
       </c>
       <c r="E247" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F247" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G247">
         <v>240</v>
@@ -20003,10 +21265,10 @@
         <v>282</v>
       </c>
       <c r="E248" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F248" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G248">
         <v>245</v>
@@ -20032,10 +21294,10 @@
         <v>282</v>
       </c>
       <c r="E249" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F249" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G249">
         <v>245</v>
@@ -20061,10 +21323,10 @@
         <v>282</v>
       </c>
       <c r="E250" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F250" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G250">
         <v>235</v>
@@ -20090,10 +21352,10 @@
         <v>282</v>
       </c>
       <c r="E251" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F251" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G251">
         <v>240</v>
@@ -20119,10 +21381,10 @@
         <v>304</v>
       </c>
       <c r="E252" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F252" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G252">
         <v>255</v>
@@ -20148,10 +21410,10 @@
         <v>376</v>
       </c>
       <c r="E253" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F253" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G253">
         <v>245</v>
@@ -20177,10 +21439,10 @@
         <v>407</v>
       </c>
       <c r="E254" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F254" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G254">
         <v>235</v>
@@ -20206,10 +21468,10 @@
         <v>251</v>
       </c>
       <c r="E255" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F255" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G255">
         <v>270</v>
@@ -20235,10 +21497,10 @@
         <v>251</v>
       </c>
       <c r="E256" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F256" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G256">
         <v>265</v>
@@ -20264,10 +21526,10 @@
         <v>376</v>
       </c>
       <c r="E257" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F257" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G257">
         <v>235</v>
@@ -20293,10 +21555,10 @@
         <v>251</v>
       </c>
       <c r="E258" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F258" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G258">
         <v>260</v>
@@ -20322,10 +21584,10 @@
         <v>168</v>
       </c>
       <c r="E259" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F259" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G259">
         <v>265</v>
@@ -20351,10 +21613,10 @@
         <v>282</v>
       </c>
       <c r="E260" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F260" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G260">
         <v>235</v>
@@ -20380,10 +21642,10 @@
         <v>469</v>
       </c>
       <c r="E261" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F261" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G261">
         <v>240</v>
@@ -20409,10 +21671,10 @@
         <v>376</v>
       </c>
       <c r="E262" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F262" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G262">
         <v>240</v>
@@ -20438,10 +21700,10 @@
         <v>376</v>
       </c>
       <c r="E263" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F263" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G263">
         <v>255</v>
@@ -20467,10 +21729,10 @@
         <v>376</v>
       </c>
       <c r="E264" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="F264" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G264">
         <v>235</v>
@@ -20496,10 +21758,10 @@
         <v>251</v>
       </c>
       <c r="E265" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="F265" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G265">
         <v>265</v>
@@ -20525,10 +21787,10 @@
         <v>168</v>
       </c>
       <c r="E266" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="F266" t="s">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="G266">
         <v>265</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E6E241B-5119-4640-8E61-420244025491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B676322F-E9EA-450C-99BD-EC99409983F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{14D1A837-EBA5-4F4D-AC20-023F09515306}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{14D1A837-EBA5-4F4D-AC20-023F09515306}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
     <sheet name="주문로그" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -14957,6 +14957,12 @@
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J266"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B676322F-E9EA-450C-99BD-EC99409983F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37AE0EEB-BF92-48DD-8407-AD3D2BE02F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{14D1A837-EBA5-4F4D-AC20-023F09515306}"/>
+    <workbookView xWindow="10005" yWindow="1800" windowWidth="18645" windowHeight="11295" xr2:uid="{8431F63A-43AF-4E48-9552-806C0F9D2A65}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
     <sheet name="주문로그" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3687" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="552">
   <si>
     <t>날짜</t>
   </si>
@@ -342,6 +342,57 @@
     <t>CS출고</t>
   </si>
   <si>
+    <t>X-10H-GYGC</t>
+  </si>
+  <si>
+    <t>스포츠선글라스</t>
+  </si>
+  <si>
+    <t>X-10H</t>
+  </si>
+  <si>
+    <t>공용</t>
+  </si>
+  <si>
+    <t>X-20FS-GYGG</t>
+  </si>
+  <si>
+    <t>X-20FS</t>
+  </si>
+  <si>
+    <t>S-20R-MAGG</t>
+  </si>
+  <si>
+    <t>S-20R</t>
+  </si>
+  <si>
+    <t>스토어팜</t>
+  </si>
+  <si>
+    <t>X-20FA-GYGG</t>
+  </si>
+  <si>
+    <t>X-20FA</t>
+  </si>
+  <si>
+    <t>직원구매</t>
+  </si>
+  <si>
+    <t>R-10F-GYMB</t>
+  </si>
+  <si>
+    <t>R-10F</t>
+  </si>
+  <si>
+    <t>R-10FB-GYMB</t>
+  </si>
+  <si>
+    <t>R-10FB</t>
+  </si>
+  <si>
+    <t>BJW1170-BKSL240</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1347,9 +1398,6 @@
     <t>BJW1170BKSL 바오지 여성 러닝화 블랙실버 235</t>
   </si>
   <si>
-    <t>BJW1170-BKSL240</t>
-  </si>
-  <si>
     <t>BJW1170BKSL 바오지 여성 러닝화 블랙실버 240</t>
   </si>
   <si>
@@ -1578,18 +1626,6 @@
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 255</t>
   </si>
   <si>
-    <t>X-10H-GYGC</t>
-  </si>
-  <si>
-    <t>스포츠선글라스</t>
-  </si>
-  <si>
-    <t>X-10H</t>
-  </si>
-  <si>
-    <t>공용</t>
-  </si>
-  <si>
     <t>X-10H-GYGG</t>
   </si>
   <si>
@@ -1602,12 +1638,6 @@
     <t>X-20FS-GYGC</t>
   </si>
   <si>
-    <t>X-20FS</t>
-  </si>
-  <si>
-    <t>X-20FS-GYGG</t>
-  </si>
-  <si>
     <t>X-20FS-MAGC</t>
   </si>
   <si>
@@ -1617,12 +1647,6 @@
     <t>X-20FA-GYGC</t>
   </si>
   <si>
-    <t>X-20FA</t>
-  </si>
-  <si>
-    <t>X-20FA-GYGG</t>
-  </si>
-  <si>
     <t>X-20FA-MAGC</t>
   </si>
   <si>
@@ -1662,31 +1686,13 @@
     <t>S-20R-GYGC</t>
   </si>
   <si>
-    <t>S-20R</t>
-  </si>
-  <si>
     <t>S-20R-GYGG</t>
   </si>
   <si>
     <t>S-20R-MAGC</t>
   </si>
   <si>
-    <t>S-20R-MAGG</t>
-  </si>
-  <si>
-    <t>R-10F-GYMB</t>
-  </si>
-  <si>
-    <t>R-10F</t>
-  </si>
-  <si>
     <t>R-10F-BRMB</t>
-  </si>
-  <si>
-    <t>R-10FB-GYMB</t>
-  </si>
-  <si>
-    <t>R-10FB</t>
   </si>
   <si>
     <t>R-10FB-BRMB</t>
@@ -2075,7 +2081,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D07909F-939B-4C3C-9B95-5ACF819F6F5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165B3046-8A84-41F5-9577-790D1FE71C09}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:P259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2085,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2100,31 +2106,31 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="H1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="J1" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="K1" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="L1" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="M1" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="N1" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="O1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
@@ -2132,10 +2138,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
@@ -2162,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2185,7 +2191,7 @@
         <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -2212,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -2232,10 +2238,10 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
@@ -2262,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2282,10 +2288,10 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
@@ -2312,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2332,10 +2338,10 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -2362,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2382,10 +2388,10 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -2412,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2432,10 +2438,10 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
@@ -2462,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2482,10 +2488,10 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -2512,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2532,10 +2538,10 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
@@ -2562,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2582,10 +2588,10 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -2612,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2632,16 +2638,16 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
@@ -2662,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2682,16 +2688,16 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -2712,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2732,16 +2738,16 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -2762,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2782,16 +2788,16 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -2812,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2832,16 +2838,16 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -2862,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2882,16 +2888,16 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
@@ -2912,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2932,16 +2938,16 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
@@ -2962,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2982,16 +2988,16 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
         <v>31</v>
@@ -3012,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3032,16 +3038,16 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" t="s">
         <v>149</v>
       </c>
-      <c r="C20" t="s">
-        <v>132</v>
-      </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
         <v>31</v>
@@ -3062,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3082,16 +3088,16 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" t="s">
         <v>150</v>
-      </c>
-      <c r="B21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
@@ -3112,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3132,16 +3138,16 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
@@ -3162,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3182,16 +3188,16 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
@@ -3212,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3232,16 +3238,16 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
@@ -3262,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3282,16 +3288,16 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
@@ -3312,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3332,16 +3338,16 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
         <v>31</v>
@@ -3362,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3382,16 +3388,16 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
         <v>31</v>
@@ -3412,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3432,16 +3438,16 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
         <v>31</v>
@@ -3462,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3482,16 +3488,16 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
         <v>31</v>
@@ -3512,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3532,16 +3538,16 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
         <v>31</v>
@@ -3562,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3582,16 +3588,16 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E31" t="s">
         <v>31</v>
@@ -3612,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3632,16 +3638,16 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -3662,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3682,16 +3688,16 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B33" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E33" t="s">
         <v>31</v>
@@ -3712,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3732,16 +3738,16 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E34" t="s">
         <v>31</v>
@@ -3762,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3782,16 +3788,16 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D35" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E35" t="s">
         <v>31</v>
@@ -3812,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3832,16 +3838,16 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
@@ -3862,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3882,16 +3888,16 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E37" t="s">
         <v>31</v>
@@ -3912,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3932,16 +3938,16 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E38" t="s">
         <v>31</v>
@@ -3962,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3982,16 +3988,16 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E39" t="s">
         <v>31</v>
@@ -4012,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4032,16 +4038,16 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B40" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D40" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
         <v>31</v>
@@ -4062,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4082,16 +4088,16 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" t="s">
         <v>191</v>
-      </c>
-      <c r="B41" t="s">
-        <v>192</v>
-      </c>
-      <c r="C41" t="s">
-        <v>132</v>
-      </c>
-      <c r="D41" t="s">
-        <v>174</v>
       </c>
       <c r="E41" t="s">
         <v>31</v>
@@ -4112,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4132,16 +4138,16 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D42" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E42" t="s">
         <v>31</v>
@@ -4162,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4182,16 +4188,16 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D43" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
@@ -4212,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4232,16 +4238,16 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
@@ -4262,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4282,16 +4288,16 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C45" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E45" t="s">
         <v>31</v>
@@ -4312,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4332,16 +4338,16 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C46" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D46" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E46" t="s">
         <v>31</v>
@@ -4362,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4382,16 +4388,16 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
@@ -4412,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4432,16 +4438,16 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D48" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E48" t="s">
         <v>31</v>
@@ -4462,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4482,16 +4488,16 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D49" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E49" t="s">
         <v>31</v>
@@ -4512,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4532,16 +4538,16 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D50" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E50" t="s">
         <v>31</v>
@@ -4562,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4582,16 +4588,16 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B51" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D51" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E51" t="s">
         <v>31</v>
@@ -4612,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4632,16 +4638,16 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C52" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D52" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E52" t="s">
         <v>31</v>
@@ -4662,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4682,16 +4688,16 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D53" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E53" t="s">
         <v>31</v>
@@ -4712,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4732,16 +4738,16 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B54" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D54" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E54" t="s">
         <v>31</v>
@@ -4762,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -4782,16 +4788,16 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B55" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C55" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D55" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E55" t="s">
         <v>31</v>
@@ -4812,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -4832,16 +4838,16 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B56" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C56" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E56" t="s">
         <v>31</v>
@@ -4862,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -4882,16 +4888,16 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="B57" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C57" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D57" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E57" t="s">
         <v>31</v>
@@ -4912,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -4932,16 +4938,16 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="B58" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C58" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D58" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
@@ -4962,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -4982,16 +4988,16 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="B59" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="C59" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D59" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E59" t="s">
         <v>31</v>
@@ -5012,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5032,16 +5038,16 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B60" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C60" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D60" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E60" t="s">
         <v>31</v>
@@ -5062,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5082,16 +5088,16 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>249</v>
+      </c>
+      <c r="B61" t="s">
+        <v>250</v>
+      </c>
+      <c r="C61" t="s">
+        <v>149</v>
+      </c>
+      <c r="D61" t="s">
         <v>232</v>
-      </c>
-      <c r="B61" t="s">
-        <v>233</v>
-      </c>
-      <c r="C61" t="s">
-        <v>132</v>
-      </c>
-      <c r="D61" t="s">
-        <v>215</v>
       </c>
       <c r="E61" t="s">
         <v>31</v>
@@ -5112,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5132,16 +5138,16 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="B62" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C62" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D62" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E62" t="s">
         <v>31</v>
@@ -5162,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -5182,16 +5188,16 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C63" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E63" t="s">
         <v>31</v>
@@ -5212,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -5232,16 +5238,16 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D64" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E64" t="s">
         <v>31</v>
@@ -5262,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -5282,16 +5288,16 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="B65" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C65" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D65" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
@@ -5312,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5332,16 +5338,16 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B66" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C66" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D66" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E66" t="s">
         <v>31</v>
@@ -5362,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -5382,16 +5388,16 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="B67" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C67" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D67" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E67" t="s">
         <v>31</v>
@@ -5412,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -5432,16 +5438,16 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="B68" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C68" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D68" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E68" t="s">
         <v>31</v>
@@ -5462,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -5482,16 +5488,16 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B69" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="C69" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D69" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E69" t="s">
         <v>31</v>
@@ -5512,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -5532,16 +5538,16 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B70" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C70" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D70" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E70" t="s">
         <v>31</v>
@@ -5562,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -5582,16 +5588,16 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C71" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D71" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E71" t="s">
         <v>31</v>
@@ -5612,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -5632,10 +5638,10 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B72" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -5662,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -5685,7 +5691,7 @@
         <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -5712,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -5732,10 +5738,10 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="B74" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C74" t="s">
         <v>11</v>
@@ -5762,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -5782,10 +5788,10 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B75" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
@@ -5812,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -5832,10 +5838,10 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B76" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -5862,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -5882,10 +5888,10 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B77" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
@@ -5912,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -5932,10 +5938,10 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="B78" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
@@ -5962,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -5982,10 +5988,10 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="B79" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
@@ -6012,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -6035,7 +6041,7 @@
         <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
@@ -6062,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -6082,10 +6088,10 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="B81" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
@@ -6112,7 +6118,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -6132,10 +6138,10 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="B82" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -6162,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6182,10 +6188,10 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B83" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
@@ -6212,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -6232,10 +6238,10 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B84" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
@@ -6262,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -6282,10 +6288,10 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="B85" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
@@ -6312,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -6332,10 +6338,10 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B86" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
@@ -6362,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -6382,10 +6388,10 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="B87" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
@@ -6412,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -6435,7 +6441,7 @@
         <v>80</v>
       </c>
       <c r="B88" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
@@ -6462,7 +6468,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -6482,10 +6488,10 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B89" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
@@ -6512,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -6532,10 +6538,10 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="B90" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -6562,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -6582,10 +6588,10 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B91" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
@@ -6612,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -6632,10 +6638,10 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="B92" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -6662,7 +6668,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -6682,10 +6688,10 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="B93" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="C93" t="s">
         <v>11</v>
@@ -6712,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -6732,10 +6738,10 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B94" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
@@ -6762,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -6782,10 +6788,10 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B95" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="C95" t="s">
         <v>11</v>
@@ -6812,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -6832,10 +6838,10 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="B96" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="C96" t="s">
         <v>11</v>
@@ -6862,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6882,16 +6888,16 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="B97" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E97" t="s">
         <v>31</v>
@@ -6912,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6932,16 +6938,16 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="B98" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E98" t="s">
         <v>31</v>
@@ -6962,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -6982,16 +6988,16 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B99" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E99" t="s">
         <v>31</v>
@@ -7012,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -7032,16 +7038,16 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="B100" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
       </c>
       <c r="D100" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E100" t="s">
         <v>31</v>
@@ -7062,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -7082,16 +7088,16 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="B101" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="C101" t="s">
         <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E101" t="s">
         <v>31</v>
@@ -7112,7 +7118,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -7132,16 +7138,16 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B102" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="C102" t="s">
         <v>11</v>
       </c>
       <c r="D102" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E102" t="s">
         <v>31</v>
@@ -7162,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7182,16 +7188,16 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B103" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="C103" t="s">
         <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E103" t="s">
         <v>31</v>
@@ -7212,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -7232,16 +7238,16 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B104" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="C104" t="s">
         <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E104" t="s">
         <v>31</v>
@@ -7262,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -7282,16 +7288,16 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B105" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E105" t="s">
         <v>31</v>
@@ -7312,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -7332,16 +7338,16 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>339</v>
+      </c>
+      <c r="B106" t="s">
+        <v>340</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" t="s">
         <v>322</v>
-      </c>
-      <c r="B106" t="s">
-        <v>323</v>
-      </c>
-      <c r="C106" t="s">
-        <v>11</v>
-      </c>
-      <c r="D106" t="s">
-        <v>305</v>
       </c>
       <c r="E106" t="s">
         <v>31</v>
@@ -7362,7 +7368,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -7382,16 +7388,16 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B107" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="C107" t="s">
         <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E107" t="s">
         <v>31</v>
@@ -7412,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -7432,16 +7438,16 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B108" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="C108" t="s">
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E108" t="s">
         <v>31</v>
@@ -7462,7 +7468,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -7482,16 +7488,16 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B109" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="C109" t="s">
         <v>11</v>
       </c>
       <c r="D109" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E109" t="s">
         <v>31</v>
@@ -7512,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -7532,16 +7538,16 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B110" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="C110" t="s">
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E110" t="s">
         <v>31</v>
@@ -7562,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -7582,16 +7588,16 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B111" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="C111" t="s">
         <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E111" t="s">
         <v>31</v>
@@ -7612,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -7635,7 +7641,7 @@
         <v>82</v>
       </c>
       <c r="B112" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="C112" t="s">
         <v>11</v>
@@ -7662,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L112">
         <v>2</v>
@@ -7685,7 +7691,7 @@
         <v>65</v>
       </c>
       <c r="B113" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="C113" t="s">
         <v>11</v>
@@ -7712,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L113">
         <v>4</v>
@@ -7735,7 +7741,7 @@
         <v>83</v>
       </c>
       <c r="B114" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="C114" t="s">
         <v>11</v>
@@ -7762,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L114">
         <v>3</v>
@@ -7785,7 +7791,7 @@
         <v>48</v>
       </c>
       <c r="B115" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="C115" t="s">
         <v>11</v>
@@ -7812,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -7835,7 +7841,7 @@
         <v>72</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="C116" t="s">
         <v>11</v>
@@ -7862,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L116">
         <v>1</v>
@@ -7885,7 +7891,7 @@
         <v>70</v>
       </c>
       <c r="B117" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="C117" t="s">
         <v>11</v>
@@ -7912,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L117">
         <v>1</v>
@@ -7935,7 +7941,7 @@
         <v>97</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
@@ -7962,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -7982,10 +7988,10 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="C119" t="s">
         <v>11</v>
@@ -8012,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -8035,7 +8041,7 @@
         <v>47</v>
       </c>
       <c r="B120" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="C120" t="s">
         <v>11</v>
@@ -8062,7 +8068,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -8085,7 +8091,7 @@
         <v>66</v>
       </c>
       <c r="B121" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
@@ -8112,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -8135,7 +8141,7 @@
         <v>29</v>
       </c>
       <c r="B122" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="C122" t="s">
         <v>11</v>
@@ -8162,7 +8168,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L122">
         <v>3</v>
@@ -8185,7 +8191,7 @@
         <v>94</v>
       </c>
       <c r="B123" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="C123" t="s">
         <v>11</v>
@@ -8212,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -8235,7 +8241,7 @@
         <v>64</v>
       </c>
       <c r="B124" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
@@ -8262,7 +8268,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -8285,7 +8291,7 @@
         <v>51</v>
       </c>
       <c r="B125" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="C125" t="s">
         <v>11</v>
@@ -8312,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -8332,10 +8338,10 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B126" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="C126" t="s">
         <v>11</v>
@@ -8362,7 +8368,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L126">
         <v>0</v>
@@ -8385,7 +8391,7 @@
         <v>49</v>
       </c>
       <c r="B127" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="C127" t="s">
         <v>22</v>
@@ -8412,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L127">
         <v>5</v>
@@ -8435,7 +8441,7 @@
         <v>21</v>
       </c>
       <c r="B128" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C128" t="s">
         <v>22</v>
@@ -8462,7 +8468,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -8485,7 +8491,7 @@
         <v>35</v>
       </c>
       <c r="B129" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="C129" t="s">
         <v>22</v>
@@ -8512,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L129">
         <v>6</v>
@@ -8535,7 +8541,7 @@
         <v>46</v>
       </c>
       <c r="B130" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="C130" t="s">
         <v>22</v>
@@ -8562,7 +8568,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L130">
         <v>6</v>
@@ -8585,7 +8591,7 @@
         <v>41</v>
       </c>
       <c r="B131" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="C131" t="s">
         <v>22</v>
@@ -8612,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -8635,7 +8641,7 @@
         <v>52</v>
       </c>
       <c r="B132" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="C132" t="s">
         <v>22</v>
@@ -8662,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L132">
         <v>13</v>
@@ -8685,7 +8691,7 @@
         <v>43</v>
       </c>
       <c r="B133" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="C133" t="s">
         <v>22</v>
@@ -8712,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L133">
         <v>6</v>
@@ -8735,7 +8741,7 @@
         <v>69</v>
       </c>
       <c r="B134" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="C134" t="s">
         <v>22</v>
@@ -8762,7 +8768,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L134">
         <v>7</v>
@@ -8785,7 +8791,7 @@
         <v>39</v>
       </c>
       <c r="B135" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="C135" t="s">
         <v>22</v>
@@ -8812,7 +8818,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L135">
         <v>4</v>
@@ -8835,7 +8841,7 @@
         <v>53</v>
       </c>
       <c r="B136" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="C136" t="s">
         <v>22</v>
@@ -8862,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L136">
         <v>1</v>
@@ -8882,10 +8888,10 @@
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="B137" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="C137" t="s">
         <v>22</v>
@@ -8912,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -8932,10 +8938,10 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B138" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="C138" t="s">
         <v>22</v>
@@ -8962,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -8982,10 +8988,10 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B139" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="C139" t="s">
         <v>22</v>
@@ -9012,7 +9018,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L139">
         <v>0</v>
@@ -9035,7 +9041,7 @@
         <v>76</v>
       </c>
       <c r="B140" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="C140" t="s">
         <v>22</v>
@@ -9062,7 +9068,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L140">
         <v>1</v>
@@ -9082,10 +9088,10 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="B141" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="C141" t="s">
         <v>22</v>
@@ -9112,7 +9118,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L141">
         <v>0</v>
@@ -9135,7 +9141,7 @@
         <v>59</v>
       </c>
       <c r="B142" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="C142" t="s">
         <v>22</v>
@@ -9162,7 +9168,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -9182,10 +9188,10 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="B143" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="C143" t="s">
         <v>22</v>
@@ -9212,7 +9218,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -9232,10 +9238,10 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="B144" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="C144" t="s">
         <v>22</v>
@@ -9262,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -9282,10 +9288,10 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="B145" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="C145" t="s">
         <v>22</v>
@@ -9312,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -9332,10 +9338,10 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="B146" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="C146" t="s">
         <v>22</v>
@@ -9362,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -9382,10 +9388,10 @@
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="B147" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="C147" t="s">
         <v>22</v>
@@ -9412,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L147">
         <v>0</v>
@@ -9435,7 +9441,7 @@
         <v>89</v>
       </c>
       <c r="B148" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="C148" t="s">
         <v>22</v>
@@ -9462,7 +9468,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L148">
         <v>1</v>
@@ -9482,10 +9488,10 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B149" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C149" t="s">
         <v>22</v>
@@ -9512,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -9535,7 +9541,7 @@
         <v>77</v>
       </c>
       <c r="B150" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="C150" t="s">
         <v>22</v>
@@ -9562,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -9585,7 +9591,7 @@
         <v>93</v>
       </c>
       <c r="B151" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="C151" t="s">
         <v>22</v>
@@ -9612,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -9632,16 +9638,16 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="B152" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="C152" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D152" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E152" t="s">
         <v>15</v>
@@ -9662,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -9682,16 +9688,16 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="B153" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="C153" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D153" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E153" t="s">
         <v>15</v>
@@ -9712,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -9732,16 +9738,16 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="B154" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="C154" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D154" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E154" t="s">
         <v>15</v>
@@ -9762,7 +9768,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -9782,16 +9788,16 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="B155" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="C155" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D155" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E155" t="s">
         <v>15</v>
@@ -9812,7 +9818,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -9832,16 +9838,16 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="B156" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="C156" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D156" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E156" t="s">
         <v>15</v>
@@ -9862,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -9882,16 +9888,16 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="B157" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="C157" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D157" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E157" t="s">
         <v>15</v>
@@ -9912,7 +9918,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -9932,16 +9938,16 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="B158" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="C158" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D158" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E158" t="s">
         <v>15</v>
@@ -9962,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -9982,16 +9988,16 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="B159" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="C159" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D159" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E159" t="s">
         <v>15</v>
@@ -10012,7 +10018,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -10032,16 +10038,16 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="B160" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="C160" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D160" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E160" t="s">
         <v>15</v>
@@ -10062,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -10082,16 +10088,16 @@
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>422</v>
+      </c>
+      <c r="B161" t="s">
+        <v>423</v>
+      </c>
+      <c r="C161" t="s">
+        <v>149</v>
+      </c>
+      <c r="D161" t="s">
         <v>405</v>
-      </c>
-      <c r="B161" t="s">
-        <v>406</v>
-      </c>
-      <c r="C161" t="s">
-        <v>132</v>
-      </c>
-      <c r="D161" t="s">
-        <v>388</v>
       </c>
       <c r="E161" t="s">
         <v>15</v>
@@ -10112,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -10132,16 +10138,16 @@
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="B162" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="C162" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D162" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E162" t="s">
         <v>15</v>
@@ -10162,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -10182,16 +10188,16 @@
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="B163" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="C163" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D163" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E163" t="s">
         <v>15</v>
@@ -10212,7 +10218,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -10232,16 +10238,16 @@
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="B164" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="C164" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D164" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E164" t="s">
         <v>15</v>
@@ -10262,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -10282,16 +10288,16 @@
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="B165" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="C165" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D165" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E165" t="s">
         <v>15</v>
@@ -10312,7 +10318,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -10332,16 +10338,16 @@
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="B166" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="C166" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D166" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E166" t="s">
         <v>15</v>
@@ -10362,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -10382,16 +10388,16 @@
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="B167" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="C167" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D167" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E167" t="s">
         <v>15</v>
@@ -10412,7 +10418,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -10432,16 +10438,16 @@
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="B168" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="C168" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D168" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E168" t="s">
         <v>15</v>
@@ -10462,7 +10468,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -10482,16 +10488,16 @@
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="B169" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="C169" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D169" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E169" t="s">
         <v>15</v>
@@ -10512,7 +10518,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -10532,16 +10538,16 @@
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="B170" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="C170" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D170" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E170" t="s">
         <v>15</v>
@@ -10562,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -10582,16 +10588,16 @@
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="B171" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="C171" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D171" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E171" t="s">
         <v>15</v>
@@ -10612,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -10635,7 +10641,7 @@
         <v>78</v>
       </c>
       <c r="B172" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="C172" t="s">
         <v>11</v>
@@ -10662,7 +10668,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L172">
         <v>2</v>
@@ -10685,7 +10691,7 @@
         <v>86</v>
       </c>
       <c r="B173" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="C173" t="s">
         <v>11</v>
@@ -10712,7 +10718,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L173">
         <v>2</v>
@@ -10735,7 +10741,7 @@
         <v>90</v>
       </c>
       <c r="B174" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="C174" t="s">
         <v>11</v>
@@ -10762,7 +10768,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L174">
         <v>2</v>
@@ -10782,10 +10788,10 @@
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="B175" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="C175" t="s">
         <v>11</v>
@@ -10812,7 +10818,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L175">
         <v>0</v>
@@ -10835,7 +10841,7 @@
         <v>88</v>
       </c>
       <c r="B176" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C176" t="s">
         <v>11</v>
@@ -10862,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -10882,10 +10888,10 @@
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="B177" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="C177" t="s">
         <v>11</v>
@@ -10912,7 +10918,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L177">
         <v>0</v>
@@ -10932,10 +10938,10 @@
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>435</v>
+        <v>116</v>
       </c>
       <c r="B178" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="C178" t="s">
         <v>11</v>
@@ -10962,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L178">
         <v>0</v>
@@ -10982,10 +10988,10 @@
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="B179" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="C179" t="s">
         <v>11</v>
@@ -11012,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -11035,7 +11041,7 @@
         <v>87</v>
       </c>
       <c r="B180" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="C180" t="s">
         <v>11</v>
@@ -11062,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L180">
         <v>1</v>
@@ -11082,10 +11088,10 @@
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="B181" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="C181" t="s">
         <v>11</v>
@@ -11112,7 +11118,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -11135,7 +11141,7 @@
         <v>96</v>
       </c>
       <c r="B182" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="C182" t="s">
         <v>11</v>
@@ -11162,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L182">
         <v>1</v>
@@ -11182,10 +11188,10 @@
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="B183" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="C183" t="s">
         <v>11</v>
@@ -11212,7 +11218,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L183">
         <v>0</v>
@@ -11232,10 +11238,10 @@
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="B184" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="C184" t="s">
         <v>11</v>
@@ -11262,7 +11268,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L184">
         <v>0</v>
@@ -11285,7 +11291,7 @@
         <v>84</v>
       </c>
       <c r="B185" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="C185" t="s">
         <v>11</v>
@@ -11312,7 +11318,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L185">
         <v>1</v>
@@ -11332,10 +11338,10 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="B186" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="C186" t="s">
         <v>11</v>
@@ -11362,7 +11368,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L186">
         <v>0</v>
@@ -11385,7 +11391,7 @@
         <v>44</v>
       </c>
       <c r="B187" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="C187" t="s">
         <v>11</v>
@@ -11412,7 +11418,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L187">
         <v>5</v>
@@ -11435,7 +11441,7 @@
         <v>38</v>
       </c>
       <c r="B188" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="C188" t="s">
         <v>11</v>
@@ -11462,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L188">
         <v>7</v>
@@ -11485,7 +11491,7 @@
         <v>33</v>
       </c>
       <c r="B189" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="C189" t="s">
         <v>11</v>
@@ -11512,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L189">
         <v>6</v>
@@ -11535,7 +11541,7 @@
         <v>28</v>
       </c>
       <c r="B190" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="C190" t="s">
         <v>11</v>
@@ -11562,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L190">
         <v>7</v>
@@ -11582,10 +11588,10 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="B191" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="C191" t="s">
         <v>11</v>
@@ -11612,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -11635,7 +11641,7 @@
         <v>27</v>
       </c>
       <c r="B192" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="C192" t="s">
         <v>11</v>
@@ -11662,7 +11668,7 @@
         <v>5</v>
       </c>
       <c r="K192" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="L192">
         <v>10</v>
@@ -11685,7 +11691,7 @@
         <v>18</v>
       </c>
       <c r="B193" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="C193" t="s">
         <v>11</v>
@@ -11712,7 +11718,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L193">
         <v>19</v>
@@ -11735,7 +11741,7 @@
         <v>32</v>
       </c>
       <c r="B194" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="C194" t="s">
         <v>11</v>
@@ -11762,7 +11768,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L194">
         <v>14</v>
@@ -11785,7 +11791,7 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="C195" t="s">
         <v>11</v>
@@ -11812,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L195">
         <v>9</v>
@@ -11835,7 +11841,7 @@
         <v>10</v>
       </c>
       <c r="B196" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="C196" t="s">
         <v>11</v>
@@ -11862,7 +11868,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L196">
         <v>7</v>
@@ -11885,7 +11891,7 @@
         <v>58</v>
       </c>
       <c r="B197" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="C197" t="s">
         <v>11</v>
@@ -11912,7 +11918,7 @@
         <v>2</v>
       </c>
       <c r="K197" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="L197">
         <v>1</v>
@@ -11935,7 +11941,7 @@
         <v>34</v>
       </c>
       <c r="B198" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="C198" t="s">
         <v>11</v>
@@ -11962,7 +11968,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -11985,7 +11991,7 @@
         <v>20</v>
       </c>
       <c r="B199" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="C199" t="s">
         <v>11</v>
@@ -12012,7 +12018,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -12032,10 +12038,10 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="B200" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="C200" t="s">
         <v>11</v>
@@ -12062,7 +12068,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -12085,7 +12091,7 @@
         <v>50</v>
       </c>
       <c r="B201" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="C201" t="s">
         <v>11</v>
@@ -12112,7 +12118,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L201">
         <v>2</v>
@@ -12132,10 +12138,10 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="B202" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="C202" t="s">
         <v>11</v>
@@ -12162,7 +12168,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -12182,10 +12188,10 @@
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="B203" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="C203" t="s">
         <v>11</v>
@@ -12212,7 +12218,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L203">
         <v>0</v>
@@ -12232,10 +12238,10 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="B204" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="C204" t="s">
         <v>11</v>
@@ -12262,7 +12268,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -12285,7 +12291,7 @@
         <v>56</v>
       </c>
       <c r="B205" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="C205" t="s">
         <v>11</v>
@@ -12312,7 +12318,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -12332,10 +12338,10 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="B206" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="C206" t="s">
         <v>11</v>
@@ -12362,7 +12368,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -12382,10 +12388,10 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="B207" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="C207" t="s">
         <v>11</v>
@@ -12412,7 +12418,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -12432,10 +12438,10 @@
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="B208" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="C208" t="s">
         <v>11</v>
@@ -12462,7 +12468,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -12482,10 +12488,10 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="B209" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="C209" t="s">
         <v>11</v>
@@ -12512,7 +12518,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -12532,10 +12538,10 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="B210" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="C210" t="s">
         <v>11</v>
@@ -12562,7 +12568,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -12582,10 +12588,10 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="B211" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="C211" t="s">
         <v>11</v>
@@ -12612,7 +12618,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -12632,10 +12638,10 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="B212" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="C212" t="s">
         <v>11</v>
@@ -12662,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -12682,10 +12688,10 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="B213" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="C213" t="s">
         <v>11</v>
@@ -12712,7 +12718,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -12732,10 +12738,10 @@
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="B214" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="C214" t="s">
         <v>11</v>
@@ -12762,7 +12768,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L214">
         <v>0</v>
@@ -12785,7 +12791,7 @@
         <v>85</v>
       </c>
       <c r="B215" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="C215" t="s">
         <v>11</v>
@@ -12812,7 +12818,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -12832,10 +12838,10 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="B216" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="C216" t="s">
         <v>11</v>
@@ -12862,7 +12868,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -12885,7 +12891,7 @@
         <v>26</v>
       </c>
       <c r="B217" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="C217" t="s">
         <v>11</v>
@@ -12912,7 +12918,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L217">
         <v>4</v>
@@ -12935,7 +12941,7 @@
         <v>68</v>
       </c>
       <c r="B218" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="C218" t="s">
         <v>11</v>
@@ -12962,7 +12968,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L218">
         <v>3</v>
@@ -12985,7 +12991,7 @@
         <v>75</v>
       </c>
       <c r="B219" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="C219" t="s">
         <v>11</v>
@@ -13012,7 +13018,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L219">
         <v>1</v>
@@ -13035,7 +13041,7 @@
         <v>67</v>
       </c>
       <c r="B220" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="C220" t="s">
         <v>11</v>
@@ -13062,7 +13068,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L220">
         <v>1</v>
@@ -13082,10 +13088,10 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="B221" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="C221" t="s">
         <v>11</v>
@@ -13112,7 +13118,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -13135,7 +13141,7 @@
         <v>45</v>
       </c>
       <c r="B222" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="C222" t="s">
         <v>11</v>
@@ -13162,7 +13168,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -13185,7 +13191,7 @@
         <v>54</v>
       </c>
       <c r="B223" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="C223" t="s">
         <v>11</v>
@@ -13212,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L223">
         <v>8</v>
@@ -13235,7 +13241,7 @@
         <v>37</v>
       </c>
       <c r="B224" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="C224" t="s">
         <v>11</v>
@@ -13262,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L224">
         <v>6</v>
@@ -13285,7 +13291,7 @@
         <v>92</v>
       </c>
       <c r="B225" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="C225" t="s">
         <v>11</v>
@@ -13312,7 +13318,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L225">
         <v>6</v>
@@ -13335,7 +13341,7 @@
         <v>91</v>
       </c>
       <c r="B226" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="C226" t="s">
         <v>11</v>
@@ -13362,7 +13368,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L226">
         <v>1</v>
@@ -13385,7 +13391,7 @@
         <v>24</v>
       </c>
       <c r="B227" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="C227" t="s">
         <v>11</v>
@@ -13412,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L227">
         <v>5</v>
@@ -13435,7 +13441,7 @@
         <v>40</v>
       </c>
       <c r="B228" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="C228" t="s">
         <v>11</v>
@@ -13462,7 +13468,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L228">
         <v>9</v>
@@ -13485,7 +13491,7 @@
         <v>42</v>
       </c>
       <c r="B229" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="C229" t="s">
         <v>11</v>
@@ -13512,7 +13518,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L229">
         <v>5</v>
@@ -13535,7 +13541,7 @@
         <v>36</v>
       </c>
       <c r="B230" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="C230" t="s">
         <v>11</v>
@@ -13562,7 +13568,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L230">
         <v>4</v>
@@ -13582,10 +13588,10 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B231" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="C231" t="s">
         <v>11</v>
@@ -13612,7 +13618,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L231">
         <v>0</v>
@@ -13632,19 +13638,19 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>512</v>
+        <v>100</v>
       </c>
       <c r="B232" t="s">
-        <v>512</v>
+        <v>100</v>
       </c>
       <c r="C232" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D232" t="s">
-        <v>514</v>
+        <v>102</v>
       </c>
       <c r="E232" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G232">
         <v>99</v>
@@ -13659,7 +13665,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L232">
         <v>0</v>
@@ -13679,19 +13685,19 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B233" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C233" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D233" t="s">
-        <v>514</v>
+        <v>102</v>
       </c>
       <c r="E233" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G233">
         <v>99</v>
@@ -13706,7 +13712,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -13726,19 +13732,19 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B234" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C234" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D234" t="s">
-        <v>514</v>
+        <v>102</v>
       </c>
       <c r="E234" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G234">
         <v>99</v>
@@ -13753,7 +13759,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -13773,19 +13779,19 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B235" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C235" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D235" t="s">
-        <v>514</v>
+        <v>102</v>
       </c>
       <c r="E235" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G235">
         <v>99</v>
@@ -13800,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -13820,19 +13826,19 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B236" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C236" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D236" t="s">
-        <v>520</v>
+        <v>105</v>
       </c>
       <c r="E236" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G236">
         <v>99</v>
@@ -13847,7 +13853,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -13867,19 +13873,19 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>521</v>
+        <v>104</v>
       </c>
       <c r="B237" t="s">
-        <v>521</v>
+        <v>104</v>
       </c>
       <c r="C237" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D237" t="s">
-        <v>520</v>
+        <v>105</v>
       </c>
       <c r="E237" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G237">
         <v>99</v>
@@ -13894,7 +13900,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L237">
         <v>0</v>
@@ -13914,19 +13920,19 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="B238" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="C238" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D238" t="s">
-        <v>520</v>
+        <v>105</v>
       </c>
       <c r="E238" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G238">
         <v>99</v>
@@ -13941,7 +13947,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -13961,19 +13967,19 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="B239" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="C239" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D239" t="s">
-        <v>520</v>
+        <v>105</v>
       </c>
       <c r="E239" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G239">
         <v>99</v>
@@ -13988,7 +13994,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -14008,19 +14014,19 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="B240" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="C240" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D240" t="s">
-        <v>525</v>
+        <v>110</v>
       </c>
       <c r="E240" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G240">
         <v>99</v>
@@ -14035,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -14055,19 +14061,19 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>526</v>
+        <v>109</v>
       </c>
       <c r="B241" t="s">
-        <v>526</v>
+        <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D241" t="s">
-        <v>525</v>
+        <v>110</v>
       </c>
       <c r="E241" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G241">
         <v>99</v>
@@ -14082,7 +14088,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L241">
         <v>0</v>
@@ -14102,19 +14108,19 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B242" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C242" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D242" t="s">
-        <v>525</v>
+        <v>110</v>
       </c>
       <c r="E242" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G242">
         <v>99</v>
@@ -14129,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -14149,19 +14155,19 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B243" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C243" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D243" t="s">
-        <v>525</v>
+        <v>110</v>
       </c>
       <c r="E243" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G243">
         <v>99</v>
@@ -14176,7 +14182,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -14196,19 +14202,19 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B244" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C244" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D244" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="E244" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G244">
         <v>99</v>
@@ -14223,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -14243,19 +14249,19 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B245" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C245" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D245" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="E245" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G245">
         <v>99</v>
@@ -14270,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L245">
         <v>0</v>
@@ -14290,19 +14296,19 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B246" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C246" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D246" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="E246" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G246">
         <v>99</v>
@@ -14317,7 +14323,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L246">
         <v>0</v>
@@ -14337,19 +14343,19 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B247" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C247" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D247" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="E247" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G247">
         <v>99</v>
@@ -14364,7 +14370,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -14384,19 +14390,19 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B248" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C248" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D248" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E248" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G248">
         <v>99</v>
@@ -14411,7 +14417,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -14431,19 +14437,19 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B249" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C249" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D249" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E249" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G249">
         <v>99</v>
@@ -14458,7 +14464,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -14478,19 +14484,19 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B250" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C250" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D250" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E250" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G250">
         <v>99</v>
@@ -14505,7 +14511,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -14525,19 +14531,19 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B251" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C251" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D251" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E251" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G251">
         <v>99</v>
@@ -14552,7 +14558,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -14572,19 +14578,19 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B252" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C252" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D252" t="s">
-        <v>540</v>
+        <v>107</v>
       </c>
       <c r="E252" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G252">
         <v>99</v>
@@ -14599,7 +14605,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -14619,19 +14625,19 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B253" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="C253" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D253" t="s">
-        <v>540</v>
+        <v>107</v>
       </c>
       <c r="E253" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G253">
         <v>99</v>
@@ -14646,7 +14652,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L253">
         <v>0</v>
@@ -14666,19 +14672,19 @@
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B254" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C254" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D254" t="s">
-        <v>540</v>
+        <v>107</v>
       </c>
       <c r="E254" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G254">
         <v>99</v>
@@ -14693,7 +14699,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L254">
         <v>0</v>
@@ -14713,19 +14719,19 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>543</v>
+        <v>106</v>
       </c>
       <c r="B255" t="s">
-        <v>543</v>
+        <v>106</v>
       </c>
       <c r="C255" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D255" t="s">
-        <v>540</v>
+        <v>107</v>
       </c>
       <c r="E255" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G255">
         <v>99</v>
@@ -14740,7 +14746,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L255">
         <v>0</v>
@@ -14760,19 +14766,19 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>544</v>
+        <v>112</v>
       </c>
       <c r="B256" t="s">
-        <v>544</v>
+        <v>112</v>
       </c>
       <c r="C256" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D256" t="s">
-        <v>545</v>
+        <v>113</v>
       </c>
       <c r="E256" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G256">
         <v>99</v>
@@ -14787,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L256">
         <v>0</v>
@@ -14807,19 +14813,19 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B257" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C257" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D257" t="s">
-        <v>545</v>
+        <v>113</v>
       </c>
       <c r="E257" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G257">
         <v>99</v>
@@ -14834,7 +14840,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -14854,19 +14860,19 @@
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>547</v>
+        <v>114</v>
       </c>
       <c r="B258" t="s">
-        <v>547</v>
+        <v>114</v>
       </c>
       <c r="C258" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D258" t="s">
-        <v>548</v>
+        <v>115</v>
       </c>
       <c r="E258" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G258">
         <v>99</v>
@@ -14881,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L258">
         <v>0</v>
@@ -14901,19 +14907,19 @@
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B259" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C259" t="s">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="D259" t="s">
-        <v>548</v>
+        <v>115</v>
       </c>
       <c r="E259" t="s">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="G259">
         <v>99</v>
@@ -14928,7 +14934,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -14953,16 +14959,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FAFA0E-7673-4914-8991-806FCA5DE71A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B996D1D-2EA0-42D5-B8AF-279DCEC27F78}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J266"/>
+  <dimension ref="A1:J285"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -23473,6 +23473,614 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>46211</v>
+      </c>
+      <c r="B267" t="s">
+        <v>100</v>
+      </c>
+      <c r="C267" t="s">
+        <v>101</v>
+      </c>
+      <c r="D267" t="s">
+        <v>102</v>
+      </c>
+      <c r="E267" t="s">
+        <v>13</v>
+      </c>
+      <c r="F267" t="s">
+        <v>55</v>
+      </c>
+      <c r="G267">
+        <v>0</v>
+      </c>
+      <c r="H267" t="s">
+        <v>103</v>
+      </c>
+      <c r="I267">
+        <v>1</v>
+      </c>
+      <c r="J267" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>46211</v>
+      </c>
+      <c r="B268" t="s">
+        <v>104</v>
+      </c>
+      <c r="C268" t="s">
+        <v>101</v>
+      </c>
+      <c r="D268" t="s">
+        <v>105</v>
+      </c>
+      <c r="E268" t="s">
+        <v>13</v>
+      </c>
+      <c r="F268" t="s">
+        <v>55</v>
+      </c>
+      <c r="G268">
+        <v>0</v>
+      </c>
+      <c r="H268" t="s">
+        <v>103</v>
+      </c>
+      <c r="I268">
+        <v>1</v>
+      </c>
+      <c r="J268" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>46212</v>
+      </c>
+      <c r="B269" t="s">
+        <v>97</v>
+      </c>
+      <c r="C269" t="s">
+        <v>11</v>
+      </c>
+      <c r="D269" t="s">
+        <v>30</v>
+      </c>
+      <c r="E269" t="s">
+        <v>19</v>
+      </c>
+      <c r="F269" t="s">
+        <v>63</v>
+      </c>
+      <c r="G269">
+        <v>265</v>
+      </c>
+      <c r="H269" t="s">
+        <v>31</v>
+      </c>
+      <c r="I269">
+        <v>1</v>
+      </c>
+      <c r="J269" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>46212</v>
+      </c>
+      <c r="B270" t="s">
+        <v>95</v>
+      </c>
+      <c r="C270" t="s">
+        <v>11</v>
+      </c>
+      <c r="D270" t="s">
+        <v>62</v>
+      </c>
+      <c r="E270" t="s">
+        <v>98</v>
+      </c>
+      <c r="F270" t="s">
+        <v>63</v>
+      </c>
+      <c r="G270">
+        <v>265</v>
+      </c>
+      <c r="H270" t="s">
+        <v>31</v>
+      </c>
+      <c r="I270">
+        <v>1</v>
+      </c>
+      <c r="J270" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>46213</v>
+      </c>
+      <c r="B271" t="s">
+        <v>53</v>
+      </c>
+      <c r="C271" t="s">
+        <v>22</v>
+      </c>
+      <c r="D271" t="s">
+        <v>23</v>
+      </c>
+      <c r="E271" t="s">
+        <v>71</v>
+      </c>
+      <c r="F271" t="s">
+        <v>63</v>
+      </c>
+      <c r="G271">
+        <v>255</v>
+      </c>
+      <c r="H271" t="s">
+        <v>15</v>
+      </c>
+      <c r="I271">
+        <v>1</v>
+      </c>
+      <c r="J271" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>46213</v>
+      </c>
+      <c r="B272" t="s">
+        <v>84</v>
+      </c>
+      <c r="C272" t="s">
+        <v>11</v>
+      </c>
+      <c r="D272" t="s">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>71</v>
+      </c>
+      <c r="F272" t="s">
+        <v>63</v>
+      </c>
+      <c r="G272">
+        <v>250</v>
+      </c>
+      <c r="H272" t="s">
+        <v>15</v>
+      </c>
+      <c r="I272">
+        <v>1</v>
+      </c>
+      <c r="J272" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>46213</v>
+      </c>
+      <c r="B273" t="s">
+        <v>43</v>
+      </c>
+      <c r="C273" t="s">
+        <v>22</v>
+      </c>
+      <c r="D273" t="s">
+        <v>23</v>
+      </c>
+      <c r="E273" t="s">
+        <v>71</v>
+      </c>
+      <c r="F273" t="s">
+        <v>63</v>
+      </c>
+      <c r="G273">
+        <v>240</v>
+      </c>
+      <c r="H273" t="s">
+        <v>15</v>
+      </c>
+      <c r="I273">
+        <v>1</v>
+      </c>
+      <c r="J273" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>46213</v>
+      </c>
+      <c r="B274" t="s">
+        <v>106</v>
+      </c>
+      <c r="C274" t="s">
+        <v>101</v>
+      </c>
+      <c r="D274" t="s">
+        <v>107</v>
+      </c>
+      <c r="E274" t="s">
+        <v>108</v>
+      </c>
+      <c r="F274" t="s">
+        <v>63</v>
+      </c>
+      <c r="G274">
+        <v>0</v>
+      </c>
+      <c r="H274" t="s">
+        <v>103</v>
+      </c>
+      <c r="I274">
+        <v>1</v>
+      </c>
+      <c r="J274" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>46213</v>
+      </c>
+      <c r="B275" t="s">
+        <v>72</v>
+      </c>
+      <c r="C275" t="s">
+        <v>11</v>
+      </c>
+      <c r="D275" t="s">
+        <v>30</v>
+      </c>
+      <c r="E275" t="s">
+        <v>19</v>
+      </c>
+      <c r="F275" t="s">
+        <v>63</v>
+      </c>
+      <c r="G275">
+        <v>280</v>
+      </c>
+      <c r="H275" t="s">
+        <v>31</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+      <c r="J275" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>46216</v>
+      </c>
+      <c r="B276" t="s">
+        <v>109</v>
+      </c>
+      <c r="C276" t="s">
+        <v>101</v>
+      </c>
+      <c r="D276" t="s">
+        <v>110</v>
+      </c>
+      <c r="E276" t="s">
+        <v>13</v>
+      </c>
+      <c r="F276" t="s">
+        <v>111</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276" t="s">
+        <v>103</v>
+      </c>
+      <c r="I276">
+        <v>1</v>
+      </c>
+      <c r="J276" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>46216</v>
+      </c>
+      <c r="B277" t="s">
+        <v>112</v>
+      </c>
+      <c r="C277" t="s">
+        <v>101</v>
+      </c>
+      <c r="D277" t="s">
+        <v>113</v>
+      </c>
+      <c r="E277" t="s">
+        <v>108</v>
+      </c>
+      <c r="F277" t="s">
+        <v>63</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277" t="s">
+        <v>103</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+      <c r="J277" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>46216</v>
+      </c>
+      <c r="B278" t="s">
+        <v>112</v>
+      </c>
+      <c r="C278" t="s">
+        <v>101</v>
+      </c>
+      <c r="D278" t="s">
+        <v>113</v>
+      </c>
+      <c r="E278" t="s">
+        <v>108</v>
+      </c>
+      <c r="F278" t="s">
+        <v>63</v>
+      </c>
+      <c r="G278">
+        <v>0</v>
+      </c>
+      <c r="H278" t="s">
+        <v>103</v>
+      </c>
+      <c r="I278">
+        <v>1</v>
+      </c>
+      <c r="J278" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>46216</v>
+      </c>
+      <c r="B279" t="s">
+        <v>114</v>
+      </c>
+      <c r="C279" t="s">
+        <v>101</v>
+      </c>
+      <c r="D279" t="s">
+        <v>115</v>
+      </c>
+      <c r="E279" t="s">
+        <v>108</v>
+      </c>
+      <c r="F279" t="s">
+        <v>63</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279" t="s">
+        <v>103</v>
+      </c>
+      <c r="I279">
+        <v>1</v>
+      </c>
+      <c r="J279" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>46216</v>
+      </c>
+      <c r="B280" t="s">
+        <v>114</v>
+      </c>
+      <c r="C280" t="s">
+        <v>101</v>
+      </c>
+      <c r="D280" t="s">
+        <v>115</v>
+      </c>
+      <c r="E280" t="s">
+        <v>108</v>
+      </c>
+      <c r="F280" t="s">
+        <v>63</v>
+      </c>
+      <c r="G280">
+        <v>0</v>
+      </c>
+      <c r="H280" t="s">
+        <v>103</v>
+      </c>
+      <c r="I280">
+        <v>1</v>
+      </c>
+      <c r="J280" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>46216</v>
+      </c>
+      <c r="B281" t="s">
+        <v>100</v>
+      </c>
+      <c r="C281" t="s">
+        <v>101</v>
+      </c>
+      <c r="D281" t="s">
+        <v>102</v>
+      </c>
+      <c r="E281" t="s">
+        <v>108</v>
+      </c>
+      <c r="F281" t="s">
+        <v>63</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281" t="s">
+        <v>103</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+      <c r="J281" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>46216</v>
+      </c>
+      <c r="B282" t="s">
+        <v>89</v>
+      </c>
+      <c r="C282" t="s">
+        <v>22</v>
+      </c>
+      <c r="D282" t="s">
+        <v>60</v>
+      </c>
+      <c r="E282" t="s">
+        <v>19</v>
+      </c>
+      <c r="F282" t="s">
+        <v>63</v>
+      </c>
+      <c r="G282">
+        <v>240</v>
+      </c>
+      <c r="H282" t="s">
+        <v>15</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+      <c r="J282" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>46216</v>
+      </c>
+      <c r="B283" t="s">
+        <v>49</v>
+      </c>
+      <c r="C283" t="s">
+        <v>22</v>
+      </c>
+      <c r="D283" t="s">
+        <v>23</v>
+      </c>
+      <c r="E283" t="s">
+        <v>19</v>
+      </c>
+      <c r="F283" t="s">
+        <v>63</v>
+      </c>
+      <c r="G283">
+        <v>235</v>
+      </c>
+      <c r="H283" t="s">
+        <v>15</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>46216</v>
+      </c>
+      <c r="B284" t="s">
+        <v>32</v>
+      </c>
+      <c r="C284" t="s">
+        <v>11</v>
+      </c>
+      <c r="D284" t="s">
+        <v>12</v>
+      </c>
+      <c r="E284" t="s">
+        <v>71</v>
+      </c>
+      <c r="F284" t="s">
+        <v>63</v>
+      </c>
+      <c r="G284">
+        <v>245</v>
+      </c>
+      <c r="H284" t="s">
+        <v>15</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+      <c r="J284" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>46216</v>
+      </c>
+      <c r="B285" t="s">
+        <v>116</v>
+      </c>
+      <c r="C285" t="s">
+        <v>11</v>
+      </c>
+      <c r="D285" t="s">
+        <v>79</v>
+      </c>
+      <c r="E285" t="s">
+        <v>71</v>
+      </c>
+      <c r="F285" t="s">
+        <v>63</v>
+      </c>
+      <c r="G285">
+        <v>240</v>
+      </c>
+      <c r="H285" t="s">
+        <v>15</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+      <c r="J285" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37AE0EEB-BF92-48DD-8407-AD3D2BE02F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{379776C0-04BC-433D-B1A8-F1C01A90C8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10005" yWindow="1800" windowWidth="18645" windowHeight="11295" xr2:uid="{8431F63A-43AF-4E48-9552-806C0F9D2A65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{76871E0A-13E1-498A-A198-17995B89AB56}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -2081,8 +2081,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165B3046-8A84-41F5-9577-790D1FE71C09}">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04847DE6-AC47-4135-913F-6127F8693ABB}">
   <dimension ref="A1:P259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -14959,8 +14958,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B996D1D-2EA0-42D5-B8AF-279DCEC27F78}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E56F0E73-3DF0-4E40-A38F-E8109BE583BF}">
   <dimension ref="A1:J285"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{101215ED-D2AF-4A81-B261-EAAFA79C5D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45B94621-A986-4265-8163-7405DD45FF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00DC7884-9A32-4FA1-A74B-5595E9E653F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{55E39C05-5FB3-4FD9-9D4D-78FCF71D918C}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3967" uniqueCount="553">
   <si>
     <t>날짜</t>
   </si>
@@ -333,6 +333,36 @@
     <t>BJW1170-SLAP235</t>
   </si>
   <si>
+    <t>S-20R-MAGC</t>
+  </si>
+  <si>
+    <t>스포츠선글라스</t>
+  </si>
+  <si>
+    <t>S-20R</t>
+  </si>
+  <si>
+    <t>공용</t>
+  </si>
+  <si>
+    <t>S-10HA-GYGG</t>
+  </si>
+  <si>
+    <t>S-10HA</t>
+  </si>
+  <si>
+    <t>X-10H-GYGC</t>
+  </si>
+  <si>
+    <t>X-10H</t>
+  </si>
+  <si>
+    <t>X-20FS-GYGG</t>
+  </si>
+  <si>
+    <t>X-20FS</t>
+  </si>
+  <si>
     <t>DPM647-GY265</t>
   </si>
   <si>
@@ -345,18 +375,9 @@
     <t>S-20R-MAGG</t>
   </si>
   <si>
-    <t>스포츠선글라스</t>
-  </si>
-  <si>
-    <t>S-20R</t>
-  </si>
-  <si>
     <t>스토어팜</t>
   </si>
   <si>
-    <t>공용</t>
-  </si>
-  <si>
     <t>X-20FA-GYGG</t>
   </si>
   <si>
@@ -378,12 +399,6 @@
     <t>R-10FB</t>
   </si>
   <si>
-    <t>X-10H-GYGC</t>
-  </si>
-  <si>
-    <t>X-10H</t>
-  </si>
-  <si>
     <t>BJW1170-BKSL240</t>
   </si>
   <si>
@@ -1635,12 +1650,6 @@
     <t>X-20FS-GYGC</t>
   </si>
   <si>
-    <t>X-20FS</t>
-  </si>
-  <si>
-    <t>X-20FS-GYGG</t>
-  </si>
-  <si>
     <t>X-20FS-MAGC</t>
   </si>
   <si>
@@ -1659,12 +1668,6 @@
     <t>S-10HA-GYGC</t>
   </si>
   <si>
-    <t>S-10HA</t>
-  </si>
-  <si>
-    <t>S-10HA-GYGG</t>
-  </si>
-  <si>
     <t>S-10HA-MAGC</t>
   </si>
   <si>
@@ -1690,9 +1693,6 @@
   </si>
   <si>
     <t>S-20R-GYGG</t>
-  </si>
-  <si>
-    <t>S-20R-MAGC</t>
   </si>
   <si>
     <t>R-10F-BRMB</t>
@@ -2084,7 +2084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2AE562-523B-40F4-A1A4-73A09F2B592A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6822097-1E0D-42D7-ADD0-A1ADC97C699A}">
   <dimension ref="A1:P259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2093,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2108,31 +2108,31 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="M1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="N1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="O1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L2">
         <v>4</v>
@@ -2193,7 +2193,7 @@
         <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
@@ -2470,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2490,10 +2490,10 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2640,16 +2640,16 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2690,16 +2690,16 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2740,16 +2740,16 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" t="s">
         <v>161</v>
       </c>
-      <c r="C14" t="s">
-        <v>156</v>
-      </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2790,16 +2790,16 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" t="s">
         <v>162</v>
-      </c>
-      <c r="B15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D15" t="s">
-        <v>157</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2840,16 +2840,16 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2890,16 +2890,16 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
@@ -2920,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2940,16 +2940,16 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2990,16 +2990,16 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B19" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E19" t="s">
         <v>31</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3040,16 +3040,16 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E20" t="s">
         <v>31</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3090,16 +3090,16 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B21" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3140,16 +3140,16 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3190,16 +3190,16 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C23" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3240,16 +3240,16 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
@@ -3270,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3290,16 +3290,16 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3340,16 +3340,16 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E26" t="s">
         <v>31</v>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3390,16 +3390,16 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E27" t="s">
         <v>31</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3440,16 +3440,16 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B28" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E28" t="s">
         <v>31</v>
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3490,16 +3490,16 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B29" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D29" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E29" t="s">
         <v>31</v>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3540,16 +3540,16 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B30" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C30" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E30" t="s">
         <v>31</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3590,16 +3590,16 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C31" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
         <v>31</v>
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3640,16 +3640,16 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B32" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -3670,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3690,16 +3690,16 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B33" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E33" t="s">
         <v>31</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3740,16 +3740,16 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D34" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
         <v>31</v>
@@ -3770,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3790,16 +3790,16 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" t="s">
         <v>203</v>
-      </c>
-      <c r="B35" t="s">
-        <v>204</v>
-      </c>
-      <c r="C35" t="s">
-        <v>156</v>
-      </c>
-      <c r="D35" t="s">
-        <v>198</v>
       </c>
       <c r="E35" t="s">
         <v>31</v>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3840,16 +3840,16 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D36" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3890,16 +3890,16 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D37" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E37" t="s">
         <v>31</v>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3940,16 +3940,16 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C38" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D38" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E38" t="s">
         <v>31</v>
@@ -3970,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3990,16 +3990,16 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B39" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C39" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D39" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E39" t="s">
         <v>31</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4040,16 +4040,16 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D40" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E40" t="s">
         <v>31</v>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4090,16 +4090,16 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D41" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E41" t="s">
         <v>31</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4140,16 +4140,16 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B42" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C42" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D42" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E42" t="s">
         <v>31</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4190,16 +4190,16 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C43" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D43" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
@@ -4220,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4240,16 +4240,16 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4290,16 +4290,16 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B45" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C45" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E45" t="s">
         <v>31</v>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4340,16 +4340,16 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B46" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C46" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E46" t="s">
         <v>31</v>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4390,16 +4390,16 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C47" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D47" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4440,16 +4440,16 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D48" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E48" t="s">
         <v>31</v>
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4490,16 +4490,16 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B49" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D49" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E49" t="s">
         <v>31</v>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4540,16 +4540,16 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C50" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D50" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E50" t="s">
         <v>31</v>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4590,16 +4590,16 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C51" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D51" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E51" t="s">
         <v>31</v>
@@ -4620,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4640,16 +4640,16 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D52" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E52" t="s">
         <v>31</v>
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4690,16 +4690,16 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C53" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E53" t="s">
         <v>31</v>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4740,16 +4740,16 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C54" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D54" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E54" t="s">
         <v>31</v>
@@ -4770,7 +4770,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -4790,16 +4790,16 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>249</v>
+      </c>
+      <c r="B55" t="s">
+        <v>250</v>
+      </c>
+      <c r="C55" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55" t="s">
         <v>244</v>
-      </c>
-      <c r="B55" t="s">
-        <v>245</v>
-      </c>
-      <c r="C55" t="s">
-        <v>156</v>
-      </c>
-      <c r="D55" t="s">
-        <v>239</v>
       </c>
       <c r="E55" t="s">
         <v>31</v>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -4840,16 +4840,16 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B56" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C56" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D56" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E56" t="s">
         <v>31</v>
@@ -4870,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -4890,16 +4890,16 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B57" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C57" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D57" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E57" t="s">
         <v>31</v>
@@ -4920,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -4940,16 +4940,16 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B58" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C58" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D58" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
@@ -4970,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -4990,16 +4990,16 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B59" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E59" t="s">
         <v>31</v>
@@ -5020,7 +5020,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5040,16 +5040,16 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B60" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D60" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E60" t="s">
         <v>31</v>
@@ -5070,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5090,16 +5090,16 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B61" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C61" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D61" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E61" t="s">
         <v>31</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5140,16 +5140,16 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C62" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D62" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E62" t="s">
         <v>31</v>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -5190,16 +5190,16 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B63" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D63" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E63" t="s">
         <v>31</v>
@@ -5220,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -5240,16 +5240,16 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C64" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D64" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E64" t="s">
         <v>31</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -5290,16 +5290,16 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B65" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D65" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
@@ -5320,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5340,16 +5340,16 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B66" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C66" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D66" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E66" t="s">
         <v>31</v>
@@ -5370,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -5390,16 +5390,16 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B67" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C67" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E67" t="s">
         <v>31</v>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -5440,16 +5440,16 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B68" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C68" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D68" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E68" t="s">
         <v>31</v>
@@ -5470,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L68">
         <v>2</v>
@@ -5490,16 +5490,16 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B69" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C69" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D69" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E69" t="s">
         <v>31</v>
@@ -5520,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L69">
         <v>4</v>
@@ -5540,16 +5540,16 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B70" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C70" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D70" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E70" t="s">
         <v>31</v>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -5590,16 +5590,16 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>130</v>
+      </c>
+      <c r="B71" t="s">
+        <v>277</v>
+      </c>
+      <c r="C71" t="s">
+        <v>124</v>
+      </c>
+      <c r="D71" t="s">
         <v>125</v>
-      </c>
-      <c r="B71" t="s">
-        <v>272</v>
-      </c>
-      <c r="C71" t="s">
-        <v>119</v>
-      </c>
-      <c r="D71" t="s">
-        <v>120</v>
       </c>
       <c r="E71" t="s">
         <v>31</v>
@@ -5620,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B72" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -5670,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -5693,7 +5693,7 @@
         <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -5708,31 +5708,31 @@
         <v>265</v>
       </c>
       <c r="G73">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M73">
         <v>0</v>
       </c>
       <c r="N73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P73" t="s">
         <v>16</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B74" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C74" t="s">
         <v>11</v>
@@ -5770,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B75" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
@@ -5820,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -5840,10 +5840,10 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B76" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -5870,7 +5870,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -5890,10 +5890,10 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B77" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
@@ -5920,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -5940,10 +5940,10 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B78" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B79" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -6043,7 +6043,7 @@
         <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B81" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -6140,10 +6140,10 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B82" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -6170,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6190,10 +6190,10 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B83" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
@@ -6220,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B84" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
@@ -6270,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -6290,10 +6290,10 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B85" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
@@ -6320,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -6340,10 +6340,10 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B86" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
@@ -6370,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B87" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>80</v>
       </c>
       <c r="B88" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
@@ -6470,7 +6470,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -6490,10 +6490,10 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B89" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
@@ -6520,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B90" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -6570,7 +6570,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -6590,10 +6590,10 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B91" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
@@ -6620,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B92" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -6690,10 +6690,10 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B93" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C93" t="s">
         <v>11</v>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -6740,10 +6740,10 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B94" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
@@ -6770,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B95" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C95" t="s">
         <v>11</v>
@@ -6820,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -6840,10 +6840,10 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B96" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C96" t="s">
         <v>11</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6890,16 +6890,16 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B97" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E97" t="s">
         <v>31</v>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6940,16 +6940,16 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B98" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E98" t="s">
         <v>31</v>
@@ -6970,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -6990,16 +6990,16 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B99" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E99" t="s">
         <v>31</v>
@@ -7020,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -7040,16 +7040,16 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>332</v>
+      </c>
+      <c r="B100" t="s">
+        <v>333</v>
+      </c>
+      <c r="C100" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" t="s">
         <v>327</v>
-      </c>
-      <c r="B100" t="s">
-        <v>328</v>
-      </c>
-      <c r="C100" t="s">
-        <v>11</v>
-      </c>
-      <c r="D100" t="s">
-        <v>322</v>
       </c>
       <c r="E100" t="s">
         <v>31</v>
@@ -7070,7 +7070,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -7090,16 +7090,16 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C101" t="s">
         <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E101" t="s">
         <v>31</v>
@@ -7120,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -7140,16 +7140,16 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C102" t="s">
         <v>11</v>
       </c>
       <c r="D102" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E102" t="s">
         <v>31</v>
@@ -7170,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7190,16 +7190,16 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B103" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C103" t="s">
         <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E103" t="s">
         <v>31</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -7240,16 +7240,16 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B104" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C104" t="s">
         <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E104" t="s">
         <v>31</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -7290,16 +7290,16 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B105" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E105" t="s">
         <v>31</v>
@@ -7320,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -7340,16 +7340,16 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B106" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C106" t="s">
         <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E106" t="s">
         <v>31</v>
@@ -7370,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -7390,16 +7390,16 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B107" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C107" t="s">
         <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E107" t="s">
         <v>31</v>
@@ -7420,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -7440,16 +7440,16 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B108" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C108" t="s">
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E108" t="s">
         <v>31</v>
@@ -7470,7 +7470,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -7490,16 +7490,16 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B109" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C109" t="s">
         <v>11</v>
       </c>
       <c r="D109" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E109" t="s">
         <v>31</v>
@@ -7520,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -7540,16 +7540,16 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B110" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C110" t="s">
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E110" t="s">
         <v>31</v>
@@ -7570,7 +7570,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -7590,16 +7590,16 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B111" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C111" t="s">
         <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E111" t="s">
         <v>31</v>
@@ -7620,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>82</v>
       </c>
       <c r="B112" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C112" t="s">
         <v>11</v>
@@ -7670,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L112">
         <v>2</v>
@@ -7693,7 +7693,7 @@
         <v>65</v>
       </c>
       <c r="B113" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C113" t="s">
         <v>11</v>
@@ -7720,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L113">
         <v>4</v>
@@ -7743,7 +7743,7 @@
         <v>83</v>
       </c>
       <c r="B114" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C114" t="s">
         <v>11</v>
@@ -7770,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L114">
         <v>3</v>
@@ -7793,7 +7793,7 @@
         <v>48</v>
       </c>
       <c r="B115" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C115" t="s">
         <v>11</v>
@@ -7820,7 +7820,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -7843,7 +7843,7 @@
         <v>72</v>
       </c>
       <c r="B116" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C116" t="s">
         <v>11</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L116">
         <v>2</v>
@@ -7893,7 +7893,7 @@
         <v>70</v>
       </c>
       <c r="B117" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C117" t="s">
         <v>11</v>
@@ -7920,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L117">
         <v>1</v>
@@ -7940,10 +7940,10 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B118" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
@@ -7958,31 +7958,31 @@
         <v>265</v>
       </c>
       <c r="G118">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H118">
         <v>0</v>
       </c>
       <c r="I118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M118">
         <v>0</v>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P118" t="s">
         <v>16</v>
@@ -7990,10 +7990,10 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B119" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C119" t="s">
         <v>11</v>
@@ -8020,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -8043,7 +8043,7 @@
         <v>47</v>
       </c>
       <c r="B120" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C120" t="s">
         <v>11</v>
@@ -8070,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -8093,7 +8093,7 @@
         <v>66</v>
       </c>
       <c r="B121" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -8143,7 +8143,7 @@
         <v>29</v>
       </c>
       <c r="B122" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C122" t="s">
         <v>11</v>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L122">
         <v>3</v>
@@ -8193,7 +8193,7 @@
         <v>94</v>
       </c>
       <c r="B123" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C123" t="s">
         <v>11</v>
@@ -8220,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -8243,7 +8243,7 @@
         <v>64</v>
       </c>
       <c r="B124" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
@@ -8270,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -8293,7 +8293,7 @@
         <v>51</v>
       </c>
       <c r="B125" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C125" t="s">
         <v>11</v>
@@ -8320,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -8340,10 +8340,10 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B126" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C126" t="s">
         <v>11</v>
@@ -8370,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L126">
         <v>0</v>
@@ -8393,7 +8393,7 @@
         <v>49</v>
       </c>
       <c r="B127" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C127" t="s">
         <v>22</v>
@@ -8420,7 +8420,7 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L127">
         <v>6</v>
@@ -8443,7 +8443,7 @@
         <v>21</v>
       </c>
       <c r="B128" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C128" t="s">
         <v>22</v>
@@ -8470,7 +8470,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -8493,7 +8493,7 @@
         <v>35</v>
       </c>
       <c r="B129" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C129" t="s">
         <v>22</v>
@@ -8520,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L129">
         <v>6</v>
@@ -8543,7 +8543,7 @@
         <v>46</v>
       </c>
       <c r="B130" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C130" t="s">
         <v>22</v>
@@ -8570,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L130">
         <v>6</v>
@@ -8593,7 +8593,7 @@
         <v>41</v>
       </c>
       <c r="B131" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C131" t="s">
         <v>22</v>
@@ -8620,7 +8620,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -8643,7 +8643,7 @@
         <v>52</v>
       </c>
       <c r="B132" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C132" t="s">
         <v>22</v>
@@ -8670,7 +8670,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L132">
         <v>13</v>
@@ -8693,7 +8693,7 @@
         <v>43</v>
       </c>
       <c r="B133" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C133" t="s">
         <v>22</v>
@@ -8720,7 +8720,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L133">
         <v>7</v>
@@ -8743,7 +8743,7 @@
         <v>69</v>
       </c>
       <c r="B134" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C134" t="s">
         <v>22</v>
@@ -8770,7 +8770,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L134">
         <v>7</v>
@@ -8793,7 +8793,7 @@
         <v>39</v>
       </c>
       <c r="B135" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C135" t="s">
         <v>22</v>
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L135">
         <v>4</v>
@@ -8843,7 +8843,7 @@
         <v>53</v>
       </c>
       <c r="B136" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C136" t="s">
         <v>22</v>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L136">
         <v>3</v>
@@ -8893,7 +8893,7 @@
         <v>58</v>
       </c>
       <c r="B137" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C137" t="s">
         <v>22</v>
@@ -8920,7 +8920,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L137">
         <v>1</v>
@@ -8940,10 +8940,10 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B138" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C138" t="s">
         <v>22</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B139" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C139" t="s">
         <v>22</v>
@@ -9020,7 +9020,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L139">
         <v>0</v>
@@ -9043,7 +9043,7 @@
         <v>76</v>
       </c>
       <c r="B140" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C140" t="s">
         <v>22</v>
@@ -9070,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L140">
         <v>1</v>
@@ -9090,10 +9090,10 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B141" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C141" t="s">
         <v>22</v>
@@ -9120,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L141">
         <v>0</v>
@@ -9143,7 +9143,7 @@
         <v>60</v>
       </c>
       <c r="B142" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C142" t="s">
         <v>22</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -9190,10 +9190,10 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B143" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C143" t="s">
         <v>22</v>
@@ -9220,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -9240,10 +9240,10 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B144" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C144" t="s">
         <v>22</v>
@@ -9270,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -9290,10 +9290,10 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B145" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C145" t="s">
         <v>22</v>
@@ -9320,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -9340,10 +9340,10 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B146" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C146" t="s">
         <v>22</v>
@@ -9370,7 +9370,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -9390,10 +9390,10 @@
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B147" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C147" t="s">
         <v>22</v>
@@ -9420,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L147">
         <v>0</v>
@@ -9443,7 +9443,7 @@
         <v>89</v>
       </c>
       <c r="B148" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C148" t="s">
         <v>22</v>
@@ -9470,7 +9470,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L148">
         <v>2</v>
@@ -9490,10 +9490,10 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B149" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C149" t="s">
         <v>22</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -9543,7 +9543,7 @@
         <v>77</v>
       </c>
       <c r="B150" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C150" t="s">
         <v>22</v>
@@ -9570,7 +9570,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -9593,7 +9593,7 @@
         <v>93</v>
       </c>
       <c r="B151" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C151" t="s">
         <v>22</v>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -9640,16 +9640,16 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B152" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C152" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D152" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E152" t="s">
         <v>15</v>
@@ -9670,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -9690,16 +9690,16 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B153" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D153" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E153" t="s">
         <v>15</v>
@@ -9720,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -9740,16 +9740,16 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B154" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C154" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D154" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E154" t="s">
         <v>15</v>
@@ -9770,7 +9770,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -9790,16 +9790,16 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>414</v>
+      </c>
+      <c r="B155" t="s">
+        <v>415</v>
+      </c>
+      <c r="C155" t="s">
+        <v>161</v>
+      </c>
+      <c r="D155" t="s">
         <v>409</v>
-      </c>
-      <c r="B155" t="s">
-        <v>410</v>
-      </c>
-      <c r="C155" t="s">
-        <v>156</v>
-      </c>
-      <c r="D155" t="s">
-        <v>404</v>
       </c>
       <c r="E155" t="s">
         <v>15</v>
@@ -9820,7 +9820,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -9840,16 +9840,16 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B156" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C156" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D156" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E156" t="s">
         <v>15</v>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -9890,16 +9890,16 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B157" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C157" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E157" t="s">
         <v>15</v>
@@ -9920,7 +9920,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -9940,16 +9940,16 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B158" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C158" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E158" t="s">
         <v>15</v>
@@ -9970,7 +9970,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -9990,16 +9990,16 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B159" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C159" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E159" t="s">
         <v>15</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -10040,16 +10040,16 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B160" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C160" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E160" t="s">
         <v>15</v>
@@ -10070,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -10090,16 +10090,16 @@
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B161" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C161" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D161" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E161" t="s">
         <v>15</v>
@@ -10120,7 +10120,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -10140,16 +10140,16 @@
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C162" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E162" t="s">
         <v>15</v>
@@ -10170,7 +10170,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -10190,16 +10190,16 @@
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B163" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C163" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D163" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E163" t="s">
         <v>15</v>
@@ -10220,7 +10220,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -10240,16 +10240,16 @@
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B164" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C164" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E164" t="s">
         <v>15</v>
@@ -10270,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -10290,16 +10290,16 @@
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B165" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C165" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D165" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E165" t="s">
         <v>15</v>
@@ -10320,7 +10320,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -10340,16 +10340,16 @@
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B166" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C166" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D166" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E166" t="s">
         <v>15</v>
@@ -10370,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -10390,16 +10390,16 @@
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B167" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C167" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D167" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E167" t="s">
         <v>15</v>
@@ -10420,7 +10420,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -10440,16 +10440,16 @@
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B168" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C168" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D168" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E168" t="s">
         <v>15</v>
@@ -10470,7 +10470,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -10490,16 +10490,16 @@
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B169" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C169" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D169" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E169" t="s">
         <v>15</v>
@@ -10520,7 +10520,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -10540,16 +10540,16 @@
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B170" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C170" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D170" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E170" t="s">
         <v>15</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -10590,16 +10590,16 @@
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B171" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C171" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D171" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E171" t="s">
         <v>15</v>
@@ -10620,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -10643,7 +10643,7 @@
         <v>78</v>
       </c>
       <c r="B172" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C172" t="s">
         <v>11</v>
@@ -10670,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L172">
         <v>2</v>
@@ -10693,7 +10693,7 @@
         <v>86</v>
       </c>
       <c r="B173" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C173" t="s">
         <v>11</v>
@@ -10720,7 +10720,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L173">
         <v>2</v>
@@ -10743,7 +10743,7 @@
         <v>90</v>
       </c>
       <c r="B174" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C174" t="s">
         <v>11</v>
@@ -10770,7 +10770,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L174">
         <v>2</v>
@@ -10790,10 +10790,10 @@
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B175" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C175" t="s">
         <v>11</v>
@@ -10820,7 +10820,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L175">
         <v>0</v>
@@ -10843,7 +10843,7 @@
         <v>88</v>
       </c>
       <c r="B176" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C176" t="s">
         <v>11</v>
@@ -10870,7 +10870,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -10890,10 +10890,10 @@
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B177" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C177" t="s">
         <v>11</v>
@@ -10920,7 +10920,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L177">
         <v>0</v>
@@ -10940,10 +10940,10 @@
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B178" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C178" t="s">
         <v>11</v>
@@ -10970,7 +10970,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L178">
         <v>1</v>
@@ -10990,10 +10990,10 @@
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B179" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C179" t="s">
         <v>11</v>
@@ -11020,7 +11020,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -11043,7 +11043,7 @@
         <v>87</v>
       </c>
       <c r="B180" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C180" t="s">
         <v>11</v>
@@ -11070,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L180">
         <v>1</v>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B181" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C181" t="s">
         <v>11</v>
@@ -11120,7 +11120,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -11143,7 +11143,7 @@
         <v>96</v>
       </c>
       <c r="B182" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C182" t="s">
         <v>11</v>
@@ -11170,7 +11170,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L182">
         <v>1</v>
@@ -11190,10 +11190,10 @@
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B183" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C183" t="s">
         <v>11</v>
@@ -11220,7 +11220,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L183">
         <v>1</v>
@@ -11240,10 +11240,10 @@
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B184" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C184" t="s">
         <v>11</v>
@@ -11270,7 +11270,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L184">
         <v>0</v>
@@ -11293,7 +11293,7 @@
         <v>84</v>
       </c>
       <c r="B185" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C185" t="s">
         <v>11</v>
@@ -11320,7 +11320,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L185">
         <v>2</v>
@@ -11340,10 +11340,10 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B186" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C186" t="s">
         <v>11</v>
@@ -11370,7 +11370,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L186">
         <v>0</v>
@@ -11393,7 +11393,7 @@
         <v>44</v>
       </c>
       <c r="B187" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C187" t="s">
         <v>11</v>
@@ -11420,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L187">
         <v>5</v>
@@ -11443,7 +11443,7 @@
         <v>38</v>
       </c>
       <c r="B188" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C188" t="s">
         <v>11</v>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L188">
         <v>7</v>
@@ -11493,7 +11493,7 @@
         <v>33</v>
       </c>
       <c r="B189" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C189" t="s">
         <v>11</v>
@@ -11520,7 +11520,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L189">
         <v>6</v>
@@ -11543,7 +11543,7 @@
         <v>28</v>
       </c>
       <c r="B190" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C190" t="s">
         <v>11</v>
@@ -11570,7 +11570,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L190">
         <v>7</v>
@@ -11590,10 +11590,10 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B191" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C191" t="s">
         <v>11</v>
@@ -11620,7 +11620,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -11643,7 +11643,7 @@
         <v>27</v>
       </c>
       <c r="B192" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C192" t="s">
         <v>11</v>
@@ -11670,7 +11670,7 @@
         <v>5</v>
       </c>
       <c r="K192" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L192">
         <v>10</v>
@@ -11693,7 +11693,7 @@
         <v>18</v>
       </c>
       <c r="B193" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C193" t="s">
         <v>11</v>
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L193">
         <v>20</v>
@@ -11743,7 +11743,7 @@
         <v>32</v>
       </c>
       <c r="B194" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C194" t="s">
         <v>11</v>
@@ -11770,7 +11770,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L194">
         <v>16</v>
@@ -11793,7 +11793,7 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C195" t="s">
         <v>11</v>
@@ -11820,7 +11820,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L195">
         <v>9</v>
@@ -11843,7 +11843,7 @@
         <v>10</v>
       </c>
       <c r="B196" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C196" t="s">
         <v>11</v>
@@ -11870,7 +11870,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L196">
         <v>7</v>
@@ -11890,10 +11890,10 @@
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B197" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C197" t="s">
         <v>11</v>
@@ -11920,7 +11920,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -11943,7 +11943,7 @@
         <v>34</v>
       </c>
       <c r="B198" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C198" t="s">
         <v>11</v>
@@ -11970,7 +11970,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -11993,7 +11993,7 @@
         <v>20</v>
       </c>
       <c r="B199" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C199" t="s">
         <v>11</v>
@@ -12020,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -12040,10 +12040,10 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B200" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C200" t="s">
         <v>11</v>
@@ -12070,7 +12070,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -12093,7 +12093,7 @@
         <v>50</v>
       </c>
       <c r="B201" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C201" t="s">
         <v>11</v>
@@ -12120,7 +12120,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L201">
         <v>2</v>
@@ -12140,10 +12140,10 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B202" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C202" t="s">
         <v>11</v>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -12190,10 +12190,10 @@
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B203" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C203" t="s">
         <v>11</v>
@@ -12220,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L203">
         <v>0</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B204" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C204" t="s">
         <v>11</v>
@@ -12270,7 +12270,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -12293,7 +12293,7 @@
         <v>56</v>
       </c>
       <c r="B205" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C205" t="s">
         <v>11</v>
@@ -12320,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -12340,10 +12340,10 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B206" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C206" t="s">
         <v>11</v>
@@ -12370,7 +12370,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -12390,10 +12390,10 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B207" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C207" t="s">
         <v>11</v>
@@ -12420,7 +12420,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -12440,10 +12440,10 @@
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B208" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C208" t="s">
         <v>11</v>
@@ -12470,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -12490,10 +12490,10 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B209" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C209" t="s">
         <v>11</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -12540,10 +12540,10 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B210" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C210" t="s">
         <v>11</v>
@@ -12570,7 +12570,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -12590,10 +12590,10 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B211" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C211" t="s">
         <v>11</v>
@@ -12620,7 +12620,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -12640,10 +12640,10 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B212" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C212" t="s">
         <v>11</v>
@@ -12670,7 +12670,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -12690,10 +12690,10 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B213" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C213" t="s">
         <v>11</v>
@@ -12720,7 +12720,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -12740,10 +12740,10 @@
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B214" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C214" t="s">
         <v>11</v>
@@ -12770,7 +12770,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L214">
         <v>0</v>
@@ -12793,7 +12793,7 @@
         <v>85</v>
       </c>
       <c r="B215" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C215" t="s">
         <v>11</v>
@@ -12820,7 +12820,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -12840,10 +12840,10 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B216" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C216" t="s">
         <v>11</v>
@@ -12870,7 +12870,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -12893,7 +12893,7 @@
         <v>26</v>
       </c>
       <c r="B217" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C217" t="s">
         <v>11</v>
@@ -12920,7 +12920,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L217">
         <v>4</v>
@@ -12943,7 +12943,7 @@
         <v>68</v>
       </c>
       <c r="B218" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C218" t="s">
         <v>11</v>
@@ -12970,7 +12970,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L218">
         <v>3</v>
@@ -12993,7 +12993,7 @@
         <v>75</v>
       </c>
       <c r="B219" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C219" t="s">
         <v>11</v>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L219">
         <v>1</v>
@@ -13043,7 +13043,7 @@
         <v>67</v>
       </c>
       <c r="B220" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C220" t="s">
         <v>11</v>
@@ -13070,7 +13070,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L220">
         <v>1</v>
@@ -13090,10 +13090,10 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B221" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C221" t="s">
         <v>11</v>
@@ -13120,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -13143,7 +13143,7 @@
         <v>45</v>
       </c>
       <c r="B222" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C222" t="s">
         <v>11</v>
@@ -13170,7 +13170,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -13193,7 +13193,7 @@
         <v>54</v>
       </c>
       <c r="B223" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C223" t="s">
         <v>11</v>
@@ -13220,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L223">
         <v>9</v>
@@ -13243,7 +13243,7 @@
         <v>37</v>
       </c>
       <c r="B224" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C224" t="s">
         <v>11</v>
@@ -13270,7 +13270,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L224">
         <v>6</v>
@@ -13293,7 +13293,7 @@
         <v>92</v>
       </c>
       <c r="B225" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C225" t="s">
         <v>11</v>
@@ -13320,7 +13320,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L225">
         <v>6</v>
@@ -13343,7 +13343,7 @@
         <v>91</v>
       </c>
       <c r="B226" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C226" t="s">
         <v>11</v>
@@ -13370,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L226">
         <v>2</v>
@@ -13393,7 +13393,7 @@
         <v>24</v>
       </c>
       <c r="B227" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C227" t="s">
         <v>11</v>
@@ -13420,7 +13420,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L227">
         <v>5</v>
@@ -13443,7 +13443,7 @@
         <v>40</v>
       </c>
       <c r="B228" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C228" t="s">
         <v>11</v>
@@ -13470,7 +13470,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L228">
         <v>9</v>
@@ -13493,7 +13493,7 @@
         <v>42</v>
       </c>
       <c r="B229" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C229" t="s">
         <v>11</v>
@@ -13520,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L229">
         <v>5</v>
@@ -13543,7 +13543,7 @@
         <v>36</v>
       </c>
       <c r="B230" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C230" t="s">
         <v>11</v>
@@ -13570,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L230">
         <v>4</v>
@@ -13590,10 +13590,10 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B231" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C231" t="s">
         <v>11</v>
@@ -13620,7 +13620,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L231">
         <v>0</v>
@@ -13640,22 +13640,22 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B232" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C232" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D232" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E232" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G232">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -13667,19 +13667,19 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M232">
         <v>0</v>
       </c>
       <c r="N232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P232" t="s">
         <v>13</v>
@@ -13687,19 +13687,19 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B233" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C233" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D233" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E233" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G233">
         <v>99</v>
@@ -13714,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -13734,19 +13734,19 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B234" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C234" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D234" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E234" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G234">
         <v>99</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -13781,19 +13781,19 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B235" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C235" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D235" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E235" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G235">
         <v>99</v>
@@ -13808,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -13828,19 +13828,19 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B236" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C236" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D236" t="s">
-        <v>531</v>
+        <v>106</v>
       </c>
       <c r="E236" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G236">
         <v>99</v>
@@ -13855,7 +13855,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -13875,22 +13875,22 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>532</v>
+        <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>532</v>
+        <v>105</v>
       </c>
       <c r="C237" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D237" t="s">
-        <v>531</v>
+        <v>106</v>
       </c>
       <c r="E237" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G237">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -13902,19 +13902,19 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M237">
         <v>0</v>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P237" t="s">
         <v>13</v>
@@ -13922,19 +13922,19 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B238" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C238" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D238" t="s">
-        <v>531</v>
+        <v>106</v>
       </c>
       <c r="E238" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G238">
         <v>99</v>
@@ -13949,7 +13949,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -13969,19 +13969,19 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B239" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C239" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D239" t="s">
-        <v>531</v>
+        <v>106</v>
       </c>
       <c r="E239" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G239">
         <v>99</v>
@@ -13996,7 +13996,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -14016,19 +14016,19 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B240" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C240" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D240" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E240" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G240">
         <v>99</v>
@@ -14043,7 +14043,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -14063,19 +14063,19 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B241" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C241" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D241" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E241" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G241">
         <v>98</v>
@@ -14090,7 +14090,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -14110,19 +14110,19 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B242" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C242" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D242" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E242" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G242">
         <v>99</v>
@@ -14137,7 +14137,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -14157,19 +14157,19 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B243" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C243" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D243" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E243" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G243">
         <v>99</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -14204,19 +14204,19 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B244" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C244" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D244" t="s">
-        <v>539</v>
+        <v>102</v>
       </c>
       <c r="E244" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G244">
         <v>99</v>
@@ -14231,7 +14231,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -14251,22 +14251,22 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>540</v>
+        <v>101</v>
       </c>
       <c r="B245" t="s">
-        <v>540</v>
+        <v>101</v>
       </c>
       <c r="C245" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D245" t="s">
-        <v>539</v>
+        <v>102</v>
       </c>
       <c r="E245" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G245">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -14278,19 +14278,19 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M245">
         <v>0</v>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P245" t="s">
         <v>13</v>
@@ -14298,19 +14298,19 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B246" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C246" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D246" t="s">
-        <v>539</v>
+        <v>102</v>
       </c>
       <c r="E246" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G246">
         <v>99</v>
@@ -14325,7 +14325,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L246">
         <v>0</v>
@@ -14345,19 +14345,19 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B247" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C247" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D247" t="s">
-        <v>539</v>
+        <v>102</v>
       </c>
       <c r="E247" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G247">
         <v>99</v>
@@ -14372,7 +14372,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -14392,19 +14392,19 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B248" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C248" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D248" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E248" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G248">
         <v>99</v>
@@ -14419,7 +14419,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -14439,19 +14439,19 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
+        <v>546</v>
+      </c>
+      <c r="B249" t="s">
+        <v>546</v>
+      </c>
+      <c r="C249" t="s">
+        <v>98</v>
+      </c>
+      <c r="D249" t="s">
         <v>545</v>
       </c>
-      <c r="B249" t="s">
-        <v>545</v>
-      </c>
-      <c r="C249" t="s">
-        <v>101</v>
-      </c>
-      <c r="D249" t="s">
-        <v>544</v>
-      </c>
       <c r="E249" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G249">
         <v>99</v>
@@ -14466,7 +14466,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -14486,19 +14486,19 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B250" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C250" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D250" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E250" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G250">
         <v>99</v>
@@ -14513,7 +14513,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -14533,19 +14533,19 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B251" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C251" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D251" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E251" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G251">
         <v>99</v>
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -14580,19 +14580,19 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B252" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C252" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D252" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E252" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G252">
         <v>99</v>
@@ -14607,7 +14607,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -14627,19 +14627,19 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B253" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C253" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D253" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E253" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G253">
         <v>99</v>
@@ -14654,7 +14654,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L253">
         <v>0</v>
@@ -14674,22 +14674,22 @@
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>550</v>
+        <v>97</v>
       </c>
       <c r="B254" t="s">
-        <v>550</v>
+        <v>97</v>
       </c>
       <c r="C254" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D254" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E254" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G254">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H254">
         <v>0</v>
@@ -14701,19 +14701,19 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M254">
         <v>0</v>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P254" t="s">
         <v>13</v>
@@ -14721,19 +14721,19 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
+        <v>110</v>
+      </c>
+      <c r="B255" t="s">
+        <v>110</v>
+      </c>
+      <c r="C255" t="s">
+        <v>98</v>
+      </c>
+      <c r="D255" t="s">
+        <v>99</v>
+      </c>
+      <c r="E255" t="s">
         <v>100</v>
-      </c>
-      <c r="B255" t="s">
-        <v>100</v>
-      </c>
-      <c r="C255" t="s">
-        <v>101</v>
-      </c>
-      <c r="D255" t="s">
-        <v>102</v>
-      </c>
-      <c r="E255" t="s">
-        <v>104</v>
       </c>
       <c r="G255">
         <v>98</v>
@@ -14748,7 +14748,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -14768,19 +14768,19 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C256" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D256" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E256" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G256">
         <v>97</v>
@@ -14795,7 +14795,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L256">
         <v>2</v>
@@ -14821,13 +14821,13 @@
         <v>551</v>
       </c>
       <c r="C257" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D257" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E257" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G257">
         <v>99</v>
@@ -14842,7 +14842,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -14862,19 +14862,19 @@
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B258" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C258" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D258" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E258" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G258">
         <v>97</v>
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L258">
         <v>2</v>
@@ -14915,13 +14915,13 @@
         <v>552</v>
       </c>
       <c r="C259" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D259" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E259" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G259">
         <v>99</v>
@@ -14936,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -14961,8 +14961,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECD84E0-5356-4299-A1C4-92729A7533BA}">
-  <dimension ref="A1:J304"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1021BE5F-9563-4FBB-87EE-156936FDA236}">
+  <dimension ref="A1:J306"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -23415,156 +23415,156 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B265" t="s">
         <v>97</v>
       </c>
       <c r="C265" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="D265" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="E265" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F265" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G265">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H265" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="I265">
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B266" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C266" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="D266" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="E266" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="F266" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="G266">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H266" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="I266">
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B267" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C267" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="D267" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="E267" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F267" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G267">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H267" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="I267">
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B268" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C268" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="D268" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="E268" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="F268" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="G268">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H268" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="I268">
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B269" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="C269" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D269" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E269" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="F269" t="s">
         <v>63</v>
       </c>
       <c r="G269">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="H269" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I269">
         <v>1</v>
@@ -23575,28 +23575,28 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B270" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C270" t="s">
         <v>11</v>
       </c>
       <c r="D270" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E270" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="F270" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="G270">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="H270" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I270">
         <v>1</v>
@@ -23610,7 +23610,7 @@
         <v>46213</v>
       </c>
       <c r="B271" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C271" t="s">
         <v>22</v>
@@ -23625,7 +23625,7 @@
         <v>63</v>
       </c>
       <c r="G271">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="H271" t="s">
         <v>15</v>
@@ -23642,31 +23642,31 @@
         <v>46213</v>
       </c>
       <c r="B272" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C272" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="D272" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E272" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="F272" t="s">
         <v>63</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H272" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="I272">
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
@@ -23674,25 +23674,25 @@
         <v>46213</v>
       </c>
       <c r="B273" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C273" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D273" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E273" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="F273" t="s">
         <v>63</v>
       </c>
       <c r="G273">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="H273" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I273">
         <v>1</v>
@@ -23703,28 +23703,28 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B274" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C274" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D274" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E274" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="F274" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="G274">
         <v>0</v>
       </c>
       <c r="H274" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I274">
         <v>1</v>
@@ -23735,34 +23735,34 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B275" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="C275" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="D275" t="s">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="E275" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="F275" t="s">
         <v>63</v>
       </c>
       <c r="G275">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="H275" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="I275">
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
@@ -23770,25 +23770,25 @@
         <v>46216</v>
       </c>
       <c r="B276" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C276" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D276" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E276" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="F276" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="G276">
         <v>0</v>
       </c>
       <c r="H276" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I276">
         <v>1</v>
@@ -23802,16 +23802,16 @@
         <v>46216</v>
       </c>
       <c r="B277" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C277" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D277" t="s">
+        <v>116</v>
+      </c>
+      <c r="E277" t="s">
         <v>111</v>
-      </c>
-      <c r="E277" t="s">
-        <v>103</v>
       </c>
       <c r="F277" t="s">
         <v>63</v>
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="H277" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I277">
         <v>1</v>
@@ -23834,16 +23834,16 @@
         <v>46216</v>
       </c>
       <c r="B278" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C278" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D278" t="s">
+        <v>116</v>
+      </c>
+      <c r="E278" t="s">
         <v>111</v>
-      </c>
-      <c r="E278" t="s">
-        <v>103</v>
       </c>
       <c r="F278" t="s">
         <v>63</v>
@@ -23852,7 +23852,7 @@
         <v>0</v>
       </c>
       <c r="H278" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I278">
         <v>1</v>
@@ -23866,16 +23866,16 @@
         <v>46216</v>
       </c>
       <c r="B279" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C279" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D279" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E279" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F279" t="s">
         <v>63</v>
@@ -23884,7 +23884,7 @@
         <v>0</v>
       </c>
       <c r="H279" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I279">
         <v>1</v>
@@ -23898,31 +23898,31 @@
         <v>46216</v>
       </c>
       <c r="B280" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C280" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="D280" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="E280" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="F280" t="s">
         <v>63</v>
       </c>
       <c r="G280">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H280" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="I280">
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
@@ -23930,31 +23930,31 @@
         <v>46216</v>
       </c>
       <c r="B281" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="C281" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="D281" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="E281" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="F281" t="s">
         <v>63</v>
       </c>
       <c r="G281">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="H281" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="I281">
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
@@ -23962,22 +23962,22 @@
         <v>46216</v>
       </c>
       <c r="B282" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="C282" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D282" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="E282" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="F282" t="s">
         <v>63</v>
       </c>
       <c r="G282">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H282" t="s">
         <v>15</v>
@@ -23994,22 +23994,22 @@
         <v>46216</v>
       </c>
       <c r="B283" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C283" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D283" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="E283" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="F283" t="s">
         <v>63</v>
       </c>
       <c r="G283">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H283" t="s">
         <v>15</v>
@@ -24023,7 +24023,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B284" t="s">
         <v>32</v>
@@ -24035,7 +24035,7 @@
         <v>12</v>
       </c>
       <c r="E284" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="F284" t="s">
         <v>63</v>
@@ -24055,25 +24055,25 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B285" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C285" t="s">
         <v>11</v>
       </c>
       <c r="D285" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="E285" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="F285" t="s">
         <v>63</v>
       </c>
       <c r="G285">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="H285" t="s">
         <v>15</v>
@@ -24090,13 +24090,13 @@
         <v>46217</v>
       </c>
       <c r="B286" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C286" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D286" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E286" t="s">
         <v>19</v>
@@ -24105,7 +24105,7 @@
         <v>63</v>
       </c>
       <c r="G286">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H286" t="s">
         <v>15</v>
@@ -24122,7 +24122,7 @@
         <v>46217</v>
       </c>
       <c r="B287" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C287" t="s">
         <v>11</v>
@@ -24137,7 +24137,7 @@
         <v>63</v>
       </c>
       <c r="G287">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="H287" t="s">
         <v>15</v>
@@ -24154,22 +24154,22 @@
         <v>46217</v>
       </c>
       <c r="B288" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="C288" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D288" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="E288" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="F288" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G288">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="H288" t="s">
         <v>15</v>
@@ -24186,28 +24186,28 @@
         <v>46217</v>
       </c>
       <c r="B289" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="C289" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D289" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="E289" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F289" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="G289">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="H289" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I289">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J289" t="s">
         <v>16</v>
@@ -24218,28 +24218,28 @@
         <v>46217</v>
       </c>
       <c r="B290" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C290" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="D290" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="E290" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="F290" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G290">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="H290" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I290">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J290" t="s">
         <v>16</v>
@@ -24253,19 +24253,19 @@
         <v>121</v>
       </c>
       <c r="C291" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="D291" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="E291" t="s">
         <v>13</v>
       </c>
       <c r="F291" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G291">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H291" t="s">
         <v>31</v>
@@ -24282,22 +24282,22 @@
         <v>46217</v>
       </c>
       <c r="B292" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C292" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D292" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E292" t="s">
         <v>13</v>
       </c>
       <c r="F292" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G292">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H292" t="s">
         <v>31</v>
@@ -24314,28 +24314,28 @@
         <v>46217</v>
       </c>
       <c r="B293" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C293" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="D293" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="E293" t="s">
         <v>13</v>
       </c>
       <c r="F293" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G293">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="H293" t="s">
         <v>31</v>
       </c>
       <c r="I293">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J293" t="s">
         <v>16</v>
@@ -24346,22 +24346,22 @@
         <v>46217</v>
       </c>
       <c r="B294" t="s">
+        <v>127</v>
+      </c>
+      <c r="C294" t="s">
         <v>124</v>
       </c>
-      <c r="C294" t="s">
-        <v>22</v>
-      </c>
       <c r="D294" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="E294" t="s">
         <v>13</v>
       </c>
       <c r="F294" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G294">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="H294" t="s">
         <v>31</v>
@@ -24378,19 +24378,19 @@
         <v>46217</v>
       </c>
       <c r="B295" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C295" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="D295" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="E295" t="s">
         <v>13</v>
       </c>
       <c r="F295" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G295">
         <v>280</v>
@@ -24410,7 +24410,7 @@
         <v>46217</v>
       </c>
       <c r="B296" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C296" t="s">
         <v>22</v>
@@ -24422,10 +24422,10 @@
         <v>13</v>
       </c>
       <c r="F296" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G296">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="H296" t="s">
         <v>31</v>
@@ -24442,28 +24442,28 @@
         <v>46217</v>
       </c>
       <c r="B297" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C297" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="D297" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="E297" t="s">
         <v>13</v>
       </c>
       <c r="F297" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G297">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="H297" t="s">
         <v>31</v>
       </c>
       <c r="I297">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J297" t="s">
         <v>16</v>
@@ -24474,7 +24474,7 @@
         <v>46217</v>
       </c>
       <c r="B298" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="C298" t="s">
         <v>22</v>
@@ -24486,10 +24486,10 @@
         <v>13</v>
       </c>
       <c r="F298" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G298">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H298" t="s">
         <v>31</v>
@@ -24506,7 +24506,7 @@
         <v>46217</v>
       </c>
       <c r="B299" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C299" t="s">
         <v>22</v>
@@ -24518,10 +24518,10 @@
         <v>13</v>
       </c>
       <c r="F299" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G299">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H299" t="s">
         <v>31</v>
@@ -24538,7 +24538,7 @@
         <v>46217</v>
       </c>
       <c r="B300" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C300" t="s">
         <v>22</v>
@@ -24550,10 +24550,10 @@
         <v>13</v>
       </c>
       <c r="F300" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G300">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="H300" t="s">
         <v>31</v>
@@ -24570,7 +24570,7 @@
         <v>46217</v>
       </c>
       <c r="B301" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C301" t="s">
         <v>22</v>
@@ -24582,10 +24582,10 @@
         <v>13</v>
       </c>
       <c r="F301" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G301">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H301" t="s">
         <v>31</v>
@@ -24602,7 +24602,7 @@
         <v>46217</v>
       </c>
       <c r="B302" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C302" t="s">
         <v>22</v>
@@ -24614,10 +24614,10 @@
         <v>13</v>
       </c>
       <c r="F302" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G302">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H302" t="s">
         <v>31</v>
@@ -24634,22 +24634,22 @@
         <v>46217</v>
       </c>
       <c r="B303" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C303" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="D303" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="E303" t="s">
         <v>13</v>
       </c>
       <c r="F303" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G303">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H303" t="s">
         <v>31</v>
@@ -24666,30 +24666,94 @@
         <v>46217</v>
       </c>
       <c r="B304" t="s">
+        <v>136</v>
+      </c>
+      <c r="C304" t="s">
+        <v>22</v>
+      </c>
+      <c r="D304" t="s">
+        <v>74</v>
+      </c>
+      <c r="E304" t="s">
+        <v>13</v>
+      </c>
+      <c r="F304" t="s">
+        <v>122</v>
+      </c>
+      <c r="G304">
+        <v>275</v>
+      </c>
+      <c r="H304" t="s">
+        <v>31</v>
+      </c>
+      <c r="I304">
+        <v>2</v>
+      </c>
+      <c r="J304" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B305" t="s">
+        <v>137</v>
+      </c>
+      <c r="C305" t="s">
+        <v>124</v>
+      </c>
+      <c r="D305" t="s">
+        <v>125</v>
+      </c>
+      <c r="E305" t="s">
+        <v>13</v>
+      </c>
+      <c r="F305" t="s">
+        <v>122</v>
+      </c>
+      <c r="G305">
+        <v>260</v>
+      </c>
+      <c r="H305" t="s">
+        <v>31</v>
+      </c>
+      <c r="I305">
+        <v>4</v>
+      </c>
+      <c r="J305" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B306" t="s">
         <v>18</v>
       </c>
-      <c r="C304" t="s">
-        <v>11</v>
-      </c>
-      <c r="D304" t="s">
+      <c r="C306" t="s">
+        <v>11</v>
+      </c>
+      <c r="D306" t="s">
         <v>12</v>
       </c>
-      <c r="E304" t="s">
+      <c r="E306" t="s">
         <v>71</v>
       </c>
-      <c r="F304" t="s">
+      <c r="F306" t="s">
         <v>63</v>
       </c>
-      <c r="G304">
+      <c r="G306">
         <v>240</v>
       </c>
-      <c r="H304" t="s">
-        <v>15</v>
-      </c>
-      <c r="I304">
-        <v>1</v>
-      </c>
-      <c r="J304" t="s">
+      <c r="H306" t="s">
+        <v>15</v>
+      </c>
+      <c r="I306">
+        <v>1</v>
+      </c>
+      <c r="J306" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0605DEBD-E8E0-4C4B-8D27-3330DD2335AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D58B0F-6D11-4BCE-B6CE-0B36459E9B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{3CD98A3B-32AC-499F-9554-12B0DEADF92B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{9793EF17-DC9C-40DF-A473-5BC00A817348}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -2087,7 +2087,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7C78D4-A5A8-4EFB-ADCF-1731A440FDC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF2112D-19D1-4B36-AD21-F0F0114A6485}">
   <dimension ref="A1:P259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -14964,9 +14964,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBF609F-9446-4C68-8EBB-871681E3905C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAF8B08-09A0-4CF6-A094-0D00EA8EB361}">
   <dimension ref="A1:J330"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D58B0F-6D11-4BCE-B6CE-0B36459E9B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{250D9FE8-4934-455C-B336-CD5455AFF23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{9793EF17-DC9C-40DF-A473-5BC00A817348}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{7229C977-2B0B-4068-8770-BD977E2FCDBF}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -2087,7 +2087,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF2112D-19D1-4B36-AD21-F0F0114A6485}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76A9A0E-7836-4CBF-B67F-295268A471DD}">
   <dimension ref="A1:P259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2161,7 +2161,7 @@
         <v>260</v>
       </c>
       <c r="G2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>158</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         <v>270</v>
       </c>
       <c r="G104">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -7276,7 +7276,7 @@
         <v>158</v>
       </c>
       <c r="L104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M104">
         <v>0</v>
@@ -8661,7 +8661,7 @@
         <v>235</v>
       </c>
       <c r="G132">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H132">
         <v>0</v>
@@ -8676,7 +8676,7 @@
         <v>158</v>
       </c>
       <c r="L132">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M132">
         <v>10</v>
@@ -11411,7 +11411,7 @@
         <v>235</v>
       </c>
       <c r="G187">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -11420,13 +11420,13 @@
         <v>5</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K187" t="s">
         <v>152</v>
       </c>
       <c r="L187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M187">
         <v>3</v>
@@ -11661,7 +11661,7 @@
         <v>235</v>
       </c>
       <c r="G192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -11670,13 +11670,13 @@
         <v>10</v>
       </c>
       <c r="J192">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K192" t="s">
         <v>152</v>
       </c>
       <c r="L192">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M192">
         <v>8</v>
@@ -11811,7 +11811,7 @@
         <v>250</v>
       </c>
       <c r="G195">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>158</v>
       </c>
       <c r="L195">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M195">
         <v>8</v>
@@ -14964,12 +14964,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAF8B08-09A0-4CF6-A094-0D00EA8EB361}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6916245A-F40C-4406-9EFC-D7BAA06CB412}">
   <dimension ref="A1:J330"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="30.25" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -15061,7 +15058,7 @@
         <v>15</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -15093,7 +15090,7 @@
         <v>22</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
@@ -15349,7 +15346,7 @@
         <v>15</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
@@ -15477,7 +15474,7 @@
         <v>22</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="s">
         <v>16</v>
@@ -15573,7 +15570,7 @@
         <v>22</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="s">
         <v>16</v>
@@ -15637,7 +15634,7 @@
         <v>22</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="s">
         <v>16</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CC52AE4-9242-4280-BF3F-D9EEEA9EE235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E94C96CF-6654-44E6-95F8-580149457726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{E8A0EF21-9F67-40DF-8FE1-BCFD33364830}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{98E6D49B-EE02-4CDB-BA85-B928B2BDE159}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4223" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4426" uniqueCount="559">
   <si>
     <t>날짜</t>
   </si>
@@ -507,6 +507,15 @@
     <t>BJM898-GNBK260</t>
   </si>
   <si>
+    <t>BJW1170-BKSL235</t>
+  </si>
+  <si>
+    <t>ECW304-WHPK255</t>
+  </si>
+  <si>
+    <t>BJW1170-SLAP245</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1428,9 +1437,6 @@
     <t>BJW1170APPU 바오지 여성 러닝화 살구퍼플 255</t>
   </si>
   <si>
-    <t>BJW1170-BKSL235</t>
-  </si>
-  <si>
     <t>BJW1170BKSL 바오지 여성 러닝화 블랙실버 235</t>
   </si>
   <si>
@@ -1458,9 +1464,6 @@
     <t>BJW1170SLAP 바오지 여성 러닝화 실버살구 240</t>
   </si>
   <si>
-    <t>BJW1170-SLAP245</t>
-  </si>
-  <si>
     <t>BJW1170SLAP 바오지 여성 러닝화 실버살구 245</t>
   </si>
   <si>
@@ -1648,9 +1651,6 @@
   </si>
   <si>
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 250</t>
-  </si>
-  <si>
-    <t>ECW304-WHPK255</t>
   </si>
   <si>
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 255</t>
@@ -2102,7 +2102,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846820B7-0084-42CC-B0DF-809E127C3EB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD41C6CD-871D-402E-AA22-2A35F4C0742F}">
   <dimension ref="A1:P259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2111,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2126,31 +2126,31 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="M1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="N1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
@@ -2161,7 +2161,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2211,7 +2211,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -2261,7 +2261,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2311,7 +2311,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2361,7 +2361,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2411,7 +2411,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2461,7 +2461,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2511,7 +2511,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2561,7 +2561,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2611,7 +2611,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2658,16 +2658,16 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2708,16 +2708,16 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" t="s">
         <v>181</v>
       </c>
-      <c r="C13" t="s">
-        <v>178</v>
-      </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2758,16 +2758,16 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" t="s">
         <v>182</v>
-      </c>
-      <c r="B14" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" t="s">
-        <v>179</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2808,16 +2808,16 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2858,16 +2858,16 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2908,16 +2908,16 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2958,16 +2958,16 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3008,16 +3008,16 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3058,16 +3058,16 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C20" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3108,16 +3108,16 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3158,16 +3158,16 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3208,16 +3208,16 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C23" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3258,16 +3258,16 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C24" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3308,16 +3308,16 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C25" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3358,16 +3358,16 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3408,16 +3408,16 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B27" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C27" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3458,16 +3458,16 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B28" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3508,16 +3508,16 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B29" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3558,16 +3558,16 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3608,16 +3608,16 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C31" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3658,16 +3658,16 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D32" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3688,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3708,16 +3708,16 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3758,16 +3758,16 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>226</v>
+      </c>
+      <c r="B34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" t="s">
         <v>223</v>
-      </c>
-      <c r="B34" t="s">
-        <v>224</v>
-      </c>
-      <c r="C34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D34" t="s">
-        <v>220</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3808,16 +3808,16 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B35" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D35" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3858,16 +3858,16 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C36" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3908,16 +3908,16 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B37" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3958,16 +3958,16 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4008,16 +4008,16 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C39" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D39" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4058,16 +4058,16 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C40" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D40" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4108,16 +4108,16 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B41" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C41" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4158,16 +4158,16 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B42" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C42" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D42" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4208,16 +4208,16 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B43" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C43" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D43" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4258,16 +4258,16 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B44" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C44" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D44" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4308,16 +4308,16 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B45" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C45" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D45" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4338,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4358,16 +4358,16 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B46" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C46" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D46" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4408,16 +4408,16 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B47" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C47" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D47" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4458,16 +4458,16 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B48" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C48" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D48" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4508,16 +4508,16 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B49" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C49" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D49" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4558,16 +4558,16 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C50" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D50" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4608,16 +4608,16 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B51" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D51" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4658,16 +4658,16 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B52" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C52" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D52" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4708,16 +4708,16 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B53" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C53" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D53" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4758,16 +4758,16 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>267</v>
+      </c>
+      <c r="B54" t="s">
+        <v>268</v>
+      </c>
+      <c r="C54" t="s">
+        <v>181</v>
+      </c>
+      <c r="D54" t="s">
         <v>264</v>
-      </c>
-      <c r="B54" t="s">
-        <v>265</v>
-      </c>
-      <c r="C54" t="s">
-        <v>178</v>
-      </c>
-      <c r="D54" t="s">
-        <v>261</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -4808,16 +4808,16 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B55" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C55" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D55" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -4858,16 +4858,16 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B56" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C56" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D56" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -4908,16 +4908,16 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B57" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C57" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D57" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -4958,16 +4958,16 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B58" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C58" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5008,16 +5008,16 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B59" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C59" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5058,16 +5058,16 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B60" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C60" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D60" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5108,16 +5108,16 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B61" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D61" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5158,16 +5158,16 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B62" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C62" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D62" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -5208,16 +5208,16 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B63" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C63" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D63" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -5258,16 +5258,16 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B64" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C64" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D64" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -5308,16 +5308,16 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B65" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C65" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D65" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5358,16 +5358,16 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B66" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C66" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5388,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -5411,7 +5411,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -5438,7 +5438,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -5461,7 +5461,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -5511,7 +5511,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -5538,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L69">
         <v>4</v>
@@ -5561,7 +5561,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -5611,7 +5611,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -5658,10 +5658,10 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -5688,7 +5688,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -5738,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O73">
         <v>3</v>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B74" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -5788,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B75" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -5838,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -5858,10 +5858,10 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B76" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -5908,10 +5908,10 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B77" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -5958,10 +5958,10 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B78" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -6008,10 +6008,10 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B79" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -6061,7 +6061,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -6088,7 +6088,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B81" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B82" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6208,10 +6208,10 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B83" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -6238,7 +6238,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -6258,10 +6258,10 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B84" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -6288,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -6308,10 +6308,10 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B85" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -6338,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -6358,10 +6358,10 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B86" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -6388,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -6408,10 +6408,10 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B87" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -6461,7 +6461,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B89" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -6538,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -6588,7 +6588,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B91" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -6658,10 +6658,10 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B92" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -6758,10 +6758,10 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B94" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -6788,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -6808,10 +6808,10 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B95" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -6858,10 +6858,10 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B96" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B97" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -6938,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6961,7 +6961,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -6988,7 +6988,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L98">
         <v>1</v>
@@ -7008,10 +7008,10 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B99" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -7038,7 +7038,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -7058,10 +7058,10 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B100" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -7088,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -7108,10 +7108,10 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B101" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -7138,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -7158,10 +7158,10 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B102" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B103" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -7238,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L104">
         <v>4</v>
@@ -7308,10 +7308,10 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B105" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -7338,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -7361,7 +7361,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -7388,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B107" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -7438,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -7461,7 +7461,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -7488,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -7511,7 +7511,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -7538,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -7558,10 +7558,10 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B110" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -7608,10 +7608,10 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B111" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -7638,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -7688,7 +7688,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L112">
         <v>3</v>
@@ -7697,7 +7697,7 @@
         <v>0</v>
       </c>
       <c r="N112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O112">
         <v>3</v>
@@ -7711,7 +7711,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -7726,31 +7726,31 @@
         <v>265</v>
       </c>
       <c r="G113">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M113">
         <v>3</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P113" t="s">
         <v>16</v>
@@ -7761,7 +7761,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -7776,31 +7776,31 @@
         <v>270</v>
       </c>
       <c r="G114">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M114">
         <v>0</v>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P114" t="s">
         <v>16</v>
@@ -7811,7 +7811,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -7838,7 +7838,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L115">
         <v>2</v>
@@ -7861,7 +7861,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -7888,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L116">
         <v>2</v>
@@ -7911,7 +7911,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -7938,7 +7938,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -7961,7 +7961,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -7988,7 +7988,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B119" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -8061,7 +8061,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -8111,7 +8111,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -8138,7 +8138,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -8161,7 +8161,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L122">
         <v>4</v>
@@ -8211,7 +8211,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -8238,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -8261,7 +8261,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -8288,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -8311,7 +8311,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -8338,7 +8338,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -8361,7 +8361,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -8388,7 +8388,7 @@
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -8411,7 +8411,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -8426,31 +8426,31 @@
         <v>235</v>
       </c>
       <c r="G127">
+        <v>3</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>7</v>
+      </c>
+      <c r="J127">
         <v>4</v>
       </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>6</v>
-      </c>
-      <c r="J127">
-        <v>2</v>
-      </c>
       <c r="K127" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M127">
         <v>5</v>
       </c>
       <c r="N127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P127" t="s">
         <v>16</v>
@@ -8461,7 +8461,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -8488,7 +8488,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -8511,7 +8511,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -8538,7 +8538,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L129">
         <v>6</v>
@@ -8561,7 +8561,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -8588,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L130">
         <v>6</v>
@@ -8611,7 +8611,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -8638,7 +8638,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -8661,7 +8661,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -8688,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L132">
         <v>17</v>
@@ -8697,7 +8697,7 @@
         <v>10</v>
       </c>
       <c r="N132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132">
         <v>13</v>
@@ -8711,7 +8711,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -8738,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L133">
         <v>7</v>
@@ -8761,7 +8761,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -8788,7 +8788,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L134">
         <v>9</v>
@@ -8811,7 +8811,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -8838,7 +8838,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L135">
         <v>4</v>
@@ -8861,7 +8861,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -8888,7 +8888,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L136">
         <v>3</v>
@@ -8911,7 +8911,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L137">
         <v>1</v>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B138" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -8988,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -9008,10 +9008,10 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B139" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -9038,7 +9038,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L139">
         <v>0</v>
@@ -9061,7 +9061,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L140">
         <v>1</v>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B141" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -9138,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L141">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -9188,7 +9188,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -9208,10 +9208,10 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B143" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -9258,10 +9258,10 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B144" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -9288,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -9308,10 +9308,10 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B145" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -9358,10 +9358,10 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B146" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -9388,7 +9388,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -9408,10 +9408,10 @@
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -9438,7 +9438,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L147">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -9488,7 +9488,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L148">
         <v>2</v>
@@ -9508,10 +9508,10 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -9561,7 +9561,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -9588,7 +9588,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -9611,7 +9611,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -9658,16 +9658,16 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B152" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C152" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D152" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -9688,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -9708,16 +9708,16 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B153" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C153" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -9738,7 +9738,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -9758,16 +9758,16 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>423</v>
+      </c>
+      <c r="B154" t="s">
+        <v>424</v>
+      </c>
+      <c r="C154" t="s">
+        <v>181</v>
+      </c>
+      <c r="D154" t="s">
         <v>420</v>
-      </c>
-      <c r="B154" t="s">
-        <v>421</v>
-      </c>
-      <c r="C154" t="s">
-        <v>178</v>
-      </c>
-      <c r="D154" t="s">
-        <v>417</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -9788,7 +9788,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -9808,16 +9808,16 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B155" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C155" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -9838,7 +9838,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -9858,16 +9858,16 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B156" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C156" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -9888,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -9908,16 +9908,16 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B157" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C157" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D157" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -9958,16 +9958,16 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B158" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C158" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D158" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -9988,7 +9988,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -10008,16 +10008,16 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B159" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C159" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D159" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -10038,7 +10038,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -10058,16 +10058,16 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B160" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C160" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D160" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -10088,7 +10088,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -10108,16 +10108,16 @@
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B161" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C161" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D161" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -10138,7 +10138,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -10158,16 +10158,16 @@
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B162" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C162" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D162" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -10188,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -10208,16 +10208,16 @@
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B163" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C163" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D163" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -10238,7 +10238,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -10258,16 +10258,16 @@
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B164" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C164" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D164" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -10288,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -10308,16 +10308,16 @@
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B165" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C165" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D165" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -10338,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -10358,16 +10358,16 @@
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B166" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C166" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D166" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -10388,7 +10388,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -10408,16 +10408,16 @@
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B167" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C167" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D167" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -10438,7 +10438,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -10458,16 +10458,16 @@
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B168" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C168" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D168" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -10488,7 +10488,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -10508,16 +10508,16 @@
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B169" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C169" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D169" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -10538,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -10558,16 +10558,16 @@
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B170" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C170" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D170" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -10588,7 +10588,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -10608,16 +10608,16 @@
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B171" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C171" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -10638,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -10661,7 +10661,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -10676,31 +10676,31 @@
         <v>235</v>
       </c>
       <c r="G172">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J172">
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L172">
+        <v>4</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="N172">
+        <v>1</v>
+      </c>
+      <c r="O172">
         <v>3</v>
-      </c>
-      <c r="M172">
-        <v>0</v>
-      </c>
-      <c r="N172">
-        <v>0</v>
-      </c>
-      <c r="O172">
-        <v>2</v>
       </c>
       <c r="P172" t="s">
         <v>16</v>
@@ -10711,7 +10711,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -10738,7 +10738,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L173">
         <v>3</v>
@@ -10761,7 +10761,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -10776,31 +10776,31 @@
         <v>245</v>
       </c>
       <c r="G174">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H174">
         <v>0</v>
       </c>
       <c r="I174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J174">
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P174" t="s">
         <v>16</v>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B175" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -10838,7 +10838,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L175">
         <v>0</v>
@@ -10861,7 +10861,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -10888,7 +10888,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -10908,10 +10908,10 @@
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>462</v>
+        <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -10926,31 +10926,31 @@
         <v>235</v>
       </c>
       <c r="G177">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H177">
         <v>0</v>
       </c>
       <c r="I177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J177">
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P177" t="s">
         <v>16</v>
@@ -10961,7 +10961,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -10988,7 +10988,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L178">
         <v>1</v>
@@ -11008,10 +11008,10 @@
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B179" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -11061,7 +11061,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -11076,31 +11076,31 @@
         <v>250</v>
       </c>
       <c r="G180">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H180">
         <v>0</v>
       </c>
       <c r="I180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J180">
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P180" t="s">
         <v>16</v>
@@ -11108,10 +11108,10 @@
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B181" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -11161,7 +11161,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -11176,31 +11176,31 @@
         <v>235</v>
       </c>
       <c r="G182">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H182">
         <v>0</v>
       </c>
       <c r="I182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J182">
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L182">
+        <v>3</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
         <v>2</v>
       </c>
-      <c r="M182">
-        <v>0</v>
-      </c>
-      <c r="N182">
-        <v>1</v>
-      </c>
       <c r="O182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P182" t="s">
         <v>16</v>
@@ -11211,7 +11211,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -11226,31 +11226,31 @@
         <v>240</v>
       </c>
       <c r="G183">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H183">
         <v>0</v>
       </c>
       <c r="I183">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J183">
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L183">
+        <v>4</v>
+      </c>
+      <c r="M183">
         <v>2</v>
       </c>
-      <c r="M183">
-        <v>0</v>
-      </c>
       <c r="N183">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O183">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P183" t="s">
         <v>16</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>472</v>
+        <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -11276,31 +11276,31 @@
         <v>245</v>
       </c>
       <c r="G184">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
       <c r="I184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J184">
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P184" t="s">
         <v>16</v>
@@ -11311,7 +11311,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -11326,31 +11326,31 @@
         <v>250</v>
       </c>
       <c r="G185">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H185">
         <v>0</v>
       </c>
       <c r="I185">
+        <v>3</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185" t="s">
+        <v>169</v>
+      </c>
+      <c r="L185">
+        <v>3</v>
+      </c>
+      <c r="M185">
+        <v>1</v>
+      </c>
+      <c r="N185">
         <v>2</v>
       </c>
-      <c r="J185">
-        <v>0</v>
-      </c>
-      <c r="K185" t="s">
-        <v>166</v>
-      </c>
-      <c r="L185">
-        <v>2</v>
-      </c>
-      <c r="M185">
-        <v>0</v>
-      </c>
-      <c r="N185">
-        <v>1</v>
-      </c>
       <c r="O185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P185" t="s">
         <v>16</v>
@@ -11358,10 +11358,10 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B186" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -11388,7 +11388,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L186">
         <v>0</v>
@@ -11411,7 +11411,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -11438,7 +11438,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L187">
         <v>7</v>
@@ -11461,7 +11461,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -11488,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -11511,7 +11511,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -11538,7 +11538,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L189">
         <v>7</v>
@@ -11561,7 +11561,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -11588,7 +11588,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L190">
         <v>7</v>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B191" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -11638,7 +11638,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -11661,7 +11661,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -11688,7 +11688,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L192">
         <v>12</v>
@@ -11711,7 +11711,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L193">
         <v>20</v>
@@ -11761,7 +11761,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -11788,7 +11788,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L194">
         <v>20</v>
@@ -11811,7 +11811,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -11838,7 +11838,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -11861,7 +11861,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -11888,7 +11888,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L196">
         <v>7</v>
@@ -11908,10 +11908,10 @@
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B197" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -11938,7 +11938,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -11961,7 +11961,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -11988,7 +11988,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -12011,7 +12011,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -12038,7 +12038,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -12058,10 +12058,10 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B200" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -12088,7 +12088,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -12126,31 +12126,31 @@
         <v>255</v>
       </c>
       <c r="G201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H201">
         <v>0</v>
       </c>
       <c r="I201">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J201">
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L201">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M201">
         <v>2</v>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O201">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P201" t="s">
         <v>16</v>
@@ -12158,10 +12158,10 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B202" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -12188,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -12211,7 +12211,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -12238,7 +12238,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L203">
         <v>1</v>
@@ -12258,10 +12258,10 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B204" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -12288,7 +12288,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -12311,7 +12311,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -12338,7 +12338,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -12358,10 +12358,10 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B206" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -12388,7 +12388,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -12408,10 +12408,10 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B207" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -12458,10 +12458,10 @@
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B208" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -12488,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -12508,10 +12508,10 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B209" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -12538,7 +12538,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -12558,10 +12558,10 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B210" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -12588,7 +12588,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B211" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -12638,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -12658,10 +12658,10 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B212" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -12688,7 +12688,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -12708,10 +12708,10 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B213" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -12738,7 +12738,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -12761,7 +12761,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -12788,7 +12788,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -12811,7 +12811,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -12838,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -12858,10 +12858,10 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -12911,7 +12911,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -12926,31 +12926,31 @@
         <v>235</v>
       </c>
       <c r="G217">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H217">
         <v>0</v>
       </c>
       <c r="I217">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J217">
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L217">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M217">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O217">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P217" t="s">
         <v>16</v>
@@ -12961,7 +12961,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -12988,7 +12988,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L218">
         <v>3</v>
@@ -13011,7 +13011,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -13026,31 +13026,31 @@
         <v>245</v>
       </c>
       <c r="G219">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J219">
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P219" t="s">
         <v>16</v>
@@ -13061,7 +13061,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -13076,31 +13076,31 @@
         <v>250</v>
       </c>
       <c r="G220">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H220">
         <v>0</v>
       </c>
       <c r="I220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J220">
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P220" t="s">
         <v>16</v>
@@ -13108,10 +13108,10 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B221" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -13138,7 +13138,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -13188,7 +13188,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -13211,7 +13211,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -13226,31 +13226,31 @@
         <v>240</v>
       </c>
       <c r="G223">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H223">
         <v>0</v>
       </c>
       <c r="I223">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J223">
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L223">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M223">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O223">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P223" t="s">
         <v>16</v>
@@ -13261,7 +13261,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -13276,31 +13276,31 @@
         <v>245</v>
       </c>
       <c r="G224">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H224">
         <v>0</v>
       </c>
       <c r="I224">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J224">
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L224">
+        <v>10</v>
+      </c>
+      <c r="M224">
+        <v>5</v>
+      </c>
+      <c r="N224">
+        <v>1</v>
+      </c>
+      <c r="O224">
         <v>9</v>
-      </c>
-      <c r="M224">
-        <v>4</v>
-      </c>
-      <c r="N224">
-        <v>0</v>
-      </c>
-      <c r="O224">
-        <v>8</v>
       </c>
       <c r="P224" t="s">
         <v>16</v>
@@ -13311,7 +13311,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -13338,7 +13338,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L225">
         <v>6</v>
@@ -13361,7 +13361,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -13388,7 +13388,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L226">
         <v>2</v>
@@ -13411,7 +13411,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -13426,31 +13426,31 @@
         <v>235</v>
       </c>
       <c r="G227">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J227">
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L227">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M227">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O227">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P227" t="s">
         <v>16</v>
@@ -13461,7 +13461,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -13476,31 +13476,31 @@
         <v>240</v>
       </c>
       <c r="G228">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J228">
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L228">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M228">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O228">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P228" t="s">
         <v>16</v>
@@ -13511,7 +13511,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -13526,31 +13526,31 @@
         <v>245</v>
       </c>
       <c r="G229">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
       <c r="I229">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J229">
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L229">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M229">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O229">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P229" t="s">
         <v>16</v>
@@ -13561,7 +13561,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -13576,31 +13576,31 @@
         <v>250</v>
       </c>
       <c r="G230">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H230">
         <v>0</v>
       </c>
       <c r="I230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J230">
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L230">
+        <v>6</v>
+      </c>
+      <c r="M230">
         <v>5</v>
       </c>
-      <c r="M230">
-        <v>4</v>
-      </c>
       <c r="N230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P230" t="s">
         <v>16</v>
@@ -13608,7 +13608,7 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>536</v>
+        <v>156</v>
       </c>
       <c r="B231" t="s">
         <v>537</v>
@@ -13626,31 +13626,31 @@
         <v>255</v>
       </c>
       <c r="G231">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H231">
         <v>0</v>
       </c>
       <c r="I231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231">
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P231" t="s">
         <v>16</v>
@@ -13685,7 +13685,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -13732,7 +13732,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -13779,7 +13779,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -13873,7 +13873,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -13920,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -13967,7 +13967,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -14014,7 +14014,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -14061,7 +14061,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -14108,7 +14108,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -14155,7 +14155,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -14249,7 +14249,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -14296,7 +14296,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L245">
         <v>1</v>
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L246">
         <v>0</v>
@@ -14390,7 +14390,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -14437,7 +14437,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -14484,7 +14484,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -14531,7 +14531,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -14625,7 +14625,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -14672,7 +14672,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L253">
         <v>0</v>
@@ -14719,7 +14719,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -14766,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -14813,7 +14813,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L256">
         <v>2</v>
@@ -14860,7 +14860,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -14907,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L258">
         <v>2</v>
@@ -14954,7 +14954,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -14979,8 +14979,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0AE6982-E78F-4A96-BB14-DB6A137342DB}">
-  <dimension ref="A1:J341"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0DD2333-F3DA-49E3-97AF-6F00E0028080}">
+  <dimension ref="A1:J370"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -25892,6 +25892,934 @@
         <v>1</v>
       </c>
       <c r="J341" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A342" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B342" t="s">
+        <v>103</v>
+      </c>
+      <c r="C342" t="s">
+        <v>24</v>
+      </c>
+      <c r="D342" t="s">
+        <v>49</v>
+      </c>
+      <c r="E342" t="s">
+        <v>100</v>
+      </c>
+      <c r="F342" t="s">
+        <v>94</v>
+      </c>
+      <c r="G342">
+        <v>245</v>
+      </c>
+      <c r="H342" t="s">
+        <v>22</v>
+      </c>
+      <c r="I342">
+        <v>1</v>
+      </c>
+      <c r="J342" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A343" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B343" t="s">
+        <v>82</v>
+      </c>
+      <c r="C343" t="s">
+        <v>18</v>
+      </c>
+      <c r="D343" t="s">
+        <v>21</v>
+      </c>
+      <c r="E343" t="s">
+        <v>53</v>
+      </c>
+      <c r="F343" t="s">
+        <v>94</v>
+      </c>
+      <c r="G343">
+        <v>235</v>
+      </c>
+      <c r="H343" t="s">
+        <v>22</v>
+      </c>
+      <c r="I343">
+        <v>1</v>
+      </c>
+      <c r="J343" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A344" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B344" t="s">
+        <v>107</v>
+      </c>
+      <c r="C344" t="s">
+        <v>24</v>
+      </c>
+      <c r="D344" t="s">
+        <v>38</v>
+      </c>
+      <c r="E344" t="s">
+        <v>53</v>
+      </c>
+      <c r="F344" t="s">
+        <v>94</v>
+      </c>
+      <c r="G344">
+        <v>270</v>
+      </c>
+      <c r="H344" t="s">
+        <v>15</v>
+      </c>
+      <c r="I344">
+        <v>1</v>
+      </c>
+      <c r="J344" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A345" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B345" t="s">
+        <v>96</v>
+      </c>
+      <c r="C345" t="s">
+        <v>24</v>
+      </c>
+      <c r="D345" t="s">
+        <v>38</v>
+      </c>
+      <c r="E345" t="s">
+        <v>53</v>
+      </c>
+      <c r="F345" t="s">
+        <v>94</v>
+      </c>
+      <c r="G345">
+        <v>265</v>
+      </c>
+      <c r="H345" t="s">
+        <v>15</v>
+      </c>
+      <c r="I345">
+        <v>1</v>
+      </c>
+      <c r="J345" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A346" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B346" t="s">
+        <v>83</v>
+      </c>
+      <c r="C346" t="s">
+        <v>24</v>
+      </c>
+      <c r="D346" t="s">
+        <v>40</v>
+      </c>
+      <c r="E346" t="s">
+        <v>53</v>
+      </c>
+      <c r="F346" t="s">
+        <v>94</v>
+      </c>
+      <c r="G346">
+        <v>255</v>
+      </c>
+      <c r="H346" t="s">
+        <v>22</v>
+      </c>
+      <c r="I346">
+        <v>1</v>
+      </c>
+      <c r="J346" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A347" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B347" t="s">
+        <v>50</v>
+      </c>
+      <c r="C347" t="s">
+        <v>24</v>
+      </c>
+      <c r="D347" t="s">
+        <v>49</v>
+      </c>
+      <c r="E347" t="s">
+        <v>53</v>
+      </c>
+      <c r="F347" t="s">
+        <v>94</v>
+      </c>
+      <c r="G347">
+        <v>245</v>
+      </c>
+      <c r="H347" t="s">
+        <v>22</v>
+      </c>
+      <c r="I347">
+        <v>1</v>
+      </c>
+      <c r="J347" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A348" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B348" t="s">
+        <v>70</v>
+      </c>
+      <c r="C348" t="s">
+        <v>24</v>
+      </c>
+      <c r="D348" t="s">
+        <v>49</v>
+      </c>
+      <c r="E348" t="s">
+        <v>100</v>
+      </c>
+      <c r="F348" t="s">
+        <v>66</v>
+      </c>
+      <c r="G348">
+        <v>235</v>
+      </c>
+      <c r="H348" t="s">
+        <v>22</v>
+      </c>
+      <c r="I348">
+        <v>1</v>
+      </c>
+      <c r="J348" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A349" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B349" t="s">
+        <v>28</v>
+      </c>
+      <c r="C349" t="s">
+        <v>24</v>
+      </c>
+      <c r="D349" t="s">
+        <v>25</v>
+      </c>
+      <c r="E349" t="s">
+        <v>100</v>
+      </c>
+      <c r="F349" t="s">
+        <v>66</v>
+      </c>
+      <c r="G349">
+        <v>240</v>
+      </c>
+      <c r="H349" t="s">
+        <v>22</v>
+      </c>
+      <c r="I349">
+        <v>1</v>
+      </c>
+      <c r="J349" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A350" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B350" t="s">
+        <v>50</v>
+      </c>
+      <c r="C350" t="s">
+        <v>24</v>
+      </c>
+      <c r="D350" t="s">
+        <v>49</v>
+      </c>
+      <c r="E350" t="s">
+        <v>100</v>
+      </c>
+      <c r="F350" t="s">
+        <v>66</v>
+      </c>
+      <c r="G350">
+        <v>245</v>
+      </c>
+      <c r="H350" t="s">
+        <v>22</v>
+      </c>
+      <c r="I350">
+        <v>1</v>
+      </c>
+      <c r="J350" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A351" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B351" t="s">
+        <v>155</v>
+      </c>
+      <c r="C351" t="s">
+        <v>24</v>
+      </c>
+      <c r="D351" t="s">
+        <v>25</v>
+      </c>
+      <c r="E351" t="s">
+        <v>100</v>
+      </c>
+      <c r="F351" t="s">
+        <v>66</v>
+      </c>
+      <c r="G351">
+        <v>235</v>
+      </c>
+      <c r="H351" t="s">
+        <v>22</v>
+      </c>
+      <c r="I351">
+        <v>1</v>
+      </c>
+      <c r="J351" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A352" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B352" t="s">
+        <v>23</v>
+      </c>
+      <c r="C352" t="s">
+        <v>24</v>
+      </c>
+      <c r="D352" t="s">
+        <v>25</v>
+      </c>
+      <c r="E352" t="s">
+        <v>100</v>
+      </c>
+      <c r="F352" t="s">
+        <v>66</v>
+      </c>
+      <c r="G352">
+        <v>235</v>
+      </c>
+      <c r="H352" t="s">
+        <v>22</v>
+      </c>
+      <c r="I352">
+        <v>1</v>
+      </c>
+      <c r="J352" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A353" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B353" t="s">
+        <v>48</v>
+      </c>
+      <c r="C353" t="s">
+        <v>24</v>
+      </c>
+      <c r="D353" t="s">
+        <v>49</v>
+      </c>
+      <c r="E353" t="s">
+        <v>100</v>
+      </c>
+      <c r="F353" t="s">
+        <v>66</v>
+      </c>
+      <c r="G353">
+        <v>245</v>
+      </c>
+      <c r="H353" t="s">
+        <v>22</v>
+      </c>
+      <c r="I353">
+        <v>1</v>
+      </c>
+      <c r="J353" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A354" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B354" t="s">
+        <v>108</v>
+      </c>
+      <c r="C354" t="s">
+        <v>24</v>
+      </c>
+      <c r="D354" t="s">
+        <v>25</v>
+      </c>
+      <c r="E354" t="s">
+        <v>100</v>
+      </c>
+      <c r="F354" t="s">
+        <v>66</v>
+      </c>
+      <c r="G354">
+        <v>250</v>
+      </c>
+      <c r="H354" t="s">
+        <v>22</v>
+      </c>
+      <c r="I354">
+        <v>1</v>
+      </c>
+      <c r="J354" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A355" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B355" t="s">
+        <v>70</v>
+      </c>
+      <c r="C355" t="s">
+        <v>24</v>
+      </c>
+      <c r="D355" t="s">
+        <v>49</v>
+      </c>
+      <c r="E355" t="s">
+        <v>100</v>
+      </c>
+      <c r="F355" t="s">
+        <v>66</v>
+      </c>
+      <c r="G355">
+        <v>235</v>
+      </c>
+      <c r="H355" t="s">
+        <v>22</v>
+      </c>
+      <c r="I355">
+        <v>1</v>
+      </c>
+      <c r="J355" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A356" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B356" t="s">
+        <v>51</v>
+      </c>
+      <c r="C356" t="s">
+        <v>24</v>
+      </c>
+      <c r="D356" t="s">
+        <v>49</v>
+      </c>
+      <c r="E356" t="s">
+        <v>100</v>
+      </c>
+      <c r="F356" t="s">
+        <v>66</v>
+      </c>
+      <c r="G356">
+        <v>250</v>
+      </c>
+      <c r="H356" t="s">
+        <v>22</v>
+      </c>
+      <c r="I356">
+        <v>1</v>
+      </c>
+      <c r="J356" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A357" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B357" t="s">
+        <v>71</v>
+      </c>
+      <c r="C357" t="s">
+        <v>24</v>
+      </c>
+      <c r="D357" t="s">
+        <v>49</v>
+      </c>
+      <c r="E357" t="s">
+        <v>100</v>
+      </c>
+      <c r="F357" t="s">
+        <v>66</v>
+      </c>
+      <c r="G357">
+        <v>235</v>
+      </c>
+      <c r="H357" t="s">
+        <v>22</v>
+      </c>
+      <c r="I357">
+        <v>1</v>
+      </c>
+      <c r="J357" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A358" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B358" t="s">
+        <v>110</v>
+      </c>
+      <c r="C358" t="s">
+        <v>24</v>
+      </c>
+      <c r="D358" t="s">
+        <v>25</v>
+      </c>
+      <c r="E358" t="s">
+        <v>100</v>
+      </c>
+      <c r="F358" t="s">
+        <v>66</v>
+      </c>
+      <c r="G358">
+        <v>250</v>
+      </c>
+      <c r="H358" t="s">
+        <v>22</v>
+      </c>
+      <c r="I358">
+        <v>1</v>
+      </c>
+      <c r="J358" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A359" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B359" t="s">
+        <v>156</v>
+      </c>
+      <c r="C359" t="s">
+        <v>24</v>
+      </c>
+      <c r="D359" t="s">
+        <v>49</v>
+      </c>
+      <c r="E359" t="s">
+        <v>100</v>
+      </c>
+      <c r="F359" t="s">
+        <v>66</v>
+      </c>
+      <c r="G359">
+        <v>255</v>
+      </c>
+      <c r="H359" t="s">
+        <v>22</v>
+      </c>
+      <c r="I359">
+        <v>1</v>
+      </c>
+      <c r="J359" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A360" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B360" t="s">
+        <v>86</v>
+      </c>
+      <c r="C360" t="s">
+        <v>24</v>
+      </c>
+      <c r="D360" t="s">
+        <v>49</v>
+      </c>
+      <c r="E360" t="s">
+        <v>100</v>
+      </c>
+      <c r="F360" t="s">
+        <v>66</v>
+      </c>
+      <c r="G360">
+        <v>240</v>
+      </c>
+      <c r="H360" t="s">
+        <v>22</v>
+      </c>
+      <c r="I360">
+        <v>1</v>
+      </c>
+      <c r="J360" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A361" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B361" t="s">
+        <v>98</v>
+      </c>
+      <c r="C361" t="s">
+        <v>24</v>
+      </c>
+      <c r="D361" t="s">
+        <v>49</v>
+      </c>
+      <c r="E361" t="s">
+        <v>100</v>
+      </c>
+      <c r="F361" t="s">
+        <v>66</v>
+      </c>
+      <c r="G361">
+        <v>250</v>
+      </c>
+      <c r="H361" t="s">
+        <v>22</v>
+      </c>
+      <c r="I361">
+        <v>1</v>
+      </c>
+      <c r="J361" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A362" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B362" t="s">
+        <v>157</v>
+      </c>
+      <c r="C362" t="s">
+        <v>24</v>
+      </c>
+      <c r="D362" t="s">
+        <v>25</v>
+      </c>
+      <c r="E362" t="s">
+        <v>100</v>
+      </c>
+      <c r="F362" t="s">
+        <v>66</v>
+      </c>
+      <c r="G362">
+        <v>245</v>
+      </c>
+      <c r="H362" t="s">
+        <v>22</v>
+      </c>
+      <c r="I362">
+        <v>1</v>
+      </c>
+      <c r="J362" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A363" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B363" t="s">
+        <v>27</v>
+      </c>
+      <c r="C363" t="s">
+        <v>24</v>
+      </c>
+      <c r="D363" t="s">
+        <v>25</v>
+      </c>
+      <c r="E363" t="s">
+        <v>100</v>
+      </c>
+      <c r="F363" t="s">
+        <v>66</v>
+      </c>
+      <c r="G363">
+        <v>235</v>
+      </c>
+      <c r="H363" t="s">
+        <v>22</v>
+      </c>
+      <c r="I363">
+        <v>1</v>
+      </c>
+      <c r="J363" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A364" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B364" t="s">
+        <v>28</v>
+      </c>
+      <c r="C364" t="s">
+        <v>24</v>
+      </c>
+      <c r="D364" t="s">
+        <v>25</v>
+      </c>
+      <c r="E364" t="s">
+        <v>100</v>
+      </c>
+      <c r="F364" t="s">
+        <v>66</v>
+      </c>
+      <c r="G364">
+        <v>240</v>
+      </c>
+      <c r="H364" t="s">
+        <v>22</v>
+      </c>
+      <c r="I364">
+        <v>1</v>
+      </c>
+      <c r="J364" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A365" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B365" t="s">
+        <v>113</v>
+      </c>
+      <c r="C365" t="s">
+        <v>24</v>
+      </c>
+      <c r="D365" t="s">
+        <v>25</v>
+      </c>
+      <c r="E365" t="s">
+        <v>100</v>
+      </c>
+      <c r="F365" t="s">
+        <v>66</v>
+      </c>
+      <c r="G365">
+        <v>245</v>
+      </c>
+      <c r="H365" t="s">
+        <v>22</v>
+      </c>
+      <c r="I365">
+        <v>1</v>
+      </c>
+      <c r="J365" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A366" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B366" t="s">
+        <v>50</v>
+      </c>
+      <c r="C366" t="s">
+        <v>24</v>
+      </c>
+      <c r="D366" t="s">
+        <v>49</v>
+      </c>
+      <c r="E366" t="s">
+        <v>13</v>
+      </c>
+      <c r="F366" t="s">
+        <v>66</v>
+      </c>
+      <c r="G366">
+        <v>245</v>
+      </c>
+      <c r="H366" t="s">
+        <v>22</v>
+      </c>
+      <c r="I366">
+        <v>1</v>
+      </c>
+      <c r="J366" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A367" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B367" t="s">
+        <v>50</v>
+      </c>
+      <c r="C367" t="s">
+        <v>24</v>
+      </c>
+      <c r="D367" t="s">
+        <v>49</v>
+      </c>
+      <c r="E367" t="s">
+        <v>13</v>
+      </c>
+      <c r="F367" t="s">
+        <v>66</v>
+      </c>
+      <c r="G367">
+        <v>245</v>
+      </c>
+      <c r="H367" t="s">
+        <v>22</v>
+      </c>
+      <c r="I367">
+        <v>1</v>
+      </c>
+      <c r="J367" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A368" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B368" t="s">
+        <v>76</v>
+      </c>
+      <c r="C368" t="s">
+        <v>24</v>
+      </c>
+      <c r="D368" t="s">
+        <v>49</v>
+      </c>
+      <c r="E368" t="s">
+        <v>13</v>
+      </c>
+      <c r="F368" t="s">
+        <v>66</v>
+      </c>
+      <c r="G368">
+        <v>240</v>
+      </c>
+      <c r="H368" t="s">
+        <v>22</v>
+      </c>
+      <c r="I368">
+        <v>1</v>
+      </c>
+      <c r="J368" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A369" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B369" t="s">
+        <v>103</v>
+      </c>
+      <c r="C369" t="s">
+        <v>24</v>
+      </c>
+      <c r="D369" t="s">
+        <v>49</v>
+      </c>
+      <c r="E369" t="s">
+        <v>13</v>
+      </c>
+      <c r="F369" t="s">
+        <v>66</v>
+      </c>
+      <c r="G369">
+        <v>245</v>
+      </c>
+      <c r="H369" t="s">
+        <v>22</v>
+      </c>
+      <c r="I369">
+        <v>1</v>
+      </c>
+      <c r="J369" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A370" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B370" t="s">
+        <v>71</v>
+      </c>
+      <c r="C370" t="s">
+        <v>24</v>
+      </c>
+      <c r="D370" t="s">
+        <v>49</v>
+      </c>
+      <c r="E370" t="s">
+        <v>13</v>
+      </c>
+      <c r="F370" t="s">
+        <v>66</v>
+      </c>
+      <c r="G370">
+        <v>235</v>
+      </c>
+      <c r="H370" t="s">
+        <v>22</v>
+      </c>
+      <c r="I370">
+        <v>1</v>
+      </c>
+      <c r="J370" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E94C96CF-6654-44E6-95F8-580149457726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDDF3CF-14E0-486E-B720-9721A08CF5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{98E6D49B-EE02-4CDB-BA85-B928B2BDE159}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{12AFEA7A-9193-4FAA-8F9D-176CAE76690A}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4426" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4582" uniqueCount="591">
   <si>
     <t>날짜</t>
   </si>
@@ -546,12 +546,18 @@
     <t>2개월판매</t>
   </si>
   <si>
+    <t>이미지url</t>
+  </si>
+  <si>
     <t>BJM946BK 바오지 남성 데일리화 블랙 260</t>
   </si>
   <si>
     <t>정상</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/ed60ec093ce86cf1be9ab7d6a21dccad.jpg</t>
+  </si>
+  <si>
     <t>BJM946BK 바오지 남성 데일리화 블랙 265</t>
   </si>
   <si>
@@ -567,6 +573,9 @@
     <t>BJM946NV 바오지 남성 데일리화 네이비 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/ccea15f086483595f221192f06cf1d08.jpg</t>
+  </si>
+  <si>
     <t>BJM946NV 바오지 남성 데일리화 네이비 265</t>
   </si>
   <si>
@@ -924,6 +933,9 @@
     <t>BJM898GNBK 바오지 남성 기능화 그린블랙 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260508/43ad30e6dfa6829e2e9197096e51ddbc.jpg</t>
+  </si>
+  <si>
     <t>BJM898GNBK 바오지 남성 기능화 그린블랙 265</t>
   </si>
   <si>
@@ -942,6 +954,9 @@
     <t>BJM931WHGN 바오지 남성 러닝화 화이트그린 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260508/202cd5f60e9b6aefbdcdb821150f0847.jpg</t>
+  </si>
+  <si>
     <t>BJM931WHGN 바오지 남성 러닝화 화이트그린 265</t>
   </si>
   <si>
@@ -969,6 +984,9 @@
     <t>BJM931BK 바오지 남성 러닝화 블랙 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260508/d591f0085a95e682f634c5a2e7c3181c.jpg</t>
+  </si>
+  <si>
     <t>BJM931-BK265</t>
   </si>
   <si>
@@ -996,6 +1014,9 @@
     <t>BJM931GYOR 바오지 남성 러닝화 그레이오렌지 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260508/84fef7d7356edf7395a30196bcb089fb.jpg</t>
+  </si>
+  <si>
     <t>BJM931-GYOR265</t>
   </si>
   <si>
@@ -1026,6 +1047,9 @@
     <t>DPM641APGY 바오지 남성 러닝화 살구그레이 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/97a7c69842b4c63abef188facb775e4f.jpg</t>
+  </si>
+  <si>
     <t>DPM641APGY 바오지 남성 러닝화 살구그레이 265</t>
   </si>
   <si>
@@ -1050,6 +1074,9 @@
     <t>DPM641WHOR 바오지 남성 러닝화 화이트오렌지 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/2fb441bfd755361bb19ba77de2bee0eb.jpg</t>
+  </si>
+  <si>
     <t>DPM641WHOR 바오지 남성 러닝화 화이트오렌지 265</t>
   </si>
   <si>
@@ -1077,6 +1104,9 @@
     <t>DPM644APCO 바오지 남성 러닝화 살구커피 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/1003a283213e42fbe9e16752fcc3c555.jpg</t>
+  </si>
+  <si>
     <t>DPM644APCO 바오지 남성 러닝화 살구커피 265</t>
   </si>
   <si>
@@ -1104,6 +1134,9 @@
     <t>DPM644BK 바오지 남성 러닝화 블랙 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/42d5aa739d3370e66e2d8d12d782c91f.jpg</t>
+  </si>
+  <si>
     <t>DPM644-BK265</t>
   </si>
   <si>
@@ -1128,6 +1161,9 @@
     <t>DPM644GY 바오지 남성 러닝화 그레이 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/1dfc43085ae67e133658c892b5be798c.jpg</t>
+  </si>
+  <si>
     <t>DPM644GY 바오지 남성 러닝화 그레이 265</t>
   </si>
   <si>
@@ -1149,6 +1185,9 @@
     <t>DPM647BK 바오지 남성 러닝화 블랙 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/29c3aba06cac20436d2a9481f20bbad1.jpg</t>
+  </si>
+  <si>
     <t>DPM647BK 바오지 남성 러닝화 블랙 265</t>
   </si>
   <si>
@@ -1164,6 +1203,9 @@
     <t>DPM647GY 바오지 남성 러닝화 그레이 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/5cf5621395426e457cc806b96bf53033.jpg</t>
+  </si>
+  <si>
     <t>DPM647GY 바오지 남성 러닝화 그레이 265</t>
   </si>
   <si>
@@ -1182,6 +1224,9 @@
     <t>DPM647WHGN 바오지 남성 러닝화 화이트그린 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/f8c179a789e8e0012ab7e17ef5146546.jpg</t>
+  </si>
+  <si>
     <t>DPM647WHGN 바오지 남성 러닝화 화이트그린 265</t>
   </si>
   <si>
@@ -1197,6 +1242,9 @@
     <t>BJW1090PK 바오지 여성 데일리화 핑크 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/0bdbdba1a835ef083473109fd9b5acba.jpg</t>
+  </si>
+  <si>
     <t>BJW1090PK 바오지 여성 데일리화 핑크 240</t>
   </si>
   <si>
@@ -1212,6 +1260,9 @@
     <t>BJW1090WH 바오지 여성 데일리화 화이트 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/2b72ca06ab6cf20c097ea9cfeb1af19e.jpg</t>
+  </si>
+  <si>
     <t>BJW1090WH 바오지 여성 데일리화 화이트 240</t>
   </si>
   <si>
@@ -1227,6 +1278,9 @@
     <t>BJW1179BKSL 바오지 여성 데일리화 블랙실버 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/620fa2b989fb7b735c6460f8db0f7193.jpg</t>
+  </si>
+  <si>
     <t>BJW1179-BKSL240</t>
   </si>
   <si>
@@ -1251,6 +1305,9 @@
     <t>BJW1179GDWH 바오지 여성 데일리화 골드화이트 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/7d0830bae29f3498109786ad117520e8.jpg</t>
+  </si>
+  <si>
     <t>BJW1179-GDWH240</t>
   </si>
   <si>
@@ -1281,6 +1338,9 @@
     <t>BJW1179GY 바오지 여성 데일리화 그레이 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/12a6c4024daa1596ee483d4862903d60.jpg</t>
+  </si>
+  <si>
     <t>BJW1179GY 바오지 여성 데일리화 그레이 240</t>
   </si>
   <si>
@@ -1422,6 +1482,9 @@
     <t>BJW1170APPU 바오지 여성 러닝화 살구퍼플 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/ded5fe5f89146731f189af9a78a1c34f.jpg</t>
+  </si>
+  <si>
     <t>BJW1170APPU 바오지 여성 러닝화 살구퍼플 240</t>
   </si>
   <si>
@@ -1440,6 +1503,9 @@
     <t>BJW1170BKSL 바오지 여성 러닝화 블랙실버 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/6947c2358efbd9544338290c72785d21.jpg</t>
+  </si>
+  <si>
     <t>BJW1170BKSL 바오지 여성 러닝화 블랙실버 240</t>
   </si>
   <si>
@@ -1461,6 +1527,9 @@
     <t>BJW1170SLAP 바오지 여성 러닝화 실버살구 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/a9e2643d92235d24aa5d0935b68b8ce3.jpg</t>
+  </si>
+  <si>
     <t>BJW1170SLAP 바오지 여성 러닝화 실버살구 240</t>
   </si>
   <si>
@@ -1479,6 +1548,9 @@
     <t>DPW770AP 바오지 여성 러닝화 살구색 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/ff3edade5789b88dba27e58f0944169f.jpg</t>
+  </si>
+  <si>
     <t>DPW770AP 바오지 여성 러닝화 살구색 240</t>
   </si>
   <si>
@@ -1497,6 +1569,9 @@
     <t>DPW770BK 바오지 여성 러닝화 블랙 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/2bbe2bf75567d644f2750688699c32c8.jpg</t>
+  </si>
+  <si>
     <t>DPW770BK 바오지 여성 러닝화 블랙 240</t>
   </si>
   <si>
@@ -1515,6 +1590,9 @@
     <t>DPW770PK 바오지 여성 러닝화 핑크 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/4a9e9eefa715a7f595a6e88108550bd0.jpg</t>
+  </si>
+  <si>
     <t>DPW770PK 바오지 여성 러닝화 핑크 240</t>
   </si>
   <si>
@@ -1536,6 +1614,9 @@
     <t>DPW771AP 바오지 여성 러닝화 살구색 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/dc33a9225d366e06d103fce2d7323dfb.jpg</t>
+  </si>
+  <si>
     <t>DPW771AP 바오지 여성 러닝화 살구색 240</t>
   </si>
   <si>
@@ -1560,6 +1641,9 @@
     <t>DPW771BK 바오지 여성 러닝화 블랙 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/fc7ca9ac124b00497e04f2f57b93b418.jpg</t>
+  </si>
+  <si>
     <t>DPW771-BK240</t>
   </si>
   <si>
@@ -1590,6 +1674,9 @@
     <t>DPW771LBL 바오지 여성 러닝화 연블루 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/9e874b053bcd998829e1022dcc741b05.jpg</t>
+  </si>
+  <si>
     <t>DPW771-LBL240</t>
   </si>
   <si>
@@ -1611,6 +1698,9 @@
     <t>ECW304BK 바오지 여성 러닝화 블랙 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/f14b3d8b9788081c9a2818d0240e9afd.jpg</t>
+  </si>
+  <si>
     <t>ECW304BK 바오지 여성 러닝화 블랙 240</t>
   </si>
   <si>
@@ -1629,6 +1719,9 @@
     <t>ECW304WHLB 바오지 여성 러닝화 화이트연블루 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/7b1a3261a7072d73059e3bd136f32308.jpg</t>
+  </si>
+  <si>
     <t>ECW304WHLB 바오지 여성 러닝화 화이트연블루 240</t>
   </si>
   <si>
@@ -1642,6 +1735,9 @@
   </si>
   <si>
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 235</t>
+  </si>
+  <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/4cd2c11a8558ddc90574b8e9d521c30b.jpg</t>
   </si>
   <si>
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 240</t>
@@ -2102,11 +2198,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD41C6CD-871D-402E-AA22-2A35F4C0742F}">
-  <dimension ref="A1:P259"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4398BF1-60F4-4B49-9A29-50C600291E97}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:Q259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="17" max="17" width="134.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2155,13 +2255,16 @@
       <c r="P1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2188,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2205,13 +2308,16 @@
       <c r="P2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2238,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -2255,13 +2361,16 @@
       <c r="P3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2288,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2305,13 +2414,16 @@
       <c r="P4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2338,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2355,13 +2467,16 @@
       <c r="P5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2388,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2405,13 +2520,16 @@
       <c r="P6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2438,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2455,13 +2573,16 @@
       <c r="P7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2488,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2505,13 +2626,16 @@
       <c r="P8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2538,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2555,13 +2679,16 @@
       <c r="P9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2588,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2605,13 +2732,16 @@
       <c r="P10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2638,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2655,19 +2785,22 @@
       <c r="P11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2688,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2705,19 +2838,22 @@
       <c r="P12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" t="s">
         <v>184</v>
       </c>
-      <c r="C13" t="s">
-        <v>181</v>
-      </c>
       <c r="D13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -2738,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2755,19 +2891,22 @@
       <c r="P13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" t="s">
         <v>185</v>
-      </c>
-      <c r="B14" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" t="s">
-        <v>182</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2788,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2805,19 +2944,22 @@
       <c r="P14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -2838,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2855,19 +2997,22 @@
       <c r="P15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -2888,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2905,19 +3050,22 @@
       <c r="P16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -2938,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2955,19 +3103,22 @@
       <c r="P17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -2988,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3005,19 +3156,22 @@
       <c r="P18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3038,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3055,19 +3209,22 @@
       <c r="P19" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C20" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D20" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3088,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3105,19 +3262,22 @@
       <c r="P20" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D21" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3138,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3155,19 +3315,22 @@
       <c r="P21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C22" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3188,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3205,19 +3368,22 @@
       <c r="P22" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C23" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3238,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3255,19 +3421,22 @@
       <c r="P23" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C24" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3288,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3305,19 +3474,22 @@
       <c r="P24" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B25" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C25" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3338,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3355,19 +3527,22 @@
       <c r="P25" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D26" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3388,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3405,19 +3580,22 @@
       <c r="P26" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D27" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3438,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3455,19 +3633,22 @@
       <c r="P27" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C28" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3488,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3505,19 +3686,22 @@
       <c r="P28" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B29" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3538,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3555,19 +3739,22 @@
       <c r="P29" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C30" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D30" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3588,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3605,19 +3792,22 @@
       <c r="P30" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C31" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3638,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3655,19 +3845,22 @@
       <c r="P31" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C32" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3688,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3705,19 +3898,22 @@
       <c r="P32" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D33" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3738,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3755,19 +3951,22 @@
       <c r="P33" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" t="s">
+        <v>230</v>
+      </c>
+      <c r="C34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" t="s">
         <v>226</v>
-      </c>
-      <c r="B34" t="s">
-        <v>227</v>
-      </c>
-      <c r="C34" t="s">
-        <v>181</v>
-      </c>
-      <c r="D34" t="s">
-        <v>223</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3788,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3805,19 +4004,22 @@
       <c r="P34" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B35" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C35" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3838,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3855,19 +4057,22 @@
       <c r="P35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B36" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D36" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -3888,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3905,19 +4110,22 @@
       <c r="P36" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B37" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D37" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3938,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3955,19 +4163,22 @@
       <c r="P37" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D38" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -3988,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4005,19 +4216,22 @@
       <c r="P38" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C39" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D39" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4038,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4055,19 +4269,22 @@
       <c r="P39" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B40" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C40" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D40" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4088,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4105,19 +4322,22 @@
       <c r="P40" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B41" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C41" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D41" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4138,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4155,19 +4375,22 @@
       <c r="P41" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B42" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C42" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D42" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4188,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4205,19 +4428,22 @@
       <c r="P42" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C43" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D43" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4238,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4255,19 +4481,22 @@
       <c r="P43" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B44" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C44" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4288,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4305,19 +4534,22 @@
       <c r="P44" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C45" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D45" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4338,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4355,19 +4587,22 @@
       <c r="P45" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B46" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C46" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4388,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4405,19 +4640,22 @@
       <c r="P46" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B47" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C47" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D47" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4438,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4455,19 +4693,22 @@
       <c r="P47" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B48" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C48" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D48" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4488,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4505,19 +4746,22 @@
       <c r="P48" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B49" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D49" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4538,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4555,19 +4799,22 @@
       <c r="P49" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C50" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D50" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4588,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4605,19 +4852,22 @@
       <c r="P50" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B51" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C51" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D51" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4638,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4655,19 +4905,22 @@
       <c r="P51" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B52" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C52" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D52" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4688,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4705,19 +4958,22 @@
       <c r="P52" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B53" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D53" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4738,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4755,19 +5011,22 @@
       <c r="P53" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>270</v>
+      </c>
+      <c r="B54" t="s">
+        <v>271</v>
+      </c>
+      <c r="C54" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" t="s">
         <v>267</v>
-      </c>
-      <c r="B54" t="s">
-        <v>268</v>
-      </c>
-      <c r="C54" t="s">
-        <v>181</v>
-      </c>
-      <c r="D54" t="s">
-        <v>264</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4788,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -4805,19 +5064,22 @@
       <c r="P54" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B55" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C55" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D55" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4838,7 +5100,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -4855,19 +5117,22 @@
       <c r="P55" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B56" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C56" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4888,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -4905,19 +5170,22 @@
       <c r="P56" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B57" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C57" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D57" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4938,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -4955,19 +5223,22 @@
       <c r="P57" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B58" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C58" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4988,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5005,19 +5276,22 @@
       <c r="P58" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B59" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C59" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D59" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5038,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5055,19 +5329,22 @@
       <c r="P59" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B60" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C60" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D60" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5088,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5105,19 +5382,22 @@
       <c r="P60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B61" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C61" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5138,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5155,19 +5435,22 @@
       <c r="P61" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B62" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D62" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5188,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -5205,19 +5488,22 @@
       <c r="P62" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B63" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C63" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5238,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -5255,19 +5541,22 @@
       <c r="P63" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B64" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C64" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D64" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5288,7 +5577,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -5305,19 +5594,22 @@
       <c r="P64" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B65" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C65" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D65" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5338,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5355,19 +5647,22 @@
       <c r="P65" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B66" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C66" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5388,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -5405,13 +5700,16 @@
       <c r="P66" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -5438,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -5455,13 +5753,16 @@
       <c r="P67" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q67" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -5488,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -5505,13 +5806,16 @@
       <c r="P68" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q68" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -5538,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L69">
         <v>4</v>
@@ -5555,13 +5859,16 @@
       <c r="P69" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q69" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -5588,7 +5895,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -5605,13 +5912,16 @@
       <c r="P70" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q70" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -5638,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -5655,13 +5965,16 @@
       <c r="P71" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q71" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B72" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -5688,7 +6001,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -5705,13 +6018,16 @@
       <c r="P72" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q72" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -5738,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -5755,13 +6071,16 @@
       <c r="P73" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q73" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B74" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -5788,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -5805,13 +6124,16 @@
       <c r="P74" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q74" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B75" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -5838,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -5855,13 +6177,16 @@
       <c r="P75" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q75" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B76" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -5888,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -5905,13 +6230,16 @@
       <c r="P76" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q76" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B77" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -5938,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -5955,13 +6283,16 @@
       <c r="P77" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q77" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B78" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -5988,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -6005,13 +6336,16 @@
       <c r="P78" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q78" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B79" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -6038,7 +6372,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -6055,13 +6389,16 @@
       <c r="P79" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q79" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -6088,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -6105,13 +6442,16 @@
       <c r="P80" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q80" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B81" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -6138,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -6155,13 +6495,16 @@
       <c r="P81" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q81" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B82" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -6188,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6205,13 +6548,16 @@
       <c r="P82" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q82" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B83" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -6238,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -6255,13 +6601,16 @@
       <c r="P83" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q83" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B84" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -6288,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -6305,13 +6654,16 @@
       <c r="P84" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q84" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B85" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -6338,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -6355,13 +6707,16 @@
       <c r="P85" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q85" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B86" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -6388,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -6405,13 +6760,16 @@
       <c r="P86" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q86" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B87" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -6438,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -6455,13 +6813,16 @@
       <c r="P87" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q87" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -6488,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -6505,13 +6866,16 @@
       <c r="P88" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q88" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B89" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -6538,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -6555,13 +6919,16 @@
       <c r="P89" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q89" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -6588,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -6605,13 +6972,16 @@
       <c r="P90" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q90" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B91" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -6638,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -6655,13 +7025,16 @@
       <c r="P91" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q91" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B92" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -6688,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -6705,13 +7078,16 @@
       <c r="P92" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q92" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -6738,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -6755,13 +7131,16 @@
       <c r="P93" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q93" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B94" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -6788,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -6805,13 +7184,16 @@
       <c r="P94" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q94" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B95" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -6838,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -6855,13 +7237,16 @@
       <c r="P95" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q95" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B96" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -6888,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6905,13 +7290,16 @@
       <c r="P96" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q96" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B97" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -6938,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6955,13 +7343,16 @@
       <c r="P97" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q97" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -6988,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L98">
         <v>1</v>
@@ -7005,13 +7396,16 @@
       <c r="P98" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q98" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B99" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -7038,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -7055,13 +7449,16 @@
       <c r="P99" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q99" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B100" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -7088,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -7105,13 +7502,16 @@
       <c r="P100" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q100" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="B101" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -7138,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -7155,13 +7555,16 @@
       <c r="P101" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q101" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B102" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -7188,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7205,13 +7608,16 @@
       <c r="P102" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q102" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B103" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -7238,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -7255,13 +7661,16 @@
       <c r="P103" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q103" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -7288,7 +7697,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L104">
         <v>4</v>
@@ -7305,13 +7714,16 @@
       <c r="P104" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q104" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B105" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -7338,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -7355,13 +7767,16 @@
       <c r="P105" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q105" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -7388,7 +7803,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -7405,13 +7820,16 @@
       <c r="P106" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q106" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B107" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -7438,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -7455,13 +7873,16 @@
       <c r="P107" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q107" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -7488,7 +7909,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -7505,13 +7926,16 @@
       <c r="P108" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q108" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -7538,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -7555,13 +7979,16 @@
       <c r="P109" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q109" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B110" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -7588,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -7605,13 +8032,16 @@
       <c r="P110" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q110" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B111" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -7638,7 +8068,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -7655,13 +8085,16 @@
       <c r="P111" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q111" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -7688,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L112">
         <v>3</v>
@@ -7705,13 +8138,16 @@
       <c r="P112" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q112" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -7738,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L113">
         <v>5</v>
@@ -7755,13 +8191,16 @@
       <c r="P113" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q113" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -7788,7 +8227,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L114">
         <v>4</v>
@@ -7805,13 +8244,16 @@
       <c r="P114" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q114" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -7838,7 +8280,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L115">
         <v>2</v>
@@ -7855,13 +8297,16 @@
       <c r="P115" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q115" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -7888,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L116">
         <v>2</v>
@@ -7905,13 +8350,16 @@
       <c r="P116" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q116" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -7938,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -7955,13 +8403,16 @@
       <c r="P117" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q117" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -7988,7 +8439,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -8005,13 +8456,16 @@
       <c r="P118" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q118" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B119" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -8038,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -8055,13 +8509,16 @@
       <c r="P119" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q119" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -8088,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -8105,13 +8562,16 @@
       <c r="P120" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q120" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -8138,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -8155,13 +8615,16 @@
       <c r="P121" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q121" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -8188,7 +8651,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L122">
         <v>4</v>
@@ -8205,13 +8668,16 @@
       <c r="P122" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q122" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -8238,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -8255,13 +8721,16 @@
       <c r="P123" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q123" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -8288,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -8305,13 +8774,16 @@
       <c r="P124" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q124" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -8338,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -8355,13 +8827,16 @@
       <c r="P125" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q125" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -8405,13 +8880,16 @@
       <c r="P126" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q126" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -8455,13 +8933,16 @@
       <c r="P127" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q127" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -8505,13 +8986,16 @@
       <c r="P128" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q128" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -8538,7 +9022,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L129">
         <v>6</v>
@@ -8555,13 +9039,16 @@
       <c r="P129" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q129" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -8588,7 +9075,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L130">
         <v>6</v>
@@ -8605,13 +9092,16 @@
       <c r="P130" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q130" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -8638,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -8655,13 +9145,16 @@
       <c r="P131" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q131" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -8688,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L132">
         <v>17</v>
@@ -8705,13 +9198,16 @@
       <c r="P132" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q132" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -8738,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L133">
         <v>7</v>
@@ -8755,13 +9251,16 @@
       <c r="P133" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q133" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -8788,7 +9287,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L134">
         <v>9</v>
@@ -8805,13 +9304,16 @@
       <c r="P134" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q134" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -8838,7 +9340,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L135">
         <v>4</v>
@@ -8855,13 +9357,16 @@
       <c r="P135" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q135" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -8888,7 +9393,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L136">
         <v>3</v>
@@ -8905,13 +9410,16 @@
       <c r="P136" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q136" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -8938,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L137">
         <v>1</v>
@@ -8955,13 +9463,16 @@
       <c r="P137" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q137" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="B138" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -8988,7 +9499,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -9005,13 +9516,16 @@
       <c r="P138" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q138" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B139" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -9038,7 +9552,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L139">
         <v>0</v>
@@ -9055,13 +9569,16 @@
       <c r="P139" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q139" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -9088,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L140">
         <v>1</v>
@@ -9105,13 +9622,16 @@
       <c r="P140" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q140" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="B141" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -9138,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L141">
         <v>0</v>
@@ -9155,13 +9675,16 @@
       <c r="P141" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q141" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -9188,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -9205,13 +9728,16 @@
       <c r="P142" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q142" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="B143" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -9238,7 +9764,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -9255,13 +9781,16 @@
       <c r="P143" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q143" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="B144" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -9288,7 +9817,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -9305,13 +9834,16 @@
       <c r="P144" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q144" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="B145" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -9338,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -9355,13 +9887,16 @@
       <c r="P145" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q145" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="B146" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -9388,7 +9923,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -9405,13 +9940,16 @@
       <c r="P146" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q146" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="B147" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -9438,7 +9976,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L147">
         <v>0</v>
@@ -9455,13 +9993,16 @@
       <c r="P147" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q147" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -9488,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L148">
         <v>2</v>
@@ -9505,13 +10046,16 @@
       <c r="P148" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q148" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="B149" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -9538,7 +10082,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -9555,13 +10099,16 @@
       <c r="P149" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q149" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -9588,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -9605,13 +10152,16 @@
       <c r="P150" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q150" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -9638,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -9655,19 +10205,22 @@
       <c r="P151" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q151" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="B152" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C152" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -9688,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -9705,19 +10258,22 @@
       <c r="P152" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="B153" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="C153" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -9738,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -9755,19 +10311,22 @@
       <c r="P153" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="B154" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="C154" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D154" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -9788,7 +10347,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -9805,19 +10364,22 @@
       <c r="P154" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="B155" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="C155" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D155" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -9838,7 +10400,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -9855,19 +10417,22 @@
       <c r="P155" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="B156" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="C156" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -9888,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -9905,19 +10470,22 @@
       <c r="P156" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="B157" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="C157" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -9938,7 +10506,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -9955,19 +10523,22 @@
       <c r="P157" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="B158" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="C158" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -9988,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -10005,19 +10576,22 @@
       <c r="P158" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="B159" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="C159" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -10038,7 +10612,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -10055,19 +10629,22 @@
       <c r="P159" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="B160" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="C160" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D160" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -10088,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -10105,19 +10682,22 @@
       <c r="P160" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B161" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="C161" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D161" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -10138,7 +10718,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -10155,19 +10735,22 @@
       <c r="P161" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="B162" t="s">
+        <v>460</v>
+      </c>
+      <c r="C162" t="s">
+        <v>184</v>
+      </c>
+      <c r="D162" t="s">
         <v>440</v>
-      </c>
-      <c r="C162" t="s">
-        <v>181</v>
-      </c>
-      <c r="D162" t="s">
-        <v>420</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -10188,7 +10771,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -10205,19 +10788,22 @@
       <c r="P162" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="B163" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="C163" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D163" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -10238,7 +10824,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -10255,19 +10841,22 @@
       <c r="P163" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="B164" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="C164" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D164" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -10288,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -10305,19 +10894,22 @@
       <c r="P164" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B165" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="C165" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D165" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -10338,7 +10930,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -10355,19 +10947,22 @@
       <c r="P165" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="B166" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="C166" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D166" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -10388,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -10405,19 +11000,22 @@
       <c r="P166" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="B167" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="C167" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D167" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -10438,7 +11036,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -10455,19 +11053,22 @@
       <c r="P167" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="B168" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="C168" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D168" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -10488,7 +11089,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -10505,19 +11106,22 @@
       <c r="P168" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B169" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="C169" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D169" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -10538,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -10555,19 +11159,22 @@
       <c r="P169" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="B170" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="C170" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D170" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -10588,7 +11195,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -10605,19 +11212,22 @@
       <c r="P170" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="B171" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="C171" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D171" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -10638,7 +11248,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -10655,13 +11265,16 @@
       <c r="P171" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -10688,7 +11301,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L172">
         <v>4</v>
@@ -10705,13 +11318,16 @@
       <c r="P172" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q172" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -10738,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L173">
         <v>3</v>
@@ -10747,7 +11363,7 @@
         <v>0</v>
       </c>
       <c r="N173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O173">
         <v>2</v>
@@ -10755,13 +11371,16 @@
       <c r="P173" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q173" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -10788,7 +11407,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L174">
         <v>3</v>
@@ -10805,13 +11424,16 @@
       <c r="P174" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q174" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="B175" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -10838,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L175">
         <v>0</v>
@@ -10855,13 +11477,16 @@
       <c r="P175" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q175" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -10888,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -10897,7 +11522,7 @@
         <v>0</v>
       </c>
       <c r="N176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O176">
         <v>3</v>
@@ -10905,13 +11530,16 @@
       <c r="P176" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q176" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -10938,7 +11566,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -10955,13 +11583,16 @@
       <c r="P177" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q177" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -10988,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L178">
         <v>1</v>
@@ -11005,13 +11636,16 @@
       <c r="P178" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q178" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="B179" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -11038,7 +11672,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -11055,13 +11689,16 @@
       <c r="P179" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q179" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -11088,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -11105,13 +11742,16 @@
       <c r="P180" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q180" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="B181" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -11138,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -11155,13 +11795,16 @@
       <c r="P181" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q181" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -11188,7 +11831,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L182">
         <v>3</v>
@@ -11197,7 +11840,7 @@
         <v>1</v>
       </c>
       <c r="N182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O182">
         <v>2</v>
@@ -11205,13 +11848,16 @@
       <c r="P182" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q182" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -11238,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L183">
         <v>4</v>
@@ -11255,13 +11901,16 @@
       <c r="P183" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q183" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -11288,7 +11937,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -11305,13 +11954,16 @@
       <c r="P184" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q184" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -11338,7 +11990,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L185">
         <v>3</v>
@@ -11355,13 +12007,16 @@
       <c r="P185" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q185" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="B186" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -11388,7 +12043,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L186">
         <v>0</v>
@@ -11405,13 +12060,16 @@
       <c r="P186" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q186" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -11455,13 +12113,16 @@
       <c r="P187" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q187" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -11488,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -11505,13 +12166,16 @@
       <c r="P188" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q188" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -11538,7 +12202,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L189">
         <v>7</v>
@@ -11555,13 +12219,16 @@
       <c r="P189" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q189" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -11588,7 +12255,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L190">
         <v>7</v>
@@ -11605,13 +12272,16 @@
       <c r="P190" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q190" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="B191" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -11638,7 +12308,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -11655,13 +12325,16 @@
       <c r="P191" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q191" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -11705,13 +12378,16 @@
       <c r="P192" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q192" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -11738,7 +12414,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L193">
         <v>20</v>
@@ -11755,13 +12431,16 @@
       <c r="P193" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q193" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -11788,7 +12467,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L194">
         <v>20</v>
@@ -11805,13 +12484,16 @@
       <c r="P194" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q194" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -11838,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -11855,13 +12537,16 @@
       <c r="P195" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q195" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -11888,7 +12573,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L196">
         <v>7</v>
@@ -11905,13 +12590,16 @@
       <c r="P196" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q196" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="B197" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -11938,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -11955,13 +12643,16 @@
       <c r="P197" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q197" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -12005,13 +12696,16 @@
       <c r="P198" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q198" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -12038,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -12055,13 +12749,16 @@
       <c r="P199" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q199" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="B200" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -12088,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -12105,13 +12802,16 @@
       <c r="P200" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q200" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -12138,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -12155,13 +12855,16 @@
       <c r="P201" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q201" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="B202" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -12188,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -12205,13 +12908,16 @@
       <c r="P202" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q202" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -12238,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L203">
         <v>1</v>
@@ -12255,13 +12961,16 @@
       <c r="P203" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q203" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="B204" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -12288,7 +12997,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -12305,13 +13014,16 @@
       <c r="P204" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q204" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>501</v>
+        <v>528</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -12338,7 +13050,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -12355,13 +13067,16 @@
       <c r="P205" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q205" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="B206" t="s">
-        <v>503</v>
+        <v>530</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -12388,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -12405,13 +13120,16 @@
       <c r="P206" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q206" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>504</v>
+        <v>531</v>
       </c>
       <c r="B207" t="s">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -12438,7 +13156,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -12455,13 +13173,16 @@
       <c r="P207" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q207" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="B208" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -12488,7 +13209,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -12505,13 +13226,16 @@
       <c r="P208" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q208" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>508</v>
+        <v>536</v>
       </c>
       <c r="B209" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -12538,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -12555,13 +13279,16 @@
       <c r="P209" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q209" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="B210" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -12588,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -12605,13 +13332,16 @@
       <c r="P210" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q210" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="B211" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -12638,7 +13368,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -12655,13 +13385,16 @@
       <c r="P211" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q211" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="B212" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -12688,7 +13421,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -12705,13 +13438,16 @@
       <c r="P212" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q212" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>516</v>
+        <v>545</v>
       </c>
       <c r="B213" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -12738,7 +13474,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -12755,13 +13491,16 @@
       <c r="P213" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q213" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -12788,7 +13527,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -12805,13 +13544,16 @@
       <c r="P214" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q214" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>519</v>
+        <v>548</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -12838,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -12855,13 +13597,16 @@
       <c r="P215" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q215" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="B216" t="s">
-        <v>521</v>
+        <v>550</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -12888,7 +13633,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -12905,13 +13650,16 @@
       <c r="P216" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q216" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -12938,7 +13686,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L217">
         <v>6</v>
@@ -12955,13 +13703,16 @@
       <c r="P217" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q217" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -12988,7 +13739,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L218">
         <v>3</v>
@@ -13005,13 +13756,16 @@
       <c r="P218" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q218" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -13038,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L219">
         <v>3</v>
@@ -13055,13 +13809,16 @@
       <c r="P219" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q219" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -13088,7 +13845,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L220">
         <v>2</v>
@@ -13105,13 +13862,16 @@
       <c r="P220" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q220" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B221" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -13138,7 +13898,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -13155,13 +13915,16 @@
       <c r="P221" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q221" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -13205,13 +13968,16 @@
       <c r="P222" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q222" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -13238,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L223">
         <v>10</v>
@@ -13255,13 +14021,16 @@
       <c r="P223" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q223" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -13288,7 +14057,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L224">
         <v>10</v>
@@ -13305,13 +14074,16 @@
       <c r="P224" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q224" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -13338,7 +14110,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L225">
         <v>6</v>
@@ -13355,13 +14127,16 @@
       <c r="P225" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q225" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -13388,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L226">
         <v>2</v>
@@ -13405,13 +14180,16 @@
       <c r="P226" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q226" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -13438,7 +14216,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L227">
         <v>7</v>
@@ -13455,13 +14233,16 @@
       <c r="P227" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q227" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -13488,7 +14269,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L228">
         <v>10</v>
@@ -13497,7 +14278,7 @@
         <v>8</v>
       </c>
       <c r="N228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O228">
         <v>10</v>
@@ -13505,13 +14286,16 @@
       <c r="P228" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q228" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -13538,7 +14322,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L229">
         <v>10</v>
@@ -13555,13 +14339,16 @@
       <c r="P229" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q229" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -13588,7 +14375,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -13605,13 +14392,16 @@
       <c r="P230" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q230" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>537</v>
+        <v>569</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -13638,7 +14428,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -13655,8 +14445,11 @@
       <c r="P231" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q231" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>125</v>
       </c>
@@ -13685,7 +14478,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -13694,7 +14487,7 @@
         <v>0</v>
       </c>
       <c r="N232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O232">
         <v>2</v>
@@ -13703,12 +14496,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="B233" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="C233" t="s">
         <v>120</v>
@@ -13732,7 +14525,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -13750,12 +14543,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="B234" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -13779,7 +14572,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -13797,12 +14590,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="B235" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="C235" t="s">
         <v>120</v>
@@ -13826,7 +14619,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -13844,12 +14637,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="B236" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="C236" t="s">
         <v>120</v>
@@ -13873,7 +14666,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -13891,7 +14684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>127</v>
       </c>
@@ -13920,7 +14713,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -13929,7 +14722,7 @@
         <v>0</v>
       </c>
       <c r="N237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O237">
         <v>1</v>
@@ -13938,12 +14731,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="B238" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -13967,7 +14760,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -13985,12 +14778,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="B239" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -14014,7 +14807,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -14032,12 +14825,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>544</v>
+        <v>576</v>
       </c>
       <c r="B240" t="s">
-        <v>544</v>
+        <v>576</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -14061,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -14108,7 +14901,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -14128,10 +14921,10 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="B242" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -14155,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -14175,10 +14968,10 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="B243" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -14202,7 +14995,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -14222,10 +15015,10 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="B244" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -14249,7 +15042,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -14296,7 +15089,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L245">
         <v>1</v>
@@ -14305,7 +15098,7 @@
         <v>0</v>
       </c>
       <c r="N245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O245">
         <v>1</v>
@@ -14316,10 +15109,10 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>548</v>
+        <v>580</v>
       </c>
       <c r="B246" t="s">
-        <v>548</v>
+        <v>580</v>
       </c>
       <c r="C246" t="s">
         <v>120</v>
@@ -14343,7 +15136,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L246">
         <v>0</v>
@@ -14363,10 +15156,10 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="B247" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="C247" t="s">
         <v>120</v>
@@ -14390,7 +15183,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -14410,16 +15203,16 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="B248" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
       </c>
       <c r="D248" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="E248" t="s">
         <v>122</v>
@@ -14437,7 +15230,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -14457,16 +15250,16 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="B249" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="C249" t="s">
         <v>120</v>
       </c>
       <c r="D249" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="E249" t="s">
         <v>122</v>
@@ -14484,7 +15277,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -14504,16 +15297,16 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="B250" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
       </c>
       <c r="D250" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="E250" t="s">
         <v>122</v>
@@ -14531,7 +15324,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -14551,16 +15344,16 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="B251" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
       </c>
       <c r="D251" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="E251" t="s">
         <v>122</v>
@@ -14578,7 +15371,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -14598,10 +15391,10 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="B252" t="s">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="C252" t="s">
         <v>120</v>
@@ -14625,7 +15418,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -14645,10 +15438,10 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>556</v>
+        <v>588</v>
       </c>
       <c r="B253" t="s">
-        <v>556</v>
+        <v>588</v>
       </c>
       <c r="C253" t="s">
         <v>120</v>
@@ -14672,7 +15465,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L253">
         <v>0</v>
@@ -14719,7 +15512,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -14728,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="N254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O254">
         <v>1</v>
@@ -14766,7 +15559,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -14813,7 +15606,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L256">
         <v>2</v>
@@ -14833,10 +15626,10 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="B257" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -14860,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -14907,7 +15700,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L258">
         <v>2</v>
@@ -14927,10 +15720,10 @@
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>558</v>
+        <v>590</v>
       </c>
       <c r="B259" t="s">
-        <v>558</v>
+        <v>590</v>
       </c>
       <c r="C259" t="s">
         <v>120</v>
@@ -14954,7 +15747,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -14979,7 +15772,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0DD2333-F3DA-49E3-97AF-6F00E0028080}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A63A091A-E04E-4136-B4E3-F0066E8C3605}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J370"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDDF3CF-14E0-486E-B720-9721A08CF5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55983B4B-25C7-416E-A409-7E89EA333857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{12AFEA7A-9193-4FAA-8F9D-176CAE76690A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{DEE7CD9E-3F62-4AAF-919E-F0D0541F7FC9}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4582" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4653" uniqueCount="592">
   <si>
     <t>날짜</t>
   </si>
@@ -516,6 +516,12 @@
     <t>BJW1170-SLAP245</t>
   </si>
   <si>
+    <t>DPM644-APCO270</t>
+  </si>
+  <si>
+    <t>BJW1179-GY245</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -549,6 +555,9 @@
     <t>이미지url</t>
   </si>
   <si>
+    <t>발주수량</t>
+  </si>
+  <si>
     <t>BJM946BK 바오지 남성 데일리화 블랙 260</t>
   </si>
   <si>
@@ -1110,9 +1119,6 @@
     <t>DPM644APCO 바오지 남성 러닝화 살구커피 265</t>
   </si>
   <si>
-    <t>DPM644-APCO270</t>
-  </si>
-  <si>
     <t>DPM644APCO 바오지 남성 러닝화 살구커피 270</t>
   </si>
   <si>
@@ -1342,9 +1348,6 @@
   </si>
   <si>
     <t>BJW1179GY 바오지 여성 데일리화 그레이 240</t>
-  </si>
-  <si>
-    <t>BJW1179-GY245</t>
   </si>
   <si>
     <t>BJW1179GY 바오지 여성 데일리화 그레이 245</t>
@@ -2198,20 +2201,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4398BF1-60F4-4B49-9A29-50C600291E97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDBC09BF-1F3D-4C30-97DB-7F255DE800CA}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:Q259"/>
+  <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="17" max="17" width="134.875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2226,45 +2226,48 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="R1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2291,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2309,15 +2312,18 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2344,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -2362,15 +2368,18 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2397,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2415,15 +2424,18 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2450,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2468,15 +2480,18 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2503,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2521,15 +2536,18 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2556,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2574,15 +2592,18 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2609,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2627,15 +2648,18 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2662,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2680,15 +2704,18 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2715,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2733,15 +2760,18 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2768,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2786,21 +2816,24 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2821,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2841,19 +2874,22 @@
       <c r="Q12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" t="s">
         <v>187</v>
       </c>
-      <c r="C13" t="s">
-        <v>184</v>
-      </c>
       <c r="D13" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -2874,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2894,19 +2930,22 @@
       <c r="Q13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" t="s">
         <v>188</v>
-      </c>
-      <c r="B14" t="s">
-        <v>189</v>
-      </c>
-      <c r="C14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" t="s">
-        <v>185</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2927,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2947,19 +2986,22 @@
       <c r="Q14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -2980,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3000,19 +3042,22 @@
       <c r="Q15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3033,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3053,19 +3098,22 @@
       <c r="Q16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3086,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3106,19 +3154,22 @@
       <c r="Q17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3139,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3159,19 +3210,22 @@
       <c r="Q18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3192,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3212,19 +3266,22 @@
       <c r="Q19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3245,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3265,19 +3322,22 @@
       <c r="Q20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3298,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3318,19 +3378,22 @@
       <c r="Q21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C22" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3351,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3371,19 +3434,22 @@
       <c r="Q22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C23" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3404,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3424,19 +3490,22 @@
       <c r="Q23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3457,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3477,19 +3546,22 @@
       <c r="Q24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B25" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3510,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3530,19 +3602,22 @@
       <c r="Q25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B26" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3563,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3583,19 +3658,22 @@
       <c r="Q26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C27" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3616,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3636,19 +3714,22 @@
       <c r="Q27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3669,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3689,19 +3770,22 @@
       <c r="Q28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B29" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C29" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3722,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3742,19 +3826,22 @@
       <c r="Q29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B30" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3775,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3795,19 +3882,22 @@
       <c r="Q30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B31" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C31" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3828,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3848,19 +3938,22 @@
       <c r="Q31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B32" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C32" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D32" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3881,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3901,19 +3994,22 @@
       <c r="Q32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B33" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C33" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D33" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3934,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3954,19 +4050,22 @@
       <c r="Q33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>232</v>
+      </c>
+      <c r="B34" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" t="s">
         <v>229</v>
-      </c>
-      <c r="B34" t="s">
-        <v>230</v>
-      </c>
-      <c r="C34" t="s">
-        <v>184</v>
-      </c>
-      <c r="D34" t="s">
-        <v>226</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3987,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4007,19 +4106,22 @@
       <c r="Q34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B35" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C35" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D35" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4040,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4060,19 +4162,22 @@
       <c r="Q35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B36" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D36" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4093,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4113,19 +4218,22 @@
       <c r="Q36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B37" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C37" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4146,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4166,19 +4274,22 @@
       <c r="Q37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B38" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D38" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4199,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4219,19 +4330,22 @@
       <c r="Q38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B39" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C39" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D39" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4252,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4272,19 +4386,22 @@
       <c r="Q39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D40" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4305,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4325,19 +4442,22 @@
       <c r="Q40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B41" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D41" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4358,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4378,19 +4498,22 @@
       <c r="Q41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B42" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C42" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4411,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4431,19 +4554,22 @@
       <c r="Q42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B43" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D43" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4464,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4484,19 +4610,22 @@
       <c r="Q43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B44" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C44" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D44" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4517,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4537,19 +4666,22 @@
       <c r="Q44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B45" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C45" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4570,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4590,19 +4722,22 @@
       <c r="Q45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B46" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C46" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D46" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4623,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4643,19 +4778,22 @@
       <c r="Q46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C47" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D47" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4676,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4696,19 +4834,22 @@
       <c r="Q47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B48" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D48" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4729,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4749,19 +4890,22 @@
       <c r="Q48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B49" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C49" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4782,7 +4926,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4802,19 +4946,22 @@
       <c r="Q49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D50" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4835,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4855,19 +5002,22 @@
       <c r="Q50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B51" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C51" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4888,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4908,19 +5058,22 @@
       <c r="Q51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B52" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C52" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D52" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4941,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4961,19 +5114,22 @@
       <c r="Q52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B53" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D53" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4994,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5014,19 +5170,22 @@
       <c r="Q53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>273</v>
+      </c>
+      <c r="B54" t="s">
+        <v>274</v>
+      </c>
+      <c r="C54" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" t="s">
         <v>270</v>
-      </c>
-      <c r="B54" t="s">
-        <v>271</v>
-      </c>
-      <c r="C54" t="s">
-        <v>184</v>
-      </c>
-      <c r="D54" t="s">
-        <v>267</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5047,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5067,19 +5226,22 @@
       <c r="Q54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B55" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C55" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D55" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5100,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5120,19 +5282,22 @@
       <c r="Q55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B56" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C56" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D56" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5153,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5173,19 +5338,22 @@
       <c r="Q56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B57" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C57" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D57" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5206,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5226,19 +5394,22 @@
       <c r="Q57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B58" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D58" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5259,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5279,19 +5450,22 @@
       <c r="Q58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C59" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D59" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5312,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5332,19 +5506,22 @@
       <c r="Q59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B60" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C60" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D60" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5365,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5385,19 +5562,22 @@
       <c r="Q60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B61" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D61" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5418,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5438,19 +5618,22 @@
       <c r="Q61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B62" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C62" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D62" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5471,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -5491,19 +5674,22 @@
       <c r="Q62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B63" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C63" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D63" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5524,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -5544,19 +5730,22 @@
       <c r="Q63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B64" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C64" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D64" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5577,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -5597,19 +5786,22 @@
       <c r="Q64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B65" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D65" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5630,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5650,19 +5842,22 @@
       <c r="Q65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B66" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C66" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D66" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5683,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -5703,13 +5898,16 @@
       <c r="Q66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -5736,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -5754,15 +5952,18 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -5789,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -5807,15 +6008,18 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -5842,7 +6046,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L69">
         <v>4</v>
@@ -5860,15 +6064,18 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -5895,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -5913,15 +6120,18 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -5948,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -5966,15 +6176,18 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B72" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6001,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6019,15 +6232,18 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6054,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6072,15 +6288,18 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B74" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6107,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6125,15 +6344,18 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B75" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6160,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -6178,15 +6400,18 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B76" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6213,7 +6438,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6231,15 +6456,18 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B77" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -6266,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -6284,15 +6512,18 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B78" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -6319,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -6337,15 +6568,18 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -6372,7 +6606,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -6390,15 +6624,18 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -6425,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -6443,15 +6680,18 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B81" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -6478,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -6496,15 +6736,18 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B82" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -6531,7 +6774,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6549,15 +6792,18 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B83" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -6584,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -6602,15 +6848,18 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B84" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -6637,7 +6886,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -6655,15 +6904,18 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B85" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -6690,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -6708,15 +6960,18 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B86" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -6743,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -6761,15 +7016,18 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B87" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -6796,7 +7054,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -6814,15 +7072,18 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -6849,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -6867,15 +7128,18 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B89" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -6902,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -6920,15 +7184,18 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -6955,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -6973,15 +7240,18 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B91" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7008,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7026,15 +7296,18 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B92" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7061,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7079,15 +7352,18 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -7114,7 +7390,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -7132,15 +7408,18 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B94" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -7167,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -7185,15 +7464,18 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B95" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -7220,7 +7502,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -7238,15 +7520,18 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B96" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -7273,7 +7558,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -7291,15 +7576,18 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+      <c r="R96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B97" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -7326,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -7344,15 +7632,18 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -7367,45 +7658,48 @@
         <v>265</v>
       </c>
       <c r="G98">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M98">
         <v>0</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P98" t="s">
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>356</v>
+        <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -7420,45 +7714,48 @@
         <v>270</v>
       </c>
       <c r="G99">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H99">
         <v>0</v>
       </c>
       <c r="I99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99">
         <v>0</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P99" t="s">
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B100" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -7485,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -7503,15 +7800,18 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B101" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -7538,7 +7838,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -7556,15 +7856,18 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B102" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -7591,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7609,15 +7912,18 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -7644,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -7662,15 +7968,18 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -7697,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L104">
         <v>4</v>
@@ -7715,15 +8024,18 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+      <c r="R104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B105" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -7750,7 +8062,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -7768,15 +8080,18 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+      <c r="R105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -7803,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -7821,15 +8136,18 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+      <c r="R106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B107" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -7856,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -7874,15 +8192,18 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+      <c r="R107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -7909,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -7927,15 +8248,18 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+      <c r="R108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -7962,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -7980,15 +8304,18 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+      <c r="R109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B110" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -8015,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -8033,15 +8360,18 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+      <c r="R110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B111" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -8068,7 +8398,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -8086,15 +8416,18 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+      <c r="R111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -8121,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L112">
         <v>3</v>
@@ -8139,15 +8472,18 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+      <c r="R112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -8174,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L113">
         <v>5</v>
@@ -8192,15 +8528,18 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+      <c r="R113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -8227,7 +8566,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L114">
         <v>4</v>
@@ -8245,15 +8584,18 @@
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+      <c r="R114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -8280,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L115">
         <v>2</v>
@@ -8298,15 +8640,18 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+      <c r="R115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -8333,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L116">
         <v>2</v>
@@ -8351,15 +8696,18 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+      <c r="R116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -8386,7 +8734,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -8404,15 +8752,18 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+      <c r="R117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -8439,7 +8790,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -8457,15 +8808,18 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+      <c r="R118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B119" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -8492,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -8510,15 +8864,18 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+      <c r="R119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -8545,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -8563,15 +8920,18 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+      <c r="R120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -8598,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -8616,15 +8976,18 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+      <c r="R121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -8651,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L122">
         <v>4</v>
@@ -8669,15 +9032,18 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+      <c r="R122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -8704,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -8722,15 +9088,18 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+      <c r="R123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -8757,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -8775,15 +9144,18 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+      <c r="R124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -8810,7 +9182,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -8828,15 +9200,18 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -8863,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -8881,15 +9256,18 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -8916,7 +9294,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L127">
         <v>7</v>
@@ -8934,15 +9312,18 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+      <c r="R127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -8969,7 +9350,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -8987,15 +9368,18 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+      <c r="R128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -9022,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L129">
         <v>6</v>
@@ -9040,15 +9424,18 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+      <c r="R129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -9075,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L130">
         <v>6</v>
@@ -9093,15 +9480,18 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+      <c r="R130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -9128,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -9146,15 +9536,18 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+      <c r="R131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -9181,7 +9574,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L132">
         <v>17</v>
@@ -9199,15 +9592,18 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+      <c r="R132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -9222,45 +9618,48 @@
         <v>240</v>
       </c>
       <c r="G133">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L133">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M133">
         <v>6</v>
       </c>
       <c r="N133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O133">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P133" t="s">
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -9275,45 +9674,48 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L134">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M134">
         <v>6</v>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O134">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P134" t="s">
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -9340,7 +9742,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L135">
         <v>4</v>
@@ -9358,15 +9760,18 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -9381,45 +9786,48 @@
         <v>255</v>
       </c>
       <c r="G136">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H136">
         <v>0</v>
       </c>
       <c r="I136">
+        <v>4</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136" t="s">
+        <v>173</v>
+      </c>
+      <c r="L136">
+        <v>4</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
         <v>3</v>
       </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136" t="s">
-        <v>170</v>
-      </c>
-      <c r="L136">
-        <v>3</v>
-      </c>
-      <c r="M136">
-        <v>1</v>
-      </c>
-      <c r="N136">
-        <v>2</v>
-      </c>
       <c r="O136">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P136" t="s">
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -9446,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L137">
         <v>1</v>
@@ -9464,15 +9872,18 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B138" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -9499,7 +9910,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -9517,15 +9928,18 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B139" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -9552,7 +9966,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L139">
         <v>0</v>
@@ -9570,15 +9984,18 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -9605,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L140">
         <v>1</v>
@@ -9623,15 +10040,18 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+      <c r="R140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B141" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -9658,7 +10078,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L141">
         <v>0</v>
@@ -9676,15 +10096,18 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+      <c r="R141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -9711,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -9729,15 +10152,18 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="R142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B143" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -9764,7 +10190,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -9782,15 +10208,18 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="R143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B144" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -9817,7 +10246,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -9835,15 +10264,18 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="R144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B145" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -9870,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -9888,15 +10320,18 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="R145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B146" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -9923,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -9941,15 +10376,18 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="R146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B147" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -9976,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L147">
         <v>0</v>
@@ -9994,15 +10432,18 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+      <c r="R147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -10029,7 +10470,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L148">
         <v>2</v>
@@ -10047,15 +10488,18 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+      <c r="R148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>434</v>
+        <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -10070,45 +10514,48 @@
         <v>245</v>
       </c>
       <c r="G149">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149">
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149">
         <v>0</v>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P149" t="s">
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+      <c r="R149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -10135,7 +10582,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -10153,15 +10600,18 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+      <c r="R150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -10188,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -10206,21 +10656,24 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+      <c r="R151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B152" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C152" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D152" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -10241,7 +10694,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -10261,19 +10714,22 @@
       <c r="Q152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>442</v>
+      </c>
+      <c r="B153" t="s">
+        <v>443</v>
+      </c>
+      <c r="C153" t="s">
+        <v>187</v>
+      </c>
+      <c r="D153" t="s">
         <v>441</v>
-      </c>
-      <c r="B153" t="s">
-        <v>442</v>
-      </c>
-      <c r="C153" t="s">
-        <v>184</v>
-      </c>
-      <c r="D153" t="s">
-        <v>440</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -10294,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -10314,19 +10770,22 @@
       <c r="Q153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B154" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C154" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D154" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -10347,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -10367,19 +10826,22 @@
       <c r="Q154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B155" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C155" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D155" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -10400,7 +10862,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -10420,19 +10882,22 @@
       <c r="Q155">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B156" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C156" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D156" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -10453,7 +10918,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -10473,19 +10938,22 @@
       <c r="Q156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B157" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C157" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D157" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -10506,7 +10974,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -10526,19 +10994,22 @@
       <c r="Q157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B158" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C158" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D158" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -10559,7 +11030,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -10579,19 +11050,22 @@
       <c r="Q158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B159" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C159" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D159" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -10612,7 +11086,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -10632,19 +11106,22 @@
       <c r="Q159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B160" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C160" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D160" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -10665,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -10685,19 +11162,22 @@
       <c r="Q160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B161" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C161" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D161" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -10718,7 +11198,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -10738,19 +11218,22 @@
       <c r="Q161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B162" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C162" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D162" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -10771,7 +11254,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -10791,19 +11274,22 @@
       <c r="Q162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B163" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C163" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D163" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -10824,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -10844,19 +11330,22 @@
       <c r="Q163">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B164" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C164" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D164" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -10877,7 +11366,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -10897,19 +11386,22 @@
       <c r="Q164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B165" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C165" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D165" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -10930,7 +11422,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -10950,19 +11442,22 @@
       <c r="Q165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B166" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C166" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D166" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -10983,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -11003,19 +11498,22 @@
       <c r="Q166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B167" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C167" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D167" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -11036,7 +11534,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -11056,19 +11554,22 @@
       <c r="Q167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B168" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C168" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D168" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -11089,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -11109,19 +11610,22 @@
       <c r="Q168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B169" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C169" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D169" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -11142,7 +11646,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -11162,19 +11666,22 @@
       <c r="Q169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B170" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C170" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D170" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -11195,7 +11702,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -11215,19 +11722,22 @@
       <c r="Q170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B171" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C171" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D171" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -11248,7 +11758,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -11268,13 +11778,16 @@
       <c r="Q171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -11301,7 +11814,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L172">
         <v>4</v>
@@ -11319,15 +11832,18 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+      <c r="R172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -11354,7 +11870,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L173">
         <v>3</v>
@@ -11372,15 +11888,18 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+      <c r="R173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -11407,7 +11926,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L174">
         <v>3</v>
@@ -11425,15 +11944,18 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+      <c r="R174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B175" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -11460,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L175">
         <v>0</v>
@@ -11478,15 +12000,18 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+      <c r="R175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -11513,7 +12038,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -11531,15 +12056,18 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+      <c r="R176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -11566,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -11584,15 +12112,18 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+      <c r="R177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -11607,45 +12138,48 @@
         <v>240</v>
       </c>
       <c r="G178">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H178">
         <v>0</v>
       </c>
       <c r="I178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J178">
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M178">
         <v>0</v>
       </c>
       <c r="N178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P178" t="s">
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+      <c r="R178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B179" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -11672,7 +12206,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -11690,15 +12224,18 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+      <c r="R179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -11725,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -11743,15 +12280,18 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+      <c r="R180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B181" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -11778,7 +12318,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -11796,15 +12336,18 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+      <c r="R181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -11831,7 +12374,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L182">
         <v>3</v>
@@ -11849,15 +12392,18 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+      <c r="R182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -11884,7 +12430,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L183">
         <v>4</v>
@@ -11902,15 +12448,18 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+      <c r="R183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -11937,7 +12486,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -11955,15 +12504,18 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+      <c r="R184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -11990,7 +12542,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L185">
         <v>3</v>
@@ -12008,15 +12560,18 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+      <c r="R185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B186" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -12043,7 +12598,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L186">
         <v>0</v>
@@ -12061,15 +12616,18 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+      <c r="R186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -12096,7 +12654,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L187">
         <v>7</v>
@@ -12114,15 +12672,18 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="R187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -12149,7 +12710,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -12167,15 +12728,18 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="R188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -12202,7 +12766,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L189">
         <v>7</v>
@@ -12220,15 +12784,18 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="R189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -12255,7 +12822,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L190">
         <v>7</v>
@@ -12273,15 +12840,18 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="R190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B191" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -12308,7 +12878,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -12326,15 +12896,18 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="R191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -12361,7 +12934,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L192">
         <v>12</v>
@@ -12379,15 +12952,18 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+      <c r="R192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -12414,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L193">
         <v>20</v>
@@ -12432,15 +13008,18 @@
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+      <c r="R193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -12467,7 +13046,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L194">
         <v>20</v>
@@ -12485,15 +13064,18 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+      <c r="R194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -12520,7 +13102,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -12538,15 +13120,18 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+      <c r="R195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -12573,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L196">
         <v>7</v>
@@ -12591,15 +13176,18 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+      <c r="R196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B197" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -12626,7 +13214,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -12644,15 +13232,18 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+      <c r="R197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -12679,7 +13270,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -12697,15 +13288,18 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+      <c r="R198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -12732,7 +13326,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -12750,15 +13344,18 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+      <c r="R199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B200" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -12785,7 +13382,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -12803,15 +13400,18 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+      <c r="R200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -12838,7 +13438,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -12856,15 +13456,18 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+      <c r="R201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B202" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -12891,7 +13494,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -12909,15 +13512,18 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+      <c r="R202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -12944,7 +13550,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L203">
         <v>1</v>
@@ -12962,15 +13568,18 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+      <c r="R203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B204" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -12997,7 +13606,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -13015,15 +13624,18 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+      <c r="R204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -13050,7 +13662,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -13068,15 +13680,18 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+      <c r="R205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B206" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -13103,7 +13718,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -13121,15 +13736,18 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+      <c r="R206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B207" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -13156,7 +13774,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -13174,15 +13792,18 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+      <c r="R207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B208" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -13209,7 +13830,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -13227,15 +13848,18 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+      <c r="R208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B209" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -13262,7 +13886,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -13280,15 +13904,18 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+      <c r="R209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B210" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -13315,7 +13942,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -13333,15 +13960,18 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+      <c r="R210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B211" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -13368,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -13386,15 +14016,18 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+      <c r="R211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B212" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -13421,7 +14054,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -13439,15 +14072,18 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+      <c r="R212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B213" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -13474,7 +14110,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -13492,15 +14128,18 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+      <c r="R213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -13527,7 +14166,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -13545,15 +14184,18 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+      <c r="R214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -13580,7 +14222,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -13598,15 +14240,18 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+      <c r="R215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B216" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -13633,7 +14278,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -13651,15 +14296,18 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+      <c r="R216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -13686,7 +14334,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L217">
         <v>6</v>
@@ -13704,15 +14352,18 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+      <c r="R217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -13739,7 +14390,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L218">
         <v>3</v>
@@ -13757,15 +14408,18 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+      <c r="R218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -13792,7 +14446,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L219">
         <v>3</v>
@@ -13810,15 +14464,18 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+      <c r="R219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -13845,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L220">
         <v>2</v>
@@ -13863,15 +14520,18 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+      <c r="R220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B221" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -13898,7 +14558,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -13916,15 +14576,18 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+      <c r="R221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -13951,7 +14614,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -13969,15 +14632,18 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+      <c r="R222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -14004,7 +14670,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L223">
         <v>10</v>
@@ -14022,15 +14688,18 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+      <c r="R223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -14057,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L224">
         <v>10</v>
@@ -14075,15 +14744,18 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+      <c r="R224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -14110,7 +14782,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L225">
         <v>6</v>
@@ -14128,15 +14800,18 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+      <c r="R225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -14151,45 +14826,48 @@
         <v>255</v>
       </c>
       <c r="G226">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H226">
         <v>0</v>
       </c>
       <c r="I226">
+        <v>3</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226" t="s">
+        <v>173</v>
+      </c>
+      <c r="L226">
+        <v>3</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
         <v>2</v>
       </c>
-      <c r="J226">
-        <v>0</v>
-      </c>
-      <c r="K226" t="s">
-        <v>170</v>
-      </c>
-      <c r="L226">
-        <v>2</v>
-      </c>
-      <c r="M226">
-        <v>1</v>
-      </c>
-      <c r="N226">
-        <v>1</v>
-      </c>
       <c r="O226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P226" t="s">
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+      <c r="R226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -14204,45 +14882,48 @@
         <v>235</v>
       </c>
       <c r="G227">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J227">
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L227">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M227">
         <v>7</v>
       </c>
       <c r="N227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O227">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P227" t="s">
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+      <c r="R227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -14269,7 +14950,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L228">
         <v>10</v>
@@ -14287,15 +14968,18 @@
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+      <c r="R228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -14322,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L229">
         <v>10</v>
@@ -14340,15 +15024,18 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+      <c r="R229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -14375,7 +15062,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -14393,15 +15080,18 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+      <c r="R230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -14428,7 +15118,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -14446,10 +15136,13 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+      <c r="R231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>125</v>
       </c>
@@ -14478,7 +15171,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -14496,12 +15189,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B233" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C233" t="s">
         <v>120</v>
@@ -14525,7 +15218,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -14543,12 +15236,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B234" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -14572,7 +15265,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -14590,12 +15283,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B235" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C235" t="s">
         <v>120</v>
@@ -14619,7 +15312,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -14637,12 +15330,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B236" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C236" t="s">
         <v>120</v>
@@ -14666,7 +15359,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -14684,7 +15377,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>127</v>
       </c>
@@ -14713,7 +15406,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -14731,12 +15424,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B238" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -14760,7 +15453,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -14778,12 +15471,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B239" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -14807,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -14825,12 +15518,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B240" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -14854,7 +15547,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -14901,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -14921,10 +15614,10 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B242" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -14948,7 +15641,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -14968,10 +15661,10 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B243" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -14995,7 +15688,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -15015,10 +15708,10 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B244" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -15042,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -15089,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L245">
         <v>1</v>
@@ -15109,10 +15802,10 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B246" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C246" t="s">
         <v>120</v>
@@ -15136,7 +15829,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L246">
         <v>0</v>
@@ -15156,10 +15849,10 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B247" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C247" t="s">
         <v>120</v>
@@ -15183,7 +15876,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -15203,16 +15896,16 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B248" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
       </c>
       <c r="D248" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E248" t="s">
         <v>122</v>
@@ -15230,7 +15923,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -15250,16 +15943,16 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B249" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C249" t="s">
         <v>120</v>
       </c>
       <c r="D249" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E249" t="s">
         <v>122</v>
@@ -15277,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -15297,16 +15990,16 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B250" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
       </c>
       <c r="D250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E250" t="s">
         <v>122</v>
@@ -15324,7 +16017,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -15344,16 +16037,16 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B251" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
       </c>
       <c r="D251" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E251" t="s">
         <v>122</v>
@@ -15371,7 +16064,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -15391,10 +16084,10 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B252" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C252" t="s">
         <v>120</v>
@@ -15418,7 +16111,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -15438,10 +16131,10 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B253" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C253" t="s">
         <v>120</v>
@@ -15465,7 +16158,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L253">
         <v>0</v>
@@ -15512,7 +16205,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -15559,7 +16252,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -15606,7 +16299,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L256">
         <v>2</v>
@@ -15626,10 +16319,10 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B257" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -15653,7 +16346,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -15700,7 +16393,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L258">
         <v>2</v>
@@ -15720,10 +16413,10 @@
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B259" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C259" t="s">
         <v>120</v>
@@ -15747,7 +16440,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -15772,9 +16465,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A63A091A-E04E-4136-B4E3-F0066E8C3605}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79586A95-D631-4279-9580-87DD0951E471}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J370"/>
+  <dimension ref="A1:J380"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -27614,6 +28307,326 @@
         <v>1</v>
       </c>
       <c r="J370" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A371" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B371" t="s">
+        <v>158</v>
+      </c>
+      <c r="C371" t="s">
+        <v>24</v>
+      </c>
+      <c r="D371" t="s">
+        <v>33</v>
+      </c>
+      <c r="E371" t="s">
+        <v>100</v>
+      </c>
+      <c r="F371" t="s">
+        <v>94</v>
+      </c>
+      <c r="G371">
+        <v>270</v>
+      </c>
+      <c r="H371" t="s">
+        <v>15</v>
+      </c>
+      <c r="I371">
+        <v>1</v>
+      </c>
+      <c r="J371" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A372" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B372" t="s">
+        <v>70</v>
+      </c>
+      <c r="C372" t="s">
+        <v>24</v>
+      </c>
+      <c r="D372" t="s">
+        <v>49</v>
+      </c>
+      <c r="E372" t="s">
+        <v>100</v>
+      </c>
+      <c r="F372" t="s">
+        <v>94</v>
+      </c>
+      <c r="G372">
+        <v>235</v>
+      </c>
+      <c r="H372" t="s">
+        <v>22</v>
+      </c>
+      <c r="I372">
+        <v>1</v>
+      </c>
+      <c r="J372" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A373" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B373" t="s">
+        <v>61</v>
+      </c>
+      <c r="C373" t="s">
+        <v>18</v>
+      </c>
+      <c r="D373" t="s">
+        <v>21</v>
+      </c>
+      <c r="E373" t="s">
+        <v>100</v>
+      </c>
+      <c r="F373" t="s">
+        <v>94</v>
+      </c>
+      <c r="G373">
+        <v>245</v>
+      </c>
+      <c r="H373" t="s">
+        <v>22</v>
+      </c>
+      <c r="I373">
+        <v>1</v>
+      </c>
+      <c r="J373" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A374" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B374" t="s">
+        <v>141</v>
+      </c>
+      <c r="C374" t="s">
+        <v>24</v>
+      </c>
+      <c r="D374" t="s">
+        <v>25</v>
+      </c>
+      <c r="E374" t="s">
+        <v>100</v>
+      </c>
+      <c r="F374" t="s">
+        <v>94</v>
+      </c>
+      <c r="G374">
+        <v>240</v>
+      </c>
+      <c r="H374" t="s">
+        <v>22</v>
+      </c>
+      <c r="I374">
+        <v>1</v>
+      </c>
+      <c r="J374" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A375" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B375" t="s">
+        <v>114</v>
+      </c>
+      <c r="C375" t="s">
+        <v>24</v>
+      </c>
+      <c r="D375" t="s">
+        <v>49</v>
+      </c>
+      <c r="E375" t="s">
+        <v>100</v>
+      </c>
+      <c r="F375" t="s">
+        <v>94</v>
+      </c>
+      <c r="G375">
+        <v>255</v>
+      </c>
+      <c r="H375" t="s">
+        <v>22</v>
+      </c>
+      <c r="I375">
+        <v>1</v>
+      </c>
+      <c r="J375" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A376" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B376" t="s">
+        <v>32</v>
+      </c>
+      <c r="C376" t="s">
+        <v>24</v>
+      </c>
+      <c r="D376" t="s">
+        <v>33</v>
+      </c>
+      <c r="E376" t="s">
+        <v>53</v>
+      </c>
+      <c r="F376" t="s">
+        <v>94</v>
+      </c>
+      <c r="G376">
+        <v>265</v>
+      </c>
+      <c r="H376" t="s">
+        <v>15</v>
+      </c>
+      <c r="I376">
+        <v>1</v>
+      </c>
+      <c r="J376" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A377" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B377" t="s">
+        <v>61</v>
+      </c>
+      <c r="C377" t="s">
+        <v>18</v>
+      </c>
+      <c r="D377" t="s">
+        <v>21</v>
+      </c>
+      <c r="E377" t="s">
+        <v>53</v>
+      </c>
+      <c r="F377" t="s">
+        <v>94</v>
+      </c>
+      <c r="G377">
+        <v>245</v>
+      </c>
+      <c r="H377" t="s">
+        <v>22</v>
+      </c>
+      <c r="I377">
+        <v>1</v>
+      </c>
+      <c r="J377" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A378" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B378" t="s">
+        <v>78</v>
+      </c>
+      <c r="C378" t="s">
+        <v>18</v>
+      </c>
+      <c r="D378" t="s">
+        <v>21</v>
+      </c>
+      <c r="E378" t="s">
+        <v>53</v>
+      </c>
+      <c r="F378" t="s">
+        <v>94</v>
+      </c>
+      <c r="G378">
+        <v>240</v>
+      </c>
+      <c r="H378" t="s">
+        <v>22</v>
+      </c>
+      <c r="I378">
+        <v>1</v>
+      </c>
+      <c r="J378" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A379" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B379" t="s">
+        <v>85</v>
+      </c>
+      <c r="C379" t="s">
+        <v>18</v>
+      </c>
+      <c r="D379" t="s">
+        <v>21</v>
+      </c>
+      <c r="E379" t="s">
+        <v>53</v>
+      </c>
+      <c r="F379" t="s">
+        <v>94</v>
+      </c>
+      <c r="G379">
+        <v>255</v>
+      </c>
+      <c r="H379" t="s">
+        <v>22</v>
+      </c>
+      <c r="I379">
+        <v>1</v>
+      </c>
+      <c r="J379" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B380" t="s">
+        <v>159</v>
+      </c>
+      <c r="C380" t="s">
+        <v>18</v>
+      </c>
+      <c r="D380" t="s">
+        <v>90</v>
+      </c>
+      <c r="E380" t="s">
+        <v>53</v>
+      </c>
+      <c r="F380" t="s">
+        <v>94</v>
+      </c>
+      <c r="G380">
+        <v>245</v>
+      </c>
+      <c r="H380" t="s">
+        <v>22</v>
+      </c>
+      <c r="I380">
+        <v>1</v>
+      </c>
+      <c r="J380" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55983B4B-25C7-416E-A409-7E89EA333857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07114E84-9459-4B6F-B54E-5E85FD29AF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{DEE7CD9E-3F62-4AAF-919E-F0D0541F7FC9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F298818A-6462-4701-BFAF-ACE0211CC93D}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4653" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4863" uniqueCount="592">
   <si>
     <t>날짜</t>
   </si>
@@ -522,6 +522,21 @@
     <t>BJW1179-GY245</t>
   </si>
   <si>
+    <t>BJW1170-SLAP255</t>
+  </si>
+  <si>
+    <t>BJW1179-BKSL240</t>
+  </si>
+  <si>
+    <t>BJW1179-BKSL255</t>
+  </si>
+  <si>
+    <t>BJW1170-APPU250</t>
+  </si>
+  <si>
+    <t>DPM644-APCO275</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1122,9 +1137,6 @@
     <t>DPM644APCO 바오지 남성 러닝화 살구커피 270</t>
   </si>
   <si>
-    <t>DPM644-APCO275</t>
-  </si>
-  <si>
     <t>DPM644APCO 바오지 남성 러닝화 살구커피 275</t>
   </si>
   <si>
@@ -1287,9 +1299,6 @@
     <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/620fa2b989fb7b735c6460f8db0f7193.jpg</t>
   </si>
   <si>
-    <t>BJW1179-BKSL240</t>
-  </si>
-  <si>
     <t>BJW1179BKSL 바오지 여성 데일리화 블랙실버 240</t>
   </si>
   <si>
@@ -1302,9 +1311,6 @@
     <t>BJW1179BKSL 바오지 여성 데일리화 블랙실버 250</t>
   </si>
   <si>
-    <t>BJW1179-BKSL255</t>
-  </si>
-  <si>
     <t>BJW1179BKSL 바오지 여성 데일리화 블랙실버 255</t>
   </si>
   <si>
@@ -1494,9 +1500,6 @@
     <t>BJW1170APPU 바오지 여성 러닝화 살구퍼플 245</t>
   </si>
   <si>
-    <t>BJW1170-APPU250</t>
-  </si>
-  <si>
     <t>BJW1170APPU 바오지 여성 러닝화 살구퍼플 250</t>
   </si>
   <si>
@@ -1540,9 +1543,6 @@
   </si>
   <si>
     <t>BJW1170SLAP 바오지 여성 러닝화 실버살구 250</t>
-  </si>
-  <si>
-    <t>BJW1170-SLAP255</t>
   </si>
   <si>
     <t>BJW1170SLAP 바오지 여성 러닝화 실버살구 255</t>
@@ -2201,8 +2201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDBC09BF-1F3D-4C30-97DB-7F255DE800CA}">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A2523A-0734-4AD4-8BD3-B16C02981BFD}">
   <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2211,7 +2210,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2226,40 +2225,40 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="K1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="N1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="O1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="R1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -2267,7 +2266,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2294,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2312,7 +2311,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2323,7 +2322,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2350,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -2368,7 +2367,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2379,7 +2378,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2406,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2424,7 +2423,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2435,7 +2434,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2462,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2480,7 +2479,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2491,7 +2490,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2518,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2536,7 +2535,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2547,7 +2546,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2574,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2592,7 +2591,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2603,7 +2602,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2630,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2648,7 +2647,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2659,7 +2658,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2686,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2704,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2715,7 +2714,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2742,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2760,7 +2759,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2771,7 +2770,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2798,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2816,7 +2815,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2824,16 +2823,16 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2854,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2880,16 +2879,16 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -2910,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2936,16 +2935,16 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" t="s">
         <v>192</v>
       </c>
-      <c r="C14" t="s">
-        <v>187</v>
-      </c>
       <c r="D14" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2966,7 +2965,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2992,16 +2991,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" t="s">
         <v>193</v>
-      </c>
-      <c r="B15" t="s">
-        <v>194</v>
-      </c>
-      <c r="C15" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" t="s">
-        <v>188</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3022,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3048,16 +3047,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D16" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3078,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3104,16 +3103,16 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D17" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3134,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3160,16 +3159,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3190,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3216,16 +3215,16 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D19" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3246,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3272,16 +3271,16 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3302,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3328,16 +3327,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C21" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D21" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3358,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3384,16 +3383,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D22" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3414,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3440,16 +3439,16 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D23" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3470,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3496,16 +3495,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C24" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D24" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3526,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3552,16 +3551,16 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3582,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3608,16 +3607,16 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C26" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D26" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3638,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3664,16 +3663,16 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C27" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D27" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3694,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3720,16 +3719,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B28" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D28" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3750,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3776,16 +3775,16 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B29" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C29" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D29" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3806,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3832,16 +3831,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B30" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D30" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3862,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3888,16 +3887,16 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B31" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D31" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3918,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3944,16 +3943,16 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B32" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C32" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D32" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3974,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4000,16 +3999,16 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B33" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C33" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D33" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4030,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4056,16 +4055,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D34" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4086,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4112,16 +4111,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>239</v>
+      </c>
+      <c r="B35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" t="s">
+        <v>192</v>
+      </c>
+      <c r="D35" t="s">
         <v>234</v>
-      </c>
-      <c r="B35" t="s">
-        <v>235</v>
-      </c>
-      <c r="C35" t="s">
-        <v>187</v>
-      </c>
-      <c r="D35" t="s">
-        <v>229</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4142,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4168,16 +4167,16 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B36" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D36" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4198,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4224,16 +4223,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B37" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C37" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D37" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4254,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4280,16 +4279,16 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B38" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D38" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4310,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4336,16 +4335,16 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C39" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D39" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4366,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4392,16 +4391,16 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C40" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4422,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4448,16 +4447,16 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C41" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D41" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4478,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4504,16 +4503,16 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B42" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C42" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D42" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4534,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4560,16 +4559,16 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C43" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D43" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4590,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4616,16 +4615,16 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B44" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C44" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D44" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4646,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4672,16 +4671,16 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D45" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4702,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4728,16 +4727,16 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B46" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D46" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4758,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4784,16 +4783,16 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B47" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C47" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D47" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4814,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4840,16 +4839,16 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B48" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D48" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4870,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4896,16 +4895,16 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B49" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C49" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D49" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4926,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4952,16 +4951,16 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B50" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C50" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D50" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4982,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5008,16 +5007,16 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B51" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C51" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D51" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5038,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5064,16 +5063,16 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B52" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C52" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D52" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5094,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5120,16 +5119,16 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B53" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C53" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D53" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5150,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5176,16 +5175,16 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B54" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C54" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D54" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5206,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5232,16 +5231,16 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>280</v>
+      </c>
+      <c r="B55" t="s">
+        <v>281</v>
+      </c>
+      <c r="C55" t="s">
+        <v>192</v>
+      </c>
+      <c r="D55" t="s">
         <v>275</v>
-      </c>
-      <c r="B55" t="s">
-        <v>276</v>
-      </c>
-      <c r="C55" t="s">
-        <v>187</v>
-      </c>
-      <c r="D55" t="s">
-        <v>270</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5262,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5288,16 +5287,16 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B56" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C56" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D56" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5318,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5344,16 +5343,16 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B57" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C57" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D57" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5374,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5400,16 +5399,16 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B58" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C58" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D58" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5430,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5456,16 +5455,16 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B59" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C59" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D59" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5486,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5512,16 +5511,16 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B60" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C60" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5542,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5568,16 +5567,16 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B61" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C61" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D61" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5598,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5624,16 +5623,16 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B62" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C62" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D62" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5654,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -5680,16 +5679,16 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B63" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D63" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5710,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -5736,16 +5735,16 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B64" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C64" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D64" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5766,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -5792,16 +5791,16 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B65" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C65" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D65" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5822,7 +5821,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5848,16 +5847,16 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B66" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C66" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D66" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5878,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -5907,7 +5906,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -5934,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -5952,7 +5951,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -5963,7 +5962,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -5990,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -6008,7 +6007,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6019,7 +6018,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6046,7 +6045,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L69">
         <v>4</v>
@@ -6064,7 +6063,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6075,7 +6074,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6102,7 +6101,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6120,7 +6119,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6131,7 +6130,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6158,7 +6157,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6176,7 +6175,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6184,10 +6183,10 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B72" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6214,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6232,7 +6231,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6243,7 +6242,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6270,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6279,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="N73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73">
         <v>3</v>
@@ -6288,7 +6287,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6296,10 +6295,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B74" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6326,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6344,7 +6343,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6352,10 +6351,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B75" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6382,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -6400,7 +6399,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6408,10 +6407,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B76" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6438,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6456,7 +6455,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6464,10 +6463,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B77" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -6494,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -6512,7 +6511,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -6520,10 +6519,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B78" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -6550,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -6568,7 +6567,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -6576,10 +6575,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B79" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -6606,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -6624,7 +6623,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -6635,7 +6634,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -6662,7 +6661,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -6680,7 +6679,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -6688,10 +6687,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B81" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -6718,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -6736,7 +6735,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -6744,10 +6743,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -6774,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6792,7 +6791,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -6800,10 +6799,10 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B83" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -6830,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -6848,7 +6847,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -6856,10 +6855,10 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B84" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -6886,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -6904,7 +6903,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -6912,10 +6911,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B85" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -6942,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -6960,7 +6959,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -6968,10 +6967,10 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B86" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -6998,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7016,7 +7015,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7024,10 +7023,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B87" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7054,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7072,7 +7071,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7083,7 +7082,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7110,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -7128,7 +7127,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7136,10 +7135,10 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B89" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7166,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -7184,7 +7183,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7195,7 +7194,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7222,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -7240,7 +7239,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7248,10 +7247,10 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B91" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7278,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7296,7 +7295,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7304,10 +7303,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B92" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7334,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7352,7 +7351,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7363,7 +7362,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -7390,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -7408,7 +7407,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -7416,10 +7415,10 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B94" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -7446,7 +7445,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -7464,7 +7463,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -7472,10 +7471,10 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B95" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -7502,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -7520,7 +7519,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -7528,10 +7527,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B96" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -7558,7 +7557,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -7576,7 +7575,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -7584,10 +7583,10 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B97" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -7614,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -7632,7 +7631,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -7643,7 +7642,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -7658,37 +7657,37 @@
         <v>265</v>
       </c>
       <c r="G98">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L98">
+        <v>3</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
         <v>2</v>
       </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>1</v>
-      </c>
       <c r="O98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P98" t="s">
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -7699,7 +7698,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -7726,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L99">
         <v>1</v>
@@ -7744,7 +7743,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -7752,10 +7751,10 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>360</v>
+        <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -7770,37 +7769,37 @@
         <v>275</v>
       </c>
       <c r="G100">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H100">
         <v>0</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100">
         <v>0</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P100" t="s">
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -7808,10 +7807,10 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -7838,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -7856,7 +7855,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -7864,10 +7863,10 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B102" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -7894,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7912,7 +7911,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -7920,10 +7919,10 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B103" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -7950,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -7968,7 +7967,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -7979,7 +7978,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -7994,37 +7993,37 @@
         <v>270</v>
       </c>
       <c r="G104">
+        <v>4</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" t="s">
+        <v>178</v>
+      </c>
+      <c r="L104">
         <v>5</v>
       </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <v>1</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104" t="s">
-        <v>173</v>
-      </c>
-      <c r="L104">
-        <v>4</v>
-      </c>
       <c r="M104">
         <v>0</v>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P104" t="s">
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8032,10 +8031,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B105" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8062,7 +8061,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8080,7 +8079,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8091,7 +8090,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8118,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8136,7 +8135,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8144,10 +8143,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B107" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8174,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8192,7 +8191,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8203,7 +8202,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8230,7 +8229,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8248,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8259,7 +8258,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -8286,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -8304,7 +8303,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -8312,10 +8311,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B110" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -8342,7 +8341,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -8360,7 +8359,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -8368,10 +8367,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B111" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -8398,7 +8397,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -8416,7 +8415,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -8427,7 +8426,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -8454,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L112">
         <v>3</v>
@@ -8472,7 +8471,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -8483,7 +8482,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -8510,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L113">
         <v>5</v>
@@ -8528,7 +8527,7 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -8539,7 +8538,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -8554,37 +8553,37 @@
         <v>270</v>
       </c>
       <c r="G114">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M114">
         <v>0</v>
       </c>
       <c r="N114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P114" t="s">
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -8595,7 +8594,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -8610,37 +8609,37 @@
         <v>275</v>
       </c>
       <c r="G115">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L115">
+        <v>3</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115">
         <v>2</v>
       </c>
-      <c r="M115">
-        <v>1</v>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>1</v>
-      </c>
       <c r="P115" t="s">
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -8651,7 +8650,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -8666,22 +8665,22 @@
         <v>280</v>
       </c>
       <c r="G116">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H116">
         <v>0</v>
       </c>
       <c r="I116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M116">
         <v>0</v>
@@ -8690,13 +8689,13 @@
         <v>1</v>
       </c>
       <c r="O116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P116" t="s">
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -8707,7 +8706,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -8734,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -8752,7 +8751,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -8763,7 +8762,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -8790,7 +8789,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -8799,7 +8798,7 @@
         <v>0</v>
       </c>
       <c r="N118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O118">
         <v>1</v>
@@ -8808,7 +8807,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -8816,10 +8815,10 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B119" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -8846,7 +8845,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -8864,7 +8863,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -8875,7 +8874,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -8902,7 +8901,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -8920,7 +8919,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -8931,7 +8930,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -8958,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -8976,7 +8975,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -8987,7 +8986,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9014,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L122">
         <v>4</v>
@@ -9032,7 +9031,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9043,7 +9042,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9070,7 +9069,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9088,7 +9087,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9099,7 +9098,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9126,7 +9125,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -9144,7 +9143,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9155,7 +9154,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9182,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -9200,7 +9199,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -9211,7 +9210,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -9238,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -9256,7 +9255,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -9267,7 +9266,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -9294,7 +9293,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L127">
         <v>7</v>
@@ -9312,7 +9311,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -9323,7 +9322,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -9350,7 +9349,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -9368,7 +9367,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -9379,7 +9378,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -9394,37 +9393,37 @@
         <v>245</v>
       </c>
       <c r="G129">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H129">
         <v>0</v>
       </c>
       <c r="I129">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L129">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M129">
         <v>6</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P129" t="s">
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -9435,7 +9434,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -9450,37 +9449,37 @@
         <v>250</v>
       </c>
       <c r="G130">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H130">
         <v>0</v>
       </c>
       <c r="I130">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L130">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M130">
         <v>5</v>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P130" t="s">
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -9491,7 +9490,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -9518,7 +9517,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -9536,7 +9535,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -9547,7 +9546,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -9574,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L132">
         <v>17</v>
@@ -9592,7 +9591,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -9603,7 +9602,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -9618,37 +9617,37 @@
         <v>240</v>
       </c>
       <c r="G133">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L133">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M133">
         <v>6</v>
       </c>
       <c r="N133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O133">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P133" t="s">
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -9659,7 +9658,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -9674,37 +9673,37 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L134">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M134">
         <v>6</v>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O134">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P134" t="s">
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -9715,7 +9714,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -9730,37 +9729,37 @@
         <v>250</v>
       </c>
       <c r="G135">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H135">
         <v>0</v>
       </c>
       <c r="I135">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L135">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M135">
         <v>2</v>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O135">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P135" t="s">
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -9771,7 +9770,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -9798,7 +9797,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -9807,7 +9806,7 @@
         <v>1</v>
       </c>
       <c r="N136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O136">
         <v>4</v>
@@ -9816,7 +9815,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -9827,7 +9826,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -9842,37 +9841,37 @@
         <v>235</v>
       </c>
       <c r="G137">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H137">
         <v>0</v>
       </c>
       <c r="I137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M137">
         <v>0</v>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P137" t="s">
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -9880,10 +9879,10 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>415</v>
+        <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -9898,37 +9897,37 @@
         <v>240</v>
       </c>
       <c r="G138">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M138">
         <v>0</v>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P138" t="s">
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -9936,10 +9935,10 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B139" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -9966,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L139">
         <v>0</v>
@@ -9984,7 +9983,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -9995,7 +9994,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10010,37 +10009,37 @@
         <v>250</v>
       </c>
       <c r="G140">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H140">
         <v>0</v>
       </c>
       <c r="I140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M140">
         <v>0</v>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P140" t="s">
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10048,10 +10047,10 @@
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>420</v>
+        <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10066,37 +10065,37 @@
         <v>255</v>
       </c>
       <c r="G141">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H141">
         <v>0</v>
       </c>
       <c r="I141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141">
         <v>0</v>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" t="s">
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -10107,7 +10106,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -10134,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -10152,7 +10151,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -10160,10 +10159,10 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B143" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -10190,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -10208,7 +10207,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -10216,10 +10215,10 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B144" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -10246,7 +10245,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -10264,7 +10263,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -10272,10 +10271,10 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B145" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -10302,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -10320,7 +10319,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -10328,10 +10327,10 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B146" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -10358,7 +10357,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -10376,7 +10375,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -10384,10 +10383,10 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B147" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -10414,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L147">
         <v>0</v>
@@ -10432,7 +10431,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -10443,7 +10442,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -10458,37 +10457,37 @@
         <v>240</v>
       </c>
       <c r="G148">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L148">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M148">
         <v>0</v>
       </c>
       <c r="N148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O148">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P148" t="s">
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -10499,7 +10498,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -10526,7 +10525,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -10544,7 +10543,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -10555,7 +10554,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -10582,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -10600,7 +10599,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -10611,7 +10610,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -10638,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -10656,7 +10655,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -10664,16 +10663,16 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B152" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C152" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D152" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -10694,7 +10693,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -10720,16 +10719,16 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B153" t="s">
+        <v>445</v>
+      </c>
+      <c r="C153" t="s">
+        <v>192</v>
+      </c>
+      <c r="D153" t="s">
         <v>443</v>
-      </c>
-      <c r="C153" t="s">
-        <v>187</v>
-      </c>
-      <c r="D153" t="s">
-        <v>441</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -10750,7 +10749,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -10776,16 +10775,16 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B154" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C154" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D154" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -10806,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -10832,16 +10831,16 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B155" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C155" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D155" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -10862,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -10888,16 +10887,16 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B156" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C156" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D156" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -10918,7 +10917,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -10944,16 +10943,16 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B157" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C157" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D157" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -10974,7 +10973,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -11000,16 +10999,16 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B158" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C158" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D158" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -11030,7 +11029,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -11056,16 +11055,16 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B159" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C159" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D159" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -11086,7 +11085,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -11112,16 +11111,16 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B160" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C160" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D160" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -11142,7 +11141,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -11168,16 +11167,16 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B161" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C161" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D161" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -11198,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -11224,16 +11223,16 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B162" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C162" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D162" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -11254,7 +11253,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -11280,16 +11279,16 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B163" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C163" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D163" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -11310,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -11336,16 +11335,16 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B164" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C164" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D164" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -11366,7 +11365,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -11392,16 +11391,16 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B165" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C165" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D165" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -11422,7 +11421,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -11448,16 +11447,16 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B166" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C166" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D166" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -11478,7 +11477,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -11504,16 +11503,16 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B167" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C167" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D167" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -11534,7 +11533,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -11560,16 +11559,16 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B168" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C168" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D168" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -11590,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -11616,16 +11615,16 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B169" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C169" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D169" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -11646,7 +11645,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -11672,16 +11671,16 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B170" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C170" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D170" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -11702,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -11728,16 +11727,16 @@
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B171" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C171" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D171" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -11758,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -11787,7 +11786,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -11802,37 +11801,37 @@
         <v>235</v>
       </c>
       <c r="G172">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
+        <v>5</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172" t="s">
+        <v>178</v>
+      </c>
+      <c r="L172">
+        <v>6</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="N172">
         <v>3</v>
       </c>
-      <c r="J172">
-        <v>0</v>
-      </c>
-      <c r="K172" t="s">
-        <v>173</v>
-      </c>
-      <c r="L172">
-        <v>4</v>
-      </c>
-      <c r="M172">
-        <v>1</v>
-      </c>
-      <c r="N172">
-        <v>1</v>
-      </c>
       <c r="O172">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P172" t="s">
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -11843,7 +11842,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -11870,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L173">
         <v>3</v>
@@ -11888,7 +11887,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -11899,7 +11898,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -11914,37 +11913,37 @@
         <v>245</v>
       </c>
       <c r="G174">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H174">
         <v>0</v>
       </c>
       <c r="I174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J174">
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M174">
         <v>1</v>
       </c>
       <c r="N174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P174" t="s">
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -11952,10 +11951,10 @@
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>484</v>
+        <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -11970,37 +11969,37 @@
         <v>250</v>
       </c>
       <c r="G175">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H175">
         <v>0</v>
       </c>
       <c r="I175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175">
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M175">
         <v>0</v>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P175" t="s">
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -12011,7 +12010,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -12038,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -12056,7 +12055,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -12067,7 +12066,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -12094,7 +12093,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -12112,7 +12111,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -12123,7 +12122,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -12150,13 +12149,13 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L178">
         <v>2</v>
       </c>
       <c r="M178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N178">
         <v>2</v>
@@ -12168,7 +12167,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -12176,10 +12175,10 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B179" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -12206,7 +12205,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -12224,7 +12223,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -12235,7 +12234,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -12262,7 +12261,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -12280,7 +12279,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -12288,10 +12287,10 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B181" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -12318,7 +12317,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -12336,7 +12335,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -12347,7 +12346,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -12362,37 +12361,37 @@
         <v>235</v>
       </c>
       <c r="G182">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H182">
         <v>0</v>
       </c>
       <c r="I182">
+        <v>3</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182" t="s">
+        <v>178</v>
+      </c>
+      <c r="L182">
+        <v>4</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
         <v>2</v>
       </c>
-      <c r="J182">
-        <v>0</v>
-      </c>
-      <c r="K182" t="s">
-        <v>173</v>
-      </c>
-      <c r="L182">
+      <c r="O182">
         <v>3</v>
       </c>
-      <c r="M182">
-        <v>1</v>
-      </c>
-      <c r="N182">
-        <v>1</v>
-      </c>
-      <c r="O182">
-        <v>2</v>
-      </c>
       <c r="P182" t="s">
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -12403,7 +12402,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -12430,7 +12429,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L183">
         <v>4</v>
@@ -12448,7 +12447,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -12459,7 +12458,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -12486,7 +12485,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -12504,7 +12503,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -12515,7 +12514,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -12542,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L185">
         <v>3</v>
@@ -12551,7 +12550,7 @@
         <v>1</v>
       </c>
       <c r="N185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O185">
         <v>3</v>
@@ -12560,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -12568,7 +12567,7 @@
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="B186" t="s">
         <v>501</v>
@@ -12586,37 +12585,37 @@
         <v>255</v>
       </c>
       <c r="G186">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H186">
         <v>0</v>
       </c>
       <c r="I186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J186">
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186">
         <v>0</v>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P186" t="s">
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -12654,7 +12653,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L187">
         <v>7</v>
@@ -12710,7 +12709,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -12754,31 +12753,31 @@
         <v>245</v>
       </c>
       <c r="G189">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H189">
         <v>0</v>
       </c>
       <c r="I189">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J189">
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L189">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M189">
         <v>6</v>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O189">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P189" t="s">
         <v>16</v>
@@ -12822,7 +12821,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L190">
         <v>7</v>
@@ -12878,7 +12877,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -12934,7 +12933,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L192">
         <v>12</v>
@@ -12978,31 +12977,31 @@
         <v>240</v>
       </c>
       <c r="G193">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J193">
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L193">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M193">
         <v>17</v>
       </c>
       <c r="N193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O193">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P193" t="s">
         <v>16</v>
@@ -13046,7 +13045,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L194">
         <v>20</v>
@@ -13102,7 +13101,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -13158,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L196">
         <v>7</v>
@@ -13214,7 +13213,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -13270,7 +13269,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -13326,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -13382,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -13438,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -13494,7 +13493,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -13538,31 +13537,31 @@
         <v>240</v>
       </c>
       <c r="G203">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H203">
         <v>0</v>
       </c>
       <c r="I203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J203">
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M203">
         <v>0</v>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P203" t="s">
         <v>16</v>
@@ -13606,7 +13605,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -13662,7 +13661,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -13718,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -13774,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -13830,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -13886,7 +13885,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -13942,7 +13941,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -13998,7 +13997,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -14054,7 +14053,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -14110,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -14166,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -14222,7 +14221,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -14278,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -14334,7 +14333,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L217">
         <v>6</v>
@@ -14390,7 +14389,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L218">
         <v>3</v>
@@ -14446,7 +14445,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L219">
         <v>3</v>
@@ -14502,7 +14501,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L220">
         <v>2</v>
@@ -14558,7 +14557,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -14614,7 +14613,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -14670,7 +14669,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L223">
         <v>10</v>
@@ -14714,31 +14713,31 @@
         <v>245</v>
       </c>
       <c r="G224">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H224">
         <v>0</v>
       </c>
       <c r="I224">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J224">
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L224">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M224">
         <v>5</v>
       </c>
       <c r="N224">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O224">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P224" t="s">
         <v>16</v>
@@ -14782,7 +14781,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L225">
         <v>6</v>
@@ -14838,7 +14837,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -14894,13 +14893,13 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L227">
         <v>8</v>
       </c>
       <c r="M227">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N227">
         <v>3</v>
@@ -14950,7 +14949,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L228">
         <v>10</v>
@@ -15006,7 +15005,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L229">
         <v>10</v>
@@ -15062,7 +15061,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -15118,7 +15117,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -15171,7 +15170,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -15218,7 +15217,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -15265,7 +15264,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -15312,7 +15311,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -15359,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -15406,7 +15405,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -15453,7 +15452,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -15500,7 +15499,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -15547,7 +15546,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -15594,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -15641,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -15688,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -15735,7 +15734,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -15782,7 +15781,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L245">
         <v>1</v>
@@ -15829,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L246">
         <v>0</v>
@@ -15876,7 +15875,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -15923,7 +15922,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -15970,7 +15969,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -16017,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -16064,7 +16063,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -16111,7 +16110,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -16158,7 +16157,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L253">
         <v>0</v>
@@ -16205,7 +16204,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -16252,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -16261,7 +16260,7 @@
         <v>0</v>
       </c>
       <c r="N255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O255">
         <v>1</v>
@@ -16299,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L256">
         <v>2</v>
@@ -16346,7 +16345,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -16393,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L258">
         <v>2</v>
@@ -16440,7 +16439,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -16465,9 +16464,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79586A95-D631-4279-9580-87DD0951E471}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J380"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65318CB5-FF34-4AD3-9AE9-35631C91F845}">
+  <dimension ref="A1:J410"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -28359,7 +28357,7 @@
         <v>100</v>
       </c>
       <c r="F372" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="G372">
         <v>235</v>
@@ -28423,7 +28421,7 @@
         <v>100</v>
       </c>
       <c r="F374" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="G374">
         <v>240</v>
@@ -28627,6 +28625,966 @@
         <v>1</v>
       </c>
       <c r="J380" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A381" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B381" t="s">
+        <v>27</v>
+      </c>
+      <c r="C381" t="s">
+        <v>24</v>
+      </c>
+      <c r="D381" t="s">
+        <v>25</v>
+      </c>
+      <c r="E381" t="s">
+        <v>53</v>
+      </c>
+      <c r="F381" t="s">
+        <v>94</v>
+      </c>
+      <c r="G381">
+        <v>235</v>
+      </c>
+      <c r="H381" t="s">
+        <v>22</v>
+      </c>
+      <c r="I381">
+        <v>1</v>
+      </c>
+      <c r="J381" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A382" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B382" t="s">
+        <v>42</v>
+      </c>
+      <c r="C382" t="s">
+        <v>24</v>
+      </c>
+      <c r="D382" t="s">
+        <v>40</v>
+      </c>
+      <c r="E382" t="s">
+        <v>53</v>
+      </c>
+      <c r="F382" t="s">
+        <v>94</v>
+      </c>
+      <c r="G382">
+        <v>245</v>
+      </c>
+      <c r="H382" t="s">
+        <v>22</v>
+      </c>
+      <c r="I382">
+        <v>1</v>
+      </c>
+      <c r="J382" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A383" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B383" t="s">
+        <v>61</v>
+      </c>
+      <c r="C383" t="s">
+        <v>18</v>
+      </c>
+      <c r="D383" t="s">
+        <v>21</v>
+      </c>
+      <c r="E383" t="s">
+        <v>53</v>
+      </c>
+      <c r="F383" t="s">
+        <v>94</v>
+      </c>
+      <c r="G383">
+        <v>245</v>
+      </c>
+      <c r="H383" t="s">
+        <v>22</v>
+      </c>
+      <c r="I383">
+        <v>1</v>
+      </c>
+      <c r="J383" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A384" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B384" t="s">
+        <v>23</v>
+      </c>
+      <c r="C384" t="s">
+        <v>24</v>
+      </c>
+      <c r="D384" t="s">
+        <v>25</v>
+      </c>
+      <c r="E384" t="s">
+        <v>53</v>
+      </c>
+      <c r="F384" t="s">
+        <v>94</v>
+      </c>
+      <c r="G384">
+        <v>235</v>
+      </c>
+      <c r="H384" t="s">
+        <v>22</v>
+      </c>
+      <c r="I384">
+        <v>1</v>
+      </c>
+      <c r="J384" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B385" t="s">
+        <v>23</v>
+      </c>
+      <c r="C385" t="s">
+        <v>24</v>
+      </c>
+      <c r="D385" t="s">
+        <v>25</v>
+      </c>
+      <c r="E385" t="s">
+        <v>53</v>
+      </c>
+      <c r="F385" t="s">
+        <v>94</v>
+      </c>
+      <c r="G385">
+        <v>235</v>
+      </c>
+      <c r="H385" t="s">
+        <v>22</v>
+      </c>
+      <c r="I385">
+        <v>1</v>
+      </c>
+      <c r="J385" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A386" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B386" t="s">
+        <v>160</v>
+      </c>
+      <c r="C386" t="s">
+        <v>24</v>
+      </c>
+      <c r="D386" t="s">
+        <v>25</v>
+      </c>
+      <c r="E386" t="s">
+        <v>53</v>
+      </c>
+      <c r="F386" t="s">
+        <v>94</v>
+      </c>
+      <c r="G386">
+        <v>255</v>
+      </c>
+      <c r="H386" t="s">
+        <v>22</v>
+      </c>
+      <c r="I386">
+        <v>1</v>
+      </c>
+      <c r="J386" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B387" t="s">
+        <v>78</v>
+      </c>
+      <c r="C387" t="s">
+        <v>18</v>
+      </c>
+      <c r="D387" t="s">
+        <v>21</v>
+      </c>
+      <c r="E387" t="s">
+        <v>53</v>
+      </c>
+      <c r="F387" t="s">
+        <v>94</v>
+      </c>
+      <c r="G387">
+        <v>240</v>
+      </c>
+      <c r="H387" t="s">
+        <v>22</v>
+      </c>
+      <c r="I387">
+        <v>1</v>
+      </c>
+      <c r="J387" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B388" t="s">
+        <v>112</v>
+      </c>
+      <c r="C388" t="s">
+        <v>18</v>
+      </c>
+      <c r="D388" t="s">
+        <v>90</v>
+      </c>
+      <c r="E388" t="s">
+        <v>53</v>
+      </c>
+      <c r="F388" t="s">
+        <v>94</v>
+      </c>
+      <c r="G388">
+        <v>240</v>
+      </c>
+      <c r="H388" t="s">
+        <v>22</v>
+      </c>
+      <c r="I388">
+        <v>1</v>
+      </c>
+      <c r="J388" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B389" t="s">
+        <v>113</v>
+      </c>
+      <c r="C389" t="s">
+        <v>24</v>
+      </c>
+      <c r="D389" t="s">
+        <v>25</v>
+      </c>
+      <c r="E389" t="s">
+        <v>53</v>
+      </c>
+      <c r="F389" t="s">
+        <v>94</v>
+      </c>
+      <c r="G389">
+        <v>245</v>
+      </c>
+      <c r="H389" t="s">
+        <v>22</v>
+      </c>
+      <c r="I389">
+        <v>1</v>
+      </c>
+      <c r="J389" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B390" t="s">
+        <v>161</v>
+      </c>
+      <c r="C390" t="s">
+        <v>18</v>
+      </c>
+      <c r="D390" t="s">
+        <v>90</v>
+      </c>
+      <c r="E390" t="s">
+        <v>53</v>
+      </c>
+      <c r="F390" t="s">
+        <v>94</v>
+      </c>
+      <c r="G390">
+        <v>240</v>
+      </c>
+      <c r="H390" t="s">
+        <v>22</v>
+      </c>
+      <c r="I390">
+        <v>1</v>
+      </c>
+      <c r="J390" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B391" t="s">
+        <v>162</v>
+      </c>
+      <c r="C391" t="s">
+        <v>18</v>
+      </c>
+      <c r="D391" t="s">
+        <v>90</v>
+      </c>
+      <c r="E391" t="s">
+        <v>53</v>
+      </c>
+      <c r="F391" t="s">
+        <v>94</v>
+      </c>
+      <c r="G391">
+        <v>255</v>
+      </c>
+      <c r="H391" t="s">
+        <v>22</v>
+      </c>
+      <c r="I391">
+        <v>1</v>
+      </c>
+      <c r="J391" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B392" t="s">
+        <v>101</v>
+      </c>
+      <c r="C392" t="s">
+        <v>24</v>
+      </c>
+      <c r="D392" t="s">
+        <v>38</v>
+      </c>
+      <c r="E392" t="s">
+        <v>53</v>
+      </c>
+      <c r="F392" t="s">
+        <v>94</v>
+      </c>
+      <c r="G392">
+        <v>280</v>
+      </c>
+      <c r="H392" t="s">
+        <v>15</v>
+      </c>
+      <c r="I392">
+        <v>1</v>
+      </c>
+      <c r="J392" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A393" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B393" t="s">
+        <v>67</v>
+      </c>
+      <c r="C393" t="s">
+        <v>24</v>
+      </c>
+      <c r="D393" t="s">
+        <v>40</v>
+      </c>
+      <c r="E393" t="s">
+        <v>53</v>
+      </c>
+      <c r="F393" t="s">
+        <v>94</v>
+      </c>
+      <c r="G393">
+        <v>240</v>
+      </c>
+      <c r="H393" t="s">
+        <v>22</v>
+      </c>
+      <c r="I393">
+        <v>1</v>
+      </c>
+      <c r="J393" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A394" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B394" t="s">
+        <v>48</v>
+      </c>
+      <c r="C394" t="s">
+        <v>24</v>
+      </c>
+      <c r="D394" t="s">
+        <v>49</v>
+      </c>
+      <c r="E394" t="s">
+        <v>53</v>
+      </c>
+      <c r="F394" t="s">
+        <v>94</v>
+      </c>
+      <c r="G394">
+        <v>245</v>
+      </c>
+      <c r="H394" t="s">
+        <v>22</v>
+      </c>
+      <c r="I394">
+        <v>1</v>
+      </c>
+      <c r="J394" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A395" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B395" t="s">
+        <v>78</v>
+      </c>
+      <c r="C395" t="s">
+        <v>18</v>
+      </c>
+      <c r="D395" t="s">
+        <v>21</v>
+      </c>
+      <c r="E395" t="s">
+        <v>53</v>
+      </c>
+      <c r="F395" t="s">
+        <v>94</v>
+      </c>
+      <c r="G395">
+        <v>240</v>
+      </c>
+      <c r="H395" t="s">
+        <v>22</v>
+      </c>
+      <c r="I395">
+        <v>1</v>
+      </c>
+      <c r="J395" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A396" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B396" t="s">
+        <v>161</v>
+      </c>
+      <c r="C396" t="s">
+        <v>18</v>
+      </c>
+      <c r="D396" t="s">
+        <v>90</v>
+      </c>
+      <c r="E396" t="s">
+        <v>53</v>
+      </c>
+      <c r="F396" t="s">
+        <v>94</v>
+      </c>
+      <c r="G396">
+        <v>240</v>
+      </c>
+      <c r="H396" t="s">
+        <v>22</v>
+      </c>
+      <c r="I396">
+        <v>1</v>
+      </c>
+      <c r="J396" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A397" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B397" t="s">
+        <v>112</v>
+      </c>
+      <c r="C397" t="s">
+        <v>18</v>
+      </c>
+      <c r="D397" t="s">
+        <v>90</v>
+      </c>
+      <c r="E397" t="s">
+        <v>53</v>
+      </c>
+      <c r="F397" t="s">
+        <v>94</v>
+      </c>
+      <c r="G397">
+        <v>240</v>
+      </c>
+      <c r="H397" t="s">
+        <v>22</v>
+      </c>
+      <c r="I397">
+        <v>1</v>
+      </c>
+      <c r="J397" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A398" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B398" t="s">
+        <v>80</v>
+      </c>
+      <c r="C398" t="s">
+        <v>18</v>
+      </c>
+      <c r="D398" t="s">
+        <v>21</v>
+      </c>
+      <c r="E398" t="s">
+        <v>53</v>
+      </c>
+      <c r="F398" t="s">
+        <v>94</v>
+      </c>
+      <c r="G398">
+        <v>250</v>
+      </c>
+      <c r="H398" t="s">
+        <v>22</v>
+      </c>
+      <c r="I398">
+        <v>1</v>
+      </c>
+      <c r="J398" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A399" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B399" t="s">
+        <v>58</v>
+      </c>
+      <c r="C399" t="s">
+        <v>24</v>
+      </c>
+      <c r="D399" t="s">
+        <v>38</v>
+      </c>
+      <c r="E399" t="s">
+        <v>100</v>
+      </c>
+      <c r="F399" t="s">
+        <v>94</v>
+      </c>
+      <c r="G399">
+        <v>275</v>
+      </c>
+      <c r="H399" t="s">
+        <v>15</v>
+      </c>
+      <c r="I399">
+        <v>1</v>
+      </c>
+      <c r="J399" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A400" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B400" t="s">
+        <v>104</v>
+      </c>
+      <c r="C400" t="s">
+        <v>18</v>
+      </c>
+      <c r="D400" t="s">
+        <v>90</v>
+      </c>
+      <c r="E400" t="s">
+        <v>100</v>
+      </c>
+      <c r="F400" t="s">
+        <v>94</v>
+      </c>
+      <c r="G400">
+        <v>250</v>
+      </c>
+      <c r="H400" t="s">
+        <v>22</v>
+      </c>
+      <c r="I400">
+        <v>1</v>
+      </c>
+      <c r="J400" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A401" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B401" t="s">
+        <v>163</v>
+      </c>
+      <c r="C401" t="s">
+        <v>24</v>
+      </c>
+      <c r="D401" t="s">
+        <v>25</v>
+      </c>
+      <c r="E401" t="s">
+        <v>100</v>
+      </c>
+      <c r="F401" t="s">
+        <v>94</v>
+      </c>
+      <c r="G401">
+        <v>250</v>
+      </c>
+      <c r="H401" t="s">
+        <v>22</v>
+      </c>
+      <c r="I401">
+        <v>1</v>
+      </c>
+      <c r="J401" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A402" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B402" t="s">
+        <v>75</v>
+      </c>
+      <c r="C402" t="s">
+        <v>18</v>
+      </c>
+      <c r="D402" t="s">
+        <v>21</v>
+      </c>
+      <c r="E402" t="s">
+        <v>100</v>
+      </c>
+      <c r="F402" t="s">
+        <v>94</v>
+      </c>
+      <c r="G402">
+        <v>250</v>
+      </c>
+      <c r="H402" t="s">
+        <v>22</v>
+      </c>
+      <c r="I402">
+        <v>1</v>
+      </c>
+      <c r="J402" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A403" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B403" t="s">
+        <v>34</v>
+      </c>
+      <c r="C403" t="s">
+        <v>24</v>
+      </c>
+      <c r="D403" t="s">
+        <v>33</v>
+      </c>
+      <c r="E403" t="s">
+        <v>100</v>
+      </c>
+      <c r="F403" t="s">
+        <v>94</v>
+      </c>
+      <c r="G403">
+        <v>270</v>
+      </c>
+      <c r="H403" t="s">
+        <v>15</v>
+      </c>
+      <c r="I403">
+        <v>1</v>
+      </c>
+      <c r="J403" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A404" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B404" t="s">
+        <v>59</v>
+      </c>
+      <c r="C404" t="s">
+        <v>24</v>
+      </c>
+      <c r="D404" t="s">
+        <v>47</v>
+      </c>
+      <c r="E404" t="s">
+        <v>100</v>
+      </c>
+      <c r="F404" t="s">
+        <v>94</v>
+      </c>
+      <c r="G404">
+        <v>240</v>
+      </c>
+      <c r="H404" t="s">
+        <v>22</v>
+      </c>
+      <c r="I404">
+        <v>1</v>
+      </c>
+      <c r="J404" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A405" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B405" t="s">
+        <v>75</v>
+      </c>
+      <c r="C405" t="s">
+        <v>18</v>
+      </c>
+      <c r="D405" t="s">
+        <v>21</v>
+      </c>
+      <c r="E405" t="s">
+        <v>100</v>
+      </c>
+      <c r="F405" t="s">
+        <v>94</v>
+      </c>
+      <c r="G405">
+        <v>250</v>
+      </c>
+      <c r="H405" t="s">
+        <v>22</v>
+      </c>
+      <c r="I405">
+        <v>1</v>
+      </c>
+      <c r="J405" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A406" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B406" t="s">
+        <v>32</v>
+      </c>
+      <c r="C406" t="s">
+        <v>24</v>
+      </c>
+      <c r="D406" t="s">
+        <v>33</v>
+      </c>
+      <c r="E406" t="s">
+        <v>100</v>
+      </c>
+      <c r="F406" t="s">
+        <v>94</v>
+      </c>
+      <c r="G406">
+        <v>265</v>
+      </c>
+      <c r="H406" t="s">
+        <v>15</v>
+      </c>
+      <c r="I406">
+        <v>1</v>
+      </c>
+      <c r="J406" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A407" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B407" t="s">
+        <v>89</v>
+      </c>
+      <c r="C407" t="s">
+        <v>18</v>
+      </c>
+      <c r="D407" t="s">
+        <v>90</v>
+      </c>
+      <c r="E407" t="s">
+        <v>100</v>
+      </c>
+      <c r="F407" t="s">
+        <v>94</v>
+      </c>
+      <c r="G407">
+        <v>235</v>
+      </c>
+      <c r="H407" t="s">
+        <v>22</v>
+      </c>
+      <c r="I407">
+        <v>1</v>
+      </c>
+      <c r="J407" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A408" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B408" t="s">
+        <v>107</v>
+      </c>
+      <c r="C408" t="s">
+        <v>24</v>
+      </c>
+      <c r="D408" t="s">
+        <v>38</v>
+      </c>
+      <c r="E408" t="s">
+        <v>100</v>
+      </c>
+      <c r="F408" t="s">
+        <v>94</v>
+      </c>
+      <c r="G408">
+        <v>270</v>
+      </c>
+      <c r="H408" t="s">
+        <v>15</v>
+      </c>
+      <c r="I408">
+        <v>1</v>
+      </c>
+      <c r="J408" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A409" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B409" t="s">
+        <v>164</v>
+      </c>
+      <c r="C409" t="s">
+        <v>24</v>
+      </c>
+      <c r="D409" t="s">
+        <v>33</v>
+      </c>
+      <c r="E409" t="s">
+        <v>100</v>
+      </c>
+      <c r="F409" t="s">
+        <v>94</v>
+      </c>
+      <c r="G409">
+        <v>275</v>
+      </c>
+      <c r="H409" t="s">
+        <v>15</v>
+      </c>
+      <c r="I409">
+        <v>1</v>
+      </c>
+      <c r="J409" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A410" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B410" t="s">
+        <v>74</v>
+      </c>
+      <c r="C410" t="s">
+        <v>18</v>
+      </c>
+      <c r="D410" t="s">
+        <v>21</v>
+      </c>
+      <c r="E410" t="s">
+        <v>100</v>
+      </c>
+      <c r="F410" t="s">
+        <v>94</v>
+      </c>
+      <c r="G410">
+        <v>245</v>
+      </c>
+      <c r="H410" t="s">
+        <v>22</v>
+      </c>
+      <c r="I410">
+        <v>1</v>
+      </c>
+      <c r="J410" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07114E84-9459-4B6F-B54E-5E85FD29AF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D064DC-2819-422C-B235-88B3A32ADE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F298818A-6462-4701-BFAF-ACE0211CC93D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="1" xr2:uid="{F298818A-6462-4701-BFAF-ACE0211CC93D}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -16467,6 +16467,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65318CB5-FF34-4AD3-9AE9-35631C91F845}">
   <dimension ref="A1:J410"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
